--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -118,7 +118,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Viewing Range=[22/02/26 - 20/05/26]</t>
+          <t>Viewing Range=[01/03/26 - 31/05/26]</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -128,7 +128,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report Updated=[20/05/26]
+          <t xml:space="preserve">Report Updated=[02/06/26]
 </t>
         </is>
       </c>
@@ -207,10 +207,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5782248.19</v>
+        <v>6101948.71</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1426.0</v>
+        <v>1502.0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0.0</v>
@@ -219,10 +219,10 @@
         <v>0.0</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1426.0</v>
+        <v>1507.0</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>377.0</v>
+        <v>371.0</v>
       </c>
     </row>
     <row r="4">
@@ -247,10 +247,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5279833.6</v>
+        <v>5514962.55</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>2351.0</v>
+        <v>2451.0</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.0</v>
@@ -259,10 +259,10 @@
         <v>0.0</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2345.0</v>
+        <v>2454.0</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>450.0</v>
+        <v>475.0</v>
       </c>
     </row>
     <row r="5">
@@ -287,10 +287,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2555174.17</v>
+        <v>2550980.84</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>343.0</v>
+        <v>341.0</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.0</v>
@@ -299,7 +299,7 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>344.0</v>
+        <v>340.0</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>104.0</v>
@@ -308,17 +308,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array AM-W45 Wireless Conference Microphone with Speaker | Bluetooth, USB &amp; 4 Mics | 360° Pickup Upto 4M | Noise Reduction &amp; Enhanced Voice | Portable Speakerphone for Video Calls/Zoom Meeting</t>
+          <t>White Mulberry |DIY| Wall Mounted Monitor Stand Mount | Supports 15-32 Inch Screens| 9 Kg Screen Load | VESA 75X75 &amp; 100X100 | Spring Assisted Wall Mounted Monitor Mount | Black - (Single Screen)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -327,10 +327,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1549822.04</v>
+        <v>1766989.74</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>360.0</v>
+        <v>714.0</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0.0</v>
@@ -339,26 +339,26 @@
         <v>0.0</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>352.0</v>
+        <v>705.0</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>32.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>White Mulberry |DIY| Wall Mounted Monitor Stand Mount | Supports 15-32 Inch Screens| 9 Kg Screen Load | VESA 75X75 &amp; 100X100 | Spring Assisted Wall Mounted Monitor Mount | Black - (Single Screen)</t>
+          <t>Audio Array AM-W45 Wireless Conference Microphone with Speaker | Bluetooth, USB &amp; 4 Mics | 360° Pickup Upto 4M | Noise Reduction &amp; Enhanced Voice | Portable Speakerphone for Video Calls/Zoom Meeting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -367,10 +367,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1547386.33</v>
+        <v>1662173.89</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>632.0</v>
+        <v>385.0</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.0</v>
@@ -379,10 +379,10 @@
         <v>0.0</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>623.0</v>
+        <v>380.0</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>65.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="8">
@@ -393,7 +393,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array Professional DJ Headphones | Studio Headphone | 50mm Drivers | 32Ω | 20Hz-20kHz | Dual Detachable Cables With Mic &amp; Controls | Buddy Share Technology | 105 dB SPL | Monitoring,Mixing AH-50</t>
+          <t>Audio Array Professional DJ Headphones| Studio Headphone| 50mm Drivers| 32Ω | 20Hz-20kHz | Dual Detachable Cables with Mic &amp; Controls| Buddy Share Technology | 105 dB SPL | Monitoring,Mixing| AH-50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -407,10 +407,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1272253.78</v>
+        <v>1419637.3</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>745.0</v>
+        <v>832.0</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.0</v>
@@ -419,10 +419,10 @@
         <v>0.0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>741.0</v>
+        <v>836.0</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>124.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="9">
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1146808.65</v>
+        <v>1390705.15</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>495.0</v>
+        <v>597.0</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0.0</v>
@@ -459,21 +459,21 @@
         <v>0.0</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>493.0</v>
+        <v>588.0</v>
       </c>
       <c r="J9" s="1" t="n">
-        <v>138.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array Mic AM-C46 Professional RGB USB Condenser Mic Kit | AI Noise-Cancellation, Mute, Monitoring &amp; Volume Controls | 192kHz/24bit Studio Quality | Gaming, Streaming, Podcast | Mac/PC/Mobile</t>
+          <t>Audio Array Studio Monitors Speaker Pair 3.5" | 50W RMS with Bluetooth 5.0 | Fiberglass Woofer &amp; 1″ Silk Dome Tweeter, Class-D | TI 3116D2 Amp | TRS, RCA, AUX Inputs, Bass &amp; Treble Control | AM-S2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1017486.56</v>
+        <v>1293937.05</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>342.0</v>
+        <v>223.0</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.0</v>
@@ -499,21 +499,21 @@
         <v>0.0</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>342.0</v>
+        <v>216.0</v>
       </c>
       <c r="J10" s="1" t="n">
-        <v>63.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array Studio Monitors Speaker Pair 3.5" | 50W RMS with Bluetooth 5.0 | Fiberglass Woofer &amp; 1″ Silk Dome Tweeter, Class-D | TI 3116D2 Amp | TRS, RCA, AUX Inputs, Bass &amp; Treble Control | AM-S2</t>
+          <t>Audio Array Professional RGB USB Condenser Mic Kit | AI Noise-Cancellation, Mute, Monitoring &amp; Volume Controls | 192kHz/24bit Studio Quality | Gaming, Streaming, Podcast | Mac/PC/Mobile | AM-C46</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -527,10 +527,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>843153.69</v>
+        <v>999453.33</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>147.0</v>
+        <v>337.0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.0</v>
@@ -539,10 +539,10 @@
         <v>0.0</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>141.0</v>
+        <v>343.0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>19.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="12">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>840942.72</v>
+        <v>893673.34</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>268.0</v>
+        <v>284.0</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0.0</v>
@@ -579,10 +579,10 @@
         <v>0.0</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>269.0</v>
+        <v>282.0</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="13">
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>668336.92</v>
+        <v>698255.52</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>206.0</v>
+        <v>215.0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.0</v>
@@ -619,10 +619,10 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>201.0</v>
+        <v>209.0</v>
       </c>
       <c r="J13" s="1" t="n">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="14">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>646004.53</v>
+        <v>692733.32</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>282.0</v>
+        <v>302.0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0.0</v>
@@ -659,21 +659,21 @@
         <v>0.0</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>283.0</v>
+        <v>303.0</v>
       </c>
       <c r="J14" s="1" t="n">
-        <v>50.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array AI-10 Professional Live Soundcard|1Ch Mixer |Bluetooth | 3 Condenser Mic Inputs, 2 mobilephones &amp; PC/Mac Outputs | +48V phantom power, 4 Voice Modes, Denoise, built-in FX | Gaming, Karaoke</t>
+          <t>Audio Array Professional Studio Recording Bundle – XLR Condenser Mic Kit, 2x2 USB Audio Interface, Closed-Back Headphone, Boom Arm, Pop Filter &amp; 48V Phantom Power| 24-bit/192kHz Podcast Kit - PB-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>510870.55</v>
+        <v>575196.6</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>199.0</v>
+        <v>68.0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.0</v>
@@ -699,21 +699,21 @@
         <v>0.0</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>198.0</v>
+        <v>67.0</v>
       </c>
       <c r="J15" s="1" t="n">
-        <v>71.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Audio Array Professional Studio Recording Bundle – XLR Condenser Mic Kit, 2x2 USB Audio Interface, Closed-Back Headphone, Boom Arm, Pop Filter &amp; 48V Phantom Power| 24-bit/192kHz Podcast Kit - PB-10</t>
+          <t>Audio Array AM-C2 XLR Condenser Microphone Kit | Boom Arm, 2M Cable, Pop Filter &amp; Mic Cover | Compatible with Audio Interface, Mixer &amp; preamp | Recording, Podcasting, Streaming, Home Studio (Black)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>498933.06</v>
+        <v>519313.66</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>59.0</v>
+        <v>162.0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.0</v>
@@ -739,21 +739,21 @@
         <v>0.0</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>59.0</v>
+        <v>160.0</v>
       </c>
       <c r="J16" s="1" t="n">
-        <v>12.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Audio Array AM-C2 XLR Condenser Microphone Kit | Boom Arm, 2M Cable, Pop Filter &amp; Mic Cover | Compatible with Audio Interface, Mixer &amp; preamp | Recording, Podcasting, Streaming, Home Studio (Black)</t>
+          <t>Audio Array Latest 2026 Edition Audio Mixer 8 Channel Hybrid USB Sound Mixer (6 Analog+2 Digital) Recording Monitoring &amp; Live, 192kHz/24-Bit OTG, 99 DSP FX, 4 XLR Mic Inputs, Phantom Power, Hi-Z M8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>490633.13</v>
+        <v>518749.02</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>153.0</v>
+        <v>76.0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.0</v>
@@ -779,21 +779,21 @@
         <v>0.0</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>150.0</v>
+        <v>75.0</v>
       </c>
       <c r="J17" s="1" t="n">
-        <v>25.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Audio Array AM-C43 XLR to 3.5mm Professional Condenser Microphone Kit | Boom Arm, 2M Cable &amp; Foam Filter | Compatible with Audio Interface, Mixer | Recording, Podcast, Streaming, Home Studio (Black)</t>
+          <t>Audio Array AI-10 Professional Live Soundcard|1Ch Mixer |Bluetooth | 3 Condenser Mic Inputs, 2 mobilephones &amp; PC/Mac Outputs | +48V phantom power, 4 Voice Modes, Denoise, built-in FX | Gaming, Karaoke</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>472796.98</v>
+        <v>517394.25</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>225.0</v>
+        <v>201.0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.0</v>
@@ -819,21 +819,21 @@
         <v>0.0</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>225.0</v>
+        <v>198.0</v>
       </c>
       <c r="J18" s="1" t="n">
-        <v>51.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Audio Array M8 Latest 2026 Edition 8-Channel Hybrid USB Summing Mixer (6 Analog + 2 Digital) for Recording &amp; Live, 192kHz/24-Bit OTG, 99 DSP FX, 4 XLR Mic Inputs, Phantom Power, Hi-Z &amp; Monitoring</t>
+          <t>Audio Array AM-C43 XLR to 3.5mm Professional Condenser Microphone Kit | Boom Arm, 2M Cable &amp; Foam Filter | Compatible with Audio Interface, Mixer | Recording, Podcast, Streaming, Home Studio (Black)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>462230.35</v>
+        <v>487693.66</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>68.0</v>
+        <v>232.0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.0</v>
@@ -859,10 +859,10 @@
         <v>0.0</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>68.0</v>
+        <v>231.0</v>
       </c>
       <c r="J19" s="1" t="n">
-        <v>13.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="20">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>439336.55</v>
+        <v>472832.93</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>334.0</v>
+        <v>358.0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.0</v>
@@ -899,10 +899,10 @@
         <v>0.0</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>330.0</v>
+        <v>357.0</v>
       </c>
       <c r="J20" s="1" t="n">
-        <v>58.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="21">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>418055.97</v>
+        <v>428449.15</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>314.0</v>
+        <v>321.0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0.0</v>
@@ -939,10 +939,10 @@
         <v>0.0</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>308.0</v>
+        <v>316.0</v>
       </c>
       <c r="J21" s="1" t="n">
-        <v>42.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="22">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>402729.32</v>
+        <v>407029.35</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>207.0</v>
+        <v>209.0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.0</v>
@@ -979,26 +979,26 @@
         <v>0.0</v>
       </c>
       <c r="I22" s="1" t="n">
-        <v>207.0</v>
+        <v>209.0</v>
       </c>
       <c r="J22" s="1" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Audio Array AI-11 USB Bluetooth Soundcard, 1Ch Mixer, Audio Interface | 2 Condenser In, 2 Out |2 Live Out+1 Accompany In | OTG for mobile and PC/MAC | Effects | Streaming, Podcasting, Gaming, Singing</t>
+          <t>TONOR TC777 Pro Gaming USB Microphone for PC, RGB Condenser Computer Mic with Tripod Stand, Quick Mute, Gain Control, for Gaming, Streaming, Podcasting, Recording, Cardioid Mic Kit for Laptop/PS4/PS5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>290639.5</v>
+        <v>328598.85</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>221.0</v>
+        <v>203.0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.0</v>
@@ -1019,10 +1019,10 @@
         <v>0.0</v>
       </c>
       <c r="I23" s="1" t="n">
-        <v>215.0</v>
+        <v>198.0</v>
       </c>
       <c r="J23" s="1" t="n">
-        <v>60.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="24">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Audio Array AA-26 Tabletop Metal Microphone Stand | Extendable height up to 22cm | Studio Sound Recording, Streaming, Podcasting, Singing | Stylish Sturdy Metal Design to last long, flat base</t>
+          <t>Audio Array Metal Mic Stand | Extendable height up to 22cm | Mic Stand For Table | Studio Sound Recording, Streaming, Podcasting, Singing | Stylish Sturdy Metal Design to last long, flat base | AA-26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>287422.77</v>
+        <v>323201.9</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>623.0</v>
+        <v>694.0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0.0</v>
@@ -1059,21 +1059,21 @@
         <v>0.0</v>
       </c>
       <c r="I24" s="1" t="n">
-        <v>621.0</v>
+        <v>694.0</v>
       </c>
       <c r="J24" s="1" t="n">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Audio Array AM-W18 Wireless Karaoke Speaker with Microphone | Portable Bluetooth Speaker for Singing &amp; Gifting with Voice Changer | Upto 8+ Hours of Playback | Bluetooth v5.3, SD Card &amp; AUX in (Pink)</t>
+          <t>Audio Array AI-11 USB Bluetooth Soundcard, 1Ch Mixer, Audio Interface | 2 Condenser In, 2 Out |2 Live Out+1 Accompany In | OTG for mobile and PC/MAC | Effects | Streaming, Podcasting, Gaming, Singing</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>287028.67</v>
+        <v>302073.45</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>286.0</v>
+        <v>229.0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0.0</v>
@@ -1099,26 +1099,26 @@
         <v>0.0</v>
       </c>
       <c r="I25" s="1" t="n">
-        <v>285.0</v>
+        <v>224.0</v>
       </c>
       <c r="J25" s="1" t="n">
-        <v>34.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TONOR TC777 Pro Gaming USB Microphone for PC, RGB Condenser Computer Mic with Tripod Stand, Quick Mute, Gain Control, for Gaming, Streaming, Podcasting, Recording, Cardioid Mic Kit for Laptop/PS4/PS5</t>
+          <t>White Mulberry Dual Monitor Arm | Height Adjustable Monitor Arm Desk Mount | Steel Dual Screen Mount for 17-32 Inch Monitors 10kg Load VESA 75x75 100x100 | Adjustable Ergonomic Desk Setup</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>284129.32</v>
+        <v>290658.97</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>177.0</v>
+        <v>172.0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0.0</v>
@@ -1139,10 +1139,10 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="1" t="n">
-        <v>176.0</v>
+        <v>173.0</v>
       </c>
       <c r="J26" s="1" t="n">
-        <v>36.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="27">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Audio Array AH-40-SL Wired Over-Ear Headphones | 40mm Drivers, 15-22KHz, 32Ω, 105dB SPL Sound, Studio Monitoring, Gaming, Live Music Headset with 3.5mm + 6.3mm Plug Compatibility</t>
+          <t>Audio Array AH-40-SL Wired Over-Ear Headphones | 40mm Drivers, 15-22KHz, 32Ω, 105dB SPL | Studio Monitoring, Gaming, Live Music Headset with 3.5mm + 6.3mm Plug Compatibility</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>279681.74</v>
+        <v>277400.46</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>275.0</v>
+        <v>267.0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0.0</v>
@@ -1179,21 +1179,21 @@
         <v>0.0</v>
       </c>
       <c r="I27" s="1" t="n">
-        <v>277.0</v>
+        <v>267.0</v>
       </c>
       <c r="J27" s="1" t="n">
-        <v>53.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Audio Array AM-C11 Pro XLR/USB Professional Dynamic Mic Kit | Premium Metal 96kHz/24bit Studio Quality | 2M XLR &amp; USB Cables,Volume Control,Mute &amp; Realtime Monitoring | Streaming,Gaming &amp; podcasting</t>
+          <t>Audio Array AM-W18 Wireless Karaoke Speaker with Microphone | Portable Bluetooth Speaker for Singing &amp; Gifting with Voice Changer | Upto 8+ Hours of Playback | Bluetooth v5.3, SD Card &amp; AUX in (Pink)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>251963.37</v>
+        <v>263615.92</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>60.0</v>
+        <v>263.0</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>0.0</v>
@@ -1219,21 +1219,21 @@
         <v>0.0</v>
       </c>
       <c r="I28" s="1" t="n">
-        <v>60.0</v>
+        <v>263.0</v>
       </c>
       <c r="J28" s="1" t="n">
-        <v>6.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>White Mulberry Dual Monitor Arm | Height Adjustable Monitor Arm Desk Mount | Steel Dual Screen Mount for 17-32 Inch Monitors 10kg Load VESA 75x75 100x100 | Adjustable Ergonomic Desk Setup</t>
+          <t>White Mulberry Monitor Arm | Wooden Metal Single Screen Desk Mount for 15-32 Inch Monitors | Monitor Arm Desk Mount | Gas Spring Adjustable Arms | 9Kg Capacity | VESA 75x75 &amp; 100x100</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>244072.6</v>
+        <v>238028.17</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>144.0</v>
+        <v>91.0</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0.0</v>
@@ -1259,21 +1259,21 @@
         <v>0.0</v>
       </c>
       <c r="I29" s="1" t="n">
-        <v>142.0</v>
+        <v>91.0</v>
       </c>
       <c r="J29" s="1" t="n">
-        <v>17.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Audio Array AM-W36 UHF Dual Wireless Premium Metal Microphone with Charging | 2X XLR Outs &amp; 1/4" Mix Out | 328ft/100M Range | Karaoke Singing, Wedding, Events | PA System, Amplifier, Mixer, Party Box</t>
+          <t>Audio Array AM-C11 Pro XLR/USB Professional Dynamic Mic Kit | Premium Metal 96kHz/24bit Studio Quality | 2M XLR &amp; USB Cables,Volume Control,Mute &amp; Realtime Monitoring | Streaming,Gaming &amp; podcasting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>232389.01</v>
+        <v>234861.26</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>44.0</v>
+        <v>56.0</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>0.0</v>
@@ -1299,26 +1299,26 @@
         <v>0.0</v>
       </c>
       <c r="I30" s="1" t="n">
-        <v>44.0</v>
+        <v>56.0</v>
       </c>
       <c r="J30" s="1" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TONOR Dynamic USB/Type-C Microphone for PC, RGB Podcast Computer Gaming Microphone with Arm Stand for Recording, Live, Streaming, YouTube, Vocals, Studio, Karaoke Microphone, Quick Mute Button, Black</t>
+          <t>Audio Array 8-Channel Hybrid USB Audio Mixer with 8 Analog + 2 Digital Inputs, 48kHz/16-Bit Processing, +50dB Gain, Combo XLR, Phantom Power, Hi-Z, 3-Band EQ, 99 DSP FX, Balanced XLR Output | AI-14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>199195.56</v>
+        <v>234624.7</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>119.0</v>
+        <v>43.0</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>0.0</v>
@@ -1339,26 +1339,26 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="1" t="n">
-        <v>120.0</v>
+        <v>42.0</v>
       </c>
       <c r="J31" s="1" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm | Wooden Metal Single Screen Desk Mount for 15-32 Inch Monitors | Monitor Arm Desk Mount | Gas Spring Adjustable Arms | 9Kg Capacity | VESA 75x75 &amp; 100x100</t>
+          <t>Audio Array AM-W36 UHF Dual Wireless Premium Metal Microphone with Charging | 2X XLR Outs &amp; 1/4" Mix Out | 328ft/100M Range | Karaoke Singing, Wedding, Events | PA System, Amplifier, Mixer, Party Box</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>198580.61</v>
+        <v>216658.5</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>76.0</v>
+        <v>41.0</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>0.0</v>
@@ -1379,26 +1379,26 @@
         <v>0.0</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>77.0</v>
+        <v>41.0</v>
       </c>
       <c r="J32" s="1" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Audio Array AM-C44 XLR/USB Professional Dynamic Podcast Microphone | Built-in Monitoring | One Touch Mute &amp; Volume Control | 192kHz/24bit Full Metal Build | 2M XLR &amp; USB Cable | Streaming, Podcasting</t>
+          <t>TONOR USB Microphone, Condenser Computer PC Mic with Tripod Stand, Metal,Pop Filter, Shock Mount for Gaming,Streaming,Podcasting,YouTube, Voice Over,Skype, Twitch,Compatible with Laptop Desktop, TC30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>194127.85</v>
+        <v>202871.26</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>49.0</v>
+        <v>110.0</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>0.0</v>
@@ -1419,21 +1419,21 @@
         <v>0.0</v>
       </c>
       <c r="I33" s="1" t="n">
-        <v>49.0</v>
+        <v>109.0</v>
       </c>
       <c r="J33" s="1" t="n">
-        <v>13.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Audio Array AM-C10 USB Plug &amp; Play Conference Microphone with Speaker | Omni Directional Pickup Upto 4M | Speaker and Mic Mute Buttons | Volume Control &amp; Mute Button | Ideal for Meeting &amp; Video Call</t>
+          <t>Audio Array AA-02 3-Panel Curved Isolation Shield with Insulation, Absorption &amp; Reflection Filter | 3/8" and 5/8" Universal Mic Mount for Recording Studio, Podcasts, Singing &amp; Broadcasting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>192476.54</v>
+        <v>199995.17</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>58.0</v>
+        <v>95.0</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>0.0</v>
@@ -1459,26 +1459,26 @@
         <v>0.0</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>58.0</v>
+        <v>92.0</v>
       </c>
       <c r="J34" s="1" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TONOR USB Microphone, Condenser Computer PC Mic with Tripod Stand, Metal,Pop Filter, Shock Mount for Gaming,Streaming,Podcasting,YouTube, Voice Over,Skype, Twitch,Compatible with Laptop Desktop, TC30</t>
+          <t>Audio Array AM-C10 USB Plug &amp; Play Conference Microphone with Speaker | Omni Directional Pickup Upto 4M | Speaker and Mic Mute Buttons | Volume Control &amp; Mute Button | Ideal for Meeting &amp; Video Call</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>191986.49</v>
+        <v>195960.43</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>104.0</v>
+        <v>59.0</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>0.0</v>
@@ -1499,26 +1499,26 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>100.0</v>
+        <v>58.0</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Audio Array AA-02 3-Panel Curved Isolation Shield with Insulation, Absorption &amp; Reflection Filter | 3/8" and 5/8" Universal Mic Mount for Recording Studio, Podcasts, Singing &amp; Broadcasting</t>
+          <t>TONOR Dynamic USB/Type-C Microphone for PC, RGB Podcast Computer Gaming Microphone with Arm Stand for Recording, Live, Streaming, YouTube, Vocals, Studio, Karaoke Microphone, Quick Mute Button, Black</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>189395.11</v>
+        <v>188947.29</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>90.0</v>
+        <v>112.0</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>0.0</v>
@@ -1539,21 +1539,21 @@
         <v>0.0</v>
       </c>
       <c r="I36" s="1" t="n">
-        <v>91.0</v>
+        <v>112.0</v>
       </c>
       <c r="J36" s="1" t="n">
-        <v>12.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Audio Array AI-03 Professional Sound Card with Bluetooth | Podcast Production Setup with 4 mic input &amp; 4 outputs | +48V phantom power, PC/Mac connectivity | 6-8hr Battery | Streaming, Singing &amp; Gaming</t>
+          <t>Audio Array AM-C44 XLR/USB Professional Dynamic Podcast Microphone | Built-in Monitoring | One Touch Mute &amp; Volume Control | 192kHz/24bit Full Metal Build | 2M XLR &amp; USB Cable | Streaming, Podcasting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>181057.07</v>
+        <v>186507.51</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>56.0</v>
+        <v>47.0</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>0.0</v>
@@ -1579,10 +1579,10 @@
         <v>0.0</v>
       </c>
       <c r="I37" s="1" t="n">
-        <v>57.0</v>
+        <v>47.0</v>
       </c>
       <c r="J37" s="1" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="38">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>171302.48</v>
+        <v>185281.28</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>63.0</v>
+        <v>68.0</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>0.0</v>
@@ -1619,10 +1619,10 @@
         <v>0.0</v>
       </c>
       <c r="I38" s="1" t="n">
-        <v>59.0</v>
+        <v>68.0</v>
       </c>
       <c r="J38" s="1" t="n">
-        <v>11.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="39">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Audio Array AA-05 Suspension Boom Scissor Microphone Arm Stand | Universal clamp with mic Holder &amp; 3/8″ to 5/8″ Adapter for Shock mounts | Suitable for Stages, Studios, Broadcasting, TV Stations</t>
+          <t>Audio Array Boom Arm | Suspension Scissor Mic Arm Stand | Universal clamp with mic Holder &amp; 3/8″ to 5/8″ Adapter for Shock mounts | Suitable for Stages, Studios, Broadcasting, TV Stations | AA-05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>165060.1</v>
+        <v>183760.1</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>294.0</v>
+        <v>328.0</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>0.0</v>
@@ -1659,21 +1659,21 @@
         <v>0.0</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>295.0</v>
+        <v>325.0</v>
       </c>
       <c r="J39" s="1" t="n">
-        <v>34.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Audio Array AH-60-BL, 60Ω, Professional Monitoring Headphones | 53mm Drivers | 10Hz–30KHz | 105dB SPL | Closed-Back, DJ &amp; Studio | 3m Cable with 3.5mm &amp; 6.3mm Plugs (Blue)</t>
+          <t>Audio Array AI-03 Professional Sound Card with Bluetooth | Podcast Production Setup with 4 mic input &amp; 4 outputs | +48V phantom power, PC/Mac connectivity | 6-8hr Battery | Streaming, Singing &amp; Gaming</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>155307.66</v>
+        <v>178176.53</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>93.0</v>
+        <v>55.0</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>0.0</v>
@@ -1699,21 +1699,21 @@
         <v>0.0</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>92.0</v>
+        <v>56.0</v>
       </c>
       <c r="J40" s="1" t="n">
-        <v>15.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Audio Array AA-19BL RGB Low Profile Boomarm Stand with Riser | 71cm reach &amp; 20 RGB lighting effects &amp; Built-In Cable Management | Matte finish with Flexible adjustments | 2Kg Weight Capacity | Black</t>
+          <t>Audio Array AK-61 Pro 61-Key Portable Electronic Keyboard with LCD Display, Built-in Speakers, Mic Input &amp; Included Mics, 255 Timbres, 512 Rhythms, Battery &amp; Adapter Powered</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>150604.23</v>
+        <v>172269.16</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>0.0</v>
@@ -1742,18 +1742,18 @@
         <v>35.0</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Audio Array AM-C45 XLR/USB Professional RGB Dynamic Podcast Microphone | Built-in Monitoring | One Touch Mute Volume &amp; Noise-Cancellation | 2M USB Cable &amp; Metal Base | Streaming, Podcasting, Singing</t>
+          <t>Audio Array AH-60-BL, 60Ω, Professional Monitoring Headphones | 53mm Drivers | 10Hz–30KHz | 105dB SPL | Closed-Back, DJ &amp; Studio | 3m Cable with 3.5mm &amp; 6.3mm Plugs (Blue)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>149854.99</v>
+        <v>155700.83</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>51.0</v>
+        <v>93.0</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>0.0</v>
@@ -1779,10 +1779,10 @@
         <v>0.0</v>
       </c>
       <c r="I42" s="1" t="n">
-        <v>51.0</v>
+        <v>93.0</v>
       </c>
       <c r="J42" s="1" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="43">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Audio Array AC-6XL Mic Cable 6.35mm Jack Male to XLR 3PIN Female Cord Wire | Microphone/Guitar Cable | Black, 1pc Pack (6 Meter/19.6 Feet)</t>
+          <t>Audio Array XLR Cable | 6.35mm Jack Male to XLR 3PIN Female Cord Wire | XLR Cable For Mic/Guitar | Black, 1pc Pack (6 Meter/19.6 Feet) | AC-6XL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>143094.95</v>
+        <v>149637.42</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>310.0</v>
+        <v>324.0</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>0.0</v>
@@ -1819,21 +1819,21 @@
         <v>0.0</v>
       </c>
       <c r="I43" s="1" t="n">
-        <v>308.0</v>
+        <v>318.0</v>
       </c>
       <c r="J43" s="1" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Audio Array AK-61 Pro 61-Key Portable Electronic Keyboard with LCD Display, Built-in Speakers, Mic Input &amp; Included Mics, 255 Timbres, 512 Rhythms, Battery &amp; Adapter Powered</t>
+          <t>Audio Array AM-C45 XLR/USB Professional RGB Dynamic Podcast Microphone | Built-in Monitoring | One Touch Mute Volume &amp; Noise-Cancellation | 2M USB Cable &amp; Metal Base | Streaming, Podcasting, Singing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>139647.99</v>
+        <v>146724.47</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>0.0</v>
@@ -1859,21 +1859,21 @@
         <v>0.0</v>
       </c>
       <c r="I44" s="1" t="n">
-        <v>29.0</v>
+        <v>50.0</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Audio Array AM-C39 XLR to 3.5mm Condenser Microphone Kit | Tripod, 2M Cable &amp; Foam Filter | Compatible with Audio Interface, Mixer | Recording, Podcast, Streaming, Home Studio (Black)</t>
+          <t>Audio Array AA-22 Desktop Mount Speaker Stands | 15KG Capacity | Height, Tilt &amp; Rotation Adjustable | Smart Cable Management | for Sound Editing, Gaming, Music Production | Red (Set of 2)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>135351.76</v>
+        <v>140122.88</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>95.0</v>
+        <v>45.0</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>0.0</v>
@@ -1899,21 +1899,21 @@
         <v>0.0</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>98.0</v>
+        <v>46.0</v>
       </c>
       <c r="J45" s="1" t="n">
-        <v>35.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Audio Array AM-W12 UHF Dual Wireless Premium Metal Microphones | 4+ Hours Receiver Battery Backup | Range up to 60m| Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box, etc</t>
+          <t>Audio Array AA-19BL RGB Low Profile Boomarm Stand with Riser | 71cm reach &amp; 20 RGB lighting effects &amp; Built-In Cable Management | Matte finish with Flexible adjustments | 2Kg Weight Capacity | Black</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>130876.37</v>
+        <v>138149.15</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>39.0</v>
+        <v>33.0</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>0.0</v>
@@ -1939,21 +1939,21 @@
         <v>0.0</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>39.0</v>
+        <v>33.0</v>
       </c>
       <c r="J46" s="1" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Audio Array AA-04 Metal Spider Shock Mount for Condenser Microphone | Anti Vibration, Suspension, Isolation | 4 Size Bottom Screws &amp; Extra Replacement Elastic Bands | Recommended For Rode, Samson, etc</t>
+          <t>Audio Array AM-W12 UHF Dual Wireless Premium Metal Microphones | 4+ Hours Receiver Battery Backup | Range up to 60m| Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box, etc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>126560.17</v>
+        <v>137656.85</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>89.0</v>
+        <v>41.0</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>0.0</v>
@@ -1979,21 +1979,21 @@
         <v>0.0</v>
       </c>
       <c r="I47" s="1" t="n">
-        <v>89.0</v>
+        <v>41.0</v>
       </c>
       <c r="J47" s="1" t="n">
-        <v>25.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Audio Array 8-Channel Hybrid USB Audio Mixer with 8 Analog + 2 Digital Inputs, 48kHz/16-Bit Processing, +50dB Gain, Combo XLR, Phantom Power, Hi-Z, 3-Band EQ, 99 DSP FX, Balanced XLR Output | AI-14</t>
+          <t>Audio Array AI-12 USB Bluetooth Soundcard | 1Ch Mixer interface | 2 mic inputs, 2 smartphone &amp; PC/Mac outputs | Karaoke Recording, Mobile/PC Streaming, Live Broadcasting | Singing, Recording,Gaming</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>118964.49</v>
+        <v>137129.6</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>22.0</v>
+        <v>116.0</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>0.0</v>
@@ -2019,21 +2019,21 @@
         <v>0.0</v>
       </c>
       <c r="I48" s="1" t="n">
-        <v>22.0</v>
+        <v>113.0</v>
       </c>
       <c r="J48" s="1" t="n">
-        <v>2.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Audio Array AI-12 USB Bluetooth Soundcard | 1Ch Mixer interface | 2 mic inputs, 2 smartphone &amp; PC/Mac outputs | Karaoke Recording, Mobile/PC Streaming, Live Broadcasting | Singing, Recording,Gaming</t>
+          <t>Audio Array AA-04 Metal Spider Shock Mount for Condenser Microphone | Anti Vibration, Suspension, Isolation | 4 Size Bottom Screws &amp; Extra Replacement Elastic Bands | Recommended For Rode, Samson, etc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>115788.93</v>
+        <v>136800.05</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>98.0</v>
+        <v>96.0</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>0.0</v>
@@ -2059,21 +2059,21 @@
         <v>0.0</v>
       </c>
       <c r="I49" s="1" t="n">
-        <v>97.0</v>
+        <v>94.0</v>
       </c>
       <c r="J49" s="1" t="n">
-        <v>40.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Audio Array AM-C3 XLR to TRS Dynamic Handheld Karaoke Microphone | Premium Metal Built with 3M Cable | Singing, Public Meetings, Studio Recording, Live Show, Party, Church, Wedding</t>
+          <t>Audio Array AM-C39 XLR to 3.5mm Condenser Microphone Kit | Tripod, 2M Cable &amp; Foam Filter | Compatible with Audio Interface, Mixer | Recording, Podcast, Streaming, Home Studio (Black)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>114964.28</v>
+        <v>135139.88</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>149.0</v>
+        <v>95.0</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>0.0</v>
@@ -2099,26 +2099,26 @@
         <v>0.0</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>150.0</v>
+        <v>94.0</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>26.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TONOR USB Gaming Microphone, Computer Condenser PC Mic with Tripod Stand &amp; Pop for Streaming, Podcasting, Vocal Recording, Compatible with iMac PC Laptop Desktop Windows Computer, TC-777</t>
+          <t>White Mulberry Dual Monitor Arm | Monitor Arm Desk Mount for 15-32 Inch Screens | Dual Gas Spring Monitor Stand | 9Kg Capacity | VESA 75x75 &amp; 100x100 | Adjustable Metal Desk Mount for Dual Screens</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>110779.64</v>
+        <v>129274.54</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>64.0</v>
+        <v>33.0</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>0.0</v>
@@ -2139,26 +2139,26 @@
         <v>0.0</v>
       </c>
       <c r="I51" s="1" t="n">
-        <v>62.0</v>
+        <v>32.0</v>
       </c>
       <c r="J51" s="1" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>White Mulberry Dual Monitor Arm | Monitor Arm Desk Mount for 15-32 Inch Screens | Dual Gas Spring Monitor Stand | 9Kg Capacity | VESA 75x75 &amp; 100x100 | Adjustable Metal Desk Mount for Dual Screens</t>
+          <t>Audio Array AM-W14 UHF Dual Wireless Premium Metal Microphone | 2X XLR Outs &amp; 1/4" Mix Out | Range up to 200ft/60m | Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>110210.97</v>
+        <v>126420.35</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>0.0</v>
@@ -2179,26 +2179,26 @@
         <v>0.0</v>
       </c>
       <c r="I52" s="1" t="n">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="J52" s="1" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Audio Array AA-22 Desktop Mount Speaker Stands | 15KG Capacity | Height, Tilt &amp; Rotation Adjustable | Smart Cable Management | for Sound Editing, Gaming, Music Production | Red (Set of 2)</t>
+          <t>TONOR USB Gaming Microphone, Computer Condenser PC Mic with Tripod Stand &amp; Pop for Streaming, Podcasting, Vocal Recording, Compatible with iMac PC Laptop Desktop Windows Computer, TC-777</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>108775.42</v>
+        <v>121198.28</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>35.0</v>
+        <v>70.0</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>0.0</v>
@@ -2219,26 +2219,26 @@
         <v>0.0</v>
       </c>
       <c r="I53" s="1" t="n">
-        <v>35.0</v>
+        <v>70.0</v>
       </c>
       <c r="J53" s="1" t="n">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Audio Array AM-C11 XLR/USB Dynamic Podcast Microphone | Built-in Monitoring | One Touch Mute and Volume Control | Premium Metal Build | 2M XLR &amp; USB Cable | Streaming, Gaming, Podcasting, Singing</t>
+          <t>TONOR TC310+ RGB Condenser Mic with Boom Arm Quick Mute, RGB Lighting, Pop Filter, Shock Mount,Gaming USB Microphone Set for PC Gain Control for Streaming Podcasting Recording Discord Twitch YouTube</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>106987.24</v>
+        <v>117332.21</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>27.0</v>
+        <v>48.0</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>0.0</v>
@@ -2259,10 +2259,10 @@
         <v>0.0</v>
       </c>
       <c r="I54" s="1" t="n">
-        <v>27.0</v>
+        <v>47.0</v>
       </c>
       <c r="J54" s="1" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="55">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106676.18</v>
+        <v>112017.69</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>0.0</v>
@@ -2299,21 +2299,21 @@
         <v>0.0</v>
       </c>
       <c r="I55" s="1" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="J55" s="1" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Audio Array AM-W14 UHF Dual Wireless Premium Metal Microphone | 2X XLR Outs &amp; 1/4" Mix Out | Range up to 200ft/60m | Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box</t>
+          <t>Audio Array MT-12 12 Analog+2 Digital Channel Hybrid Analog+USB Mixer, 48kHz DSP, 4 XLR &amp; 8 TRS Inputs, 3-Band EQ, +48V Phantom, 24dBu Balanced XLR Out, Graphical EQ, Type-C Power, Studio &amp; Streaming</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>105661.03</v>
+        <v>111428.82</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>0.0</v>
@@ -2339,21 +2339,21 @@
         <v>0.0</v>
       </c>
       <c r="I56" s="1" t="n">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="J56" s="1" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Audio Array MT-12 12 Analog+2 Digital Channel Hybrid Analog+USB Mixer, 48kHz DSP, 4 XLR &amp; 8 TRS Inputs, 3-Band EQ, +48V Phantom, 24dBu Balanced XLR Out, Graphical EQ, Type-C Power, Studio &amp; Streaming</t>
+          <t>Audio Array AK-61 Neo 61 Key Electronic Keyboard with LED Display, 200 Presets &amp; 512 Timbres, Built-in 2.0 Speakers, with Mic, Vibrato, Sustain, Transpose, Battery &amp; Adapter Powered, Headphone Out</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>103378.82</v>
+        <v>109977.95</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>13.0</v>
+        <v>26.0</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>0.0</v>
@@ -2379,7 +2379,7 @@
         <v>0.0</v>
       </c>
       <c r="I57" s="1" t="n">
-        <v>13.0</v>
+        <v>26.0</v>
       </c>
       <c r="J57" s="1" t="n">
         <v>6.0</v>
@@ -2388,17 +2388,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TONOR TC310+ RGB Condenser Mic with Boom Arm Quick Mute, RGB Lighting, Pop Filter, Shock Mount,Gaming USB Microphone Set for PC Gain Control for Streaming Podcasting Recording Discord Twitch YouTube</t>
+          <t>Audio Array AM-C3 XLR to TRS Dynamic Handheld Karaoke Microphone | Premium Metal Built with 3M Cable | Singing, Public Meetings, Studio Recording, Live Show, Party, Church, Wedding</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>101128.83</v>
+        <v>108686.32</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>41.0</v>
+        <v>140.0</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>0.0</v>
@@ -2419,21 +2419,21 @@
         <v>0.0</v>
       </c>
       <c r="I58" s="1" t="n">
-        <v>40.0</v>
+        <v>142.0</v>
       </c>
       <c r="J58" s="1" t="n">
-        <v>6.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Audio Array AM-C47 RGB USB Condenser Mic Kit | AI Noise Cancellation, 192kHz/24Bit Studio Quality, Touch Control, Headphone Monitoring | Podcasting, YouTube, Gaming &amp; Streaming | Mac/PC &amp; Mobile</t>
+          <t>Audio Array AM-C11 XLR/USB Dynamic Podcast Microphone | Built-in Monitoring | One Touch Mute and Volume Control | Premium Metal Build | 2M XLR &amp; USB Cable | Streaming, Gaming, Podcasting, Singing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>100646.59</v>
+        <v>107241.46</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>42.0</v>
+        <v>27.0</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>0.0</v>
@@ -2459,21 +2459,21 @@
         <v>0.0</v>
       </c>
       <c r="I59" s="1" t="n">
-        <v>42.0</v>
+        <v>28.0</v>
       </c>
       <c r="J59" s="1" t="n">
-        <v>11.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Audio Array Professional Studio Bundle with 24-Bit/192kHz Audio Interface, 4" Studio Monitors, Condenser Mic &amp; Stands | for Music Production, Podcasting, Dubbing, Recording &amp; Audio Mixing - UB-01</t>
+          <t>Audio Array AM-C47 RGB USB Condenser Mic Kit | AI Noise Cancellation, 192kHz/24Bit Studio Quality, Touch Control, Headphone Monitoring | Podcasting, YouTube, Gaming &amp; Streaming | Mac/PC &amp; Mobile</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>98807.63</v>
+        <v>100392.35</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>6.0</v>
+        <v>42.0</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>0.0</v>
@@ -2499,21 +2499,21 @@
         <v>0.0</v>
       </c>
       <c r="I60" s="1" t="n">
-        <v>6.0</v>
+        <v>42.0</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Audio Array Studio Monitor Bundle with 60W Powered Speakers &amp; Adjustable Metal Stands | Bluetooth, HDMI ARC, USB-C, RCA Inputs | Professional Studio Monitors for Home Studio, Streaming &amp; Gaming-UB-03</t>
+          <t>Audio Array Professional Studio Bundle with 24-Bit/192kHz Audio Interface, 4" Studio Monitors, Condenser Mic &amp; Stands | for Music Production, Podcasting, Dubbing, Recording &amp; Audio Mixing - UB-01</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>96645.79</v>
+        <v>98638.98</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>0.0</v>
@@ -2539,7 +2539,7 @@
         <v>0.0</v>
       </c>
       <c r="I61" s="1" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="J61" s="1" t="n">
         <v>2.0</v>
@@ -2548,12 +2548,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Audio Array AM-C44 Pro XLR/USB Professional Dynamic Microphone Kit | Built-in Monitoring | One Touch Mute &amp; Volume Control | 192kHz/24bit Full Metal Build | 2M XLR &amp; USB Cable | Streaming &amp; Podcasting</t>
+          <t>Audio Array Studio Monitor Bundle with 60W Powered Speakers &amp; Adjustable Metal Stands | Bluetooth, HDMI ARC, USB-C, RCA Inputs | Professional Studio Monitors for Home Studio, Streaming &amp; Gaming-UB-03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>95913.57</v>
+        <v>96647.47</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>0.0</v>
@@ -2579,21 +2579,21 @@
         <v>0.0</v>
       </c>
       <c r="I62" s="1" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="J62" s="1" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Audio Array AM-W32 UHF Dual Wireless Metal Microphones | Built-in Rechargeable Battery | 6–8 Hours Backup | 60M Range | Karaoke, DJ, Events, PA System | Echo &amp; Volume Controls</t>
+          <t>Audio Array AM-C44 Pro XLR/USB Professional Dynamic Microphone Kit | Built-in Monitoring | One Touch Mute &amp; Volume Control | 192kHz/24bit Full Metal Build | 2M XLR &amp; USB Cable | Streaming &amp; Podcasting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>92092.37</v>
+        <v>91507.65</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>0.0</v>
@@ -2619,7 +2619,7 @@
         <v>0.0</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>30.0</v>
+        <v>23.0</v>
       </c>
       <c r="J63" s="1" t="n">
         <v>5.0</v>
@@ -2628,17 +2628,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TONOR TD510 Dynamic Microphone, USB/XLR PC Microphone for Podcast, Recording, Live Streaming &amp; Gaming, XLR Cardioid Studio Mic Music Voice-Over with Quick Mute, Headphone Output, Volume Control</t>
+          <t>Audio Array Studio Monitor Bundle with 60W Powered Speakers &amp; Adjustable Metal Stands | Bluetooth, HDMI ARC, USB-C, RCA Inputs | Professional Studio Monitors for Home Studio, Streaming &amp; Gaming-UB-02</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>84154.16</v>
+        <v>88466.94</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>25.0</v>
+        <v>9.0</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>0.0</v>
@@ -2659,21 +2659,21 @@
         <v>0.0</v>
       </c>
       <c r="I64" s="1" t="n">
-        <v>25.0</v>
+        <v>8.0</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Audio Array AM-W22 | Latest 2026 Edition Wireless Microphone for Camera/iPhone/Android/iPad/Laptop, Lav Mic with Charging Case, AI Noise Reduction, 50H Battery, 230ft Range, for Recording, YouTube</t>
+          <t>Audio Array AM-W34 UHF Dual Wireless Premium Metal Microphones | 800mAh 6-8 Hours Receiver Battery Backup | Range up to 50M | Karaoke Singing, Wedding, Church | PA System, Amplifier, Mixer, Party Box</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>82956.04</v>
+        <v>85409.5</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>0.0</v>
@@ -2699,21 +2699,21 @@
         <v>0.0</v>
       </c>
       <c r="I65" s="1" t="n">
-        <v>28.0</v>
+        <v>27.0</v>
       </c>
       <c r="J65" s="1" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Audio Array Studio Monitor Bundle with 60W Powered Speakers &amp; Adjustable Metal Stands | Bluetooth, HDMI ARC, USB-C, RCA Inputs | Professional Studio Monitors for Home Studio, Streaming &amp; Gaming-UB-02</t>
+          <t>Audio Array Microphone Boom Arm with 35cm+35cm=70cm Adjustable Suspension Scissor Arm Stand, Shock Mount, Base Clamp, Pop-Filter, 3/8" to 5/8" Universal Screw Adapter, 4x Cable Ties | AA-06</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>78637.28</v>
+        <v>82986.43</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>8.0</v>
+        <v>76.0</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>0.0</v>
@@ -2739,21 +2739,21 @@
         <v>0.0</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>7.0</v>
+        <v>77.0</v>
       </c>
       <c r="J66" s="1" t="n">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Audio Array AM-W34 UHF Dual Wireless Premium Metal Microphones | 800mAh 6-8 Hours Receiver Battery Backup | Range up to 50M | Karaoke Singing, Wedding, Church | PA System, Amplifier, Mixer, Party Box</t>
+          <t>Audio Array Suspension Boom Scissor Microphone Stand | Double Layer Mesh Pop Filter | 70cm Sturdy Boom Arm with 1.8kg Capacity | 5/8" to 3/8" Screw Adapter | Mic Holder, Foam Cover, Cable Ties | AA-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>78631.54</v>
+        <v>81614.38</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>25.0</v>
+        <v>45.0</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>0.0</v>
@@ -2779,7 +2779,7 @@
         <v>0.0</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>26.0</v>
+        <v>45.0</v>
       </c>
       <c r="J67" s="1" t="n">
         <v>4.0</v>
@@ -2788,12 +2788,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Audio Array AA-01 Suspension Boom Scissor Microphone Stand | Double Layer Mesh Pop Filter | 70cm Sturdy Boom Arm with 1.8kg Capacity | 5/8" to 3/8" Screw Adapter | Mic Holder, Foam Cover, Cable Ties</t>
+          <t>Audio Array AM-W22 | Latest 2026 Edition Wireless Microphone for Camera/iPhone/Android/iPad/Laptop, Lav Mic with Charging Case, AI Noise Reduction, 50H Battery, 230ft Range, for Recording, YouTube</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>76150.83</v>
+        <v>80129.58</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>42.0</v>
+        <v>27.0</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>0.0</v>
@@ -2819,26 +2819,26 @@
         <v>0.0</v>
       </c>
       <c r="I68" s="1" t="n">
-        <v>42.0</v>
+        <v>28.0</v>
       </c>
       <c r="J68" s="1" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Audio Array AK-61 Neo 61 Key Electronic Keyboard with LED Display, 200 Presets &amp; 512 Timbres, Built-in 2.0 Speakers, with Mic, Vibrato, Sustain, Transpose, Battery &amp; Adapter Powered, Headphone Out</t>
+          <t>TONOR G11 Conference USB Microphone, Omnidirectional Condenser PC Mic for Video Conference, Recording, Skype, Online Class, Court Reporter, Plug &amp; Play Compatible with Mac OS X Windows PC Computer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>76086.43</v>
+        <v>78360.19</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>18.0</v>
+        <v>35.0</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>0.0</v>
@@ -2859,21 +2859,21 @@
         <v>0.0</v>
       </c>
       <c r="I69" s="1" t="n">
-        <v>16.0</v>
+        <v>34.0</v>
       </c>
       <c r="J69" s="1" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Audio Array AM-W35 UHF Dual Wireless Premium Karaoke Microphones | 800mah 5-6 Hours Battery Backup | Range up to 50M | Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box</t>
+          <t>Audio Array AM-W32 UHF Dual Wireless Metal Microphones | Built-in Rechargeable Battery | 6–8 Hours Backup | 60M Range | Karaoke, DJ, Events, PA System | Echo &amp; Volume Controls</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>72227.91</v>
+        <v>77485.53</v>
       </c>
       <c r="F70" s="1" t="n">
         <v>24.0</v>
@@ -2899,21 +2899,21 @@
         <v>0.0</v>
       </c>
       <c r="I70" s="1" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="J70" s="1" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Audio Array AA-06 Microphone Boom Arm with 35cm+35cm=70cm Adjustable Suspension Scissor Arm Stand, Shock Mount, Base Clamp, Pop-Filter, 3/8" to 5/8" Universal Screw Adapter, 4x Cable Ties</t>
+          <t>Audio Array AM-W35 UHF Dual Wireless Premium Karaoke Microphones | 800mah 5-6 Hours Battery Backup | Range up to 50M | Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>69776.25</v>
+        <v>75277.91</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>64.0</v>
+        <v>25.0</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>0.0</v>
@@ -2939,21 +2939,21 @@
         <v>0.0</v>
       </c>
       <c r="I71" s="1" t="n">
-        <v>63.0</v>
+        <v>25.0</v>
       </c>
       <c r="J71" s="1" t="n">
-        <v>17.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Audio Array AM-W23 Magnetic Wieless Mic with Charging Pouch 2026 Edition 24Bit/ 48Khz, iPhone/Android/iPad/Laptop, AI Noise Reduction, 50H Battery, 230ft Range for Recording, Vlogging</t>
+          <t>Audio Array Singing Bundle | Condenser Mic with Boom Arm &amp; Sound Card V8 | Voice Effects, Reverb, Bluetooth | Ideal for Podcasting, Karaoke, Live Streaming, YouTube &amp; Singing - GB-03</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>68366.99</v>
+        <v>74764.33</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>0.0</v>
@@ -2982,18 +2982,18 @@
         <v>27.0</v>
       </c>
       <c r="J72" s="1" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TONOR Wireless Microphone Isolation Shield, Mic Sound Absorbing Foam Reflector for Any Condenser Recording Equipment Studio (Black)</t>
+          <t>TONOR USB Conference Microphone, 360 Omnidirectional PC Computer Condenser Mic with Mute Button for Online Meeting/Class, Zoom Call, Skype Chatting, Plug &amp; Play (TM20,Red)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>67777.9</v>
+        <v>73450.05</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>0.0</v>
@@ -3019,26 +3019,28 @@
         <v>0.0</v>
       </c>
       <c r="I73" s="1" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="J73" s="1" t="n">
-        <v>7.0</v>
+        <v>17.0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Audio Array AM-W33 UHF Metal Solo Wireless Microphone Set | Built-in Rechargeable Battery | 6–8 Hours Backup | 50M Range | Karaoke, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box</t>
+          <t>TONOR Dynamic Karaoke Microphone for Singing with 4.5m XLR Cable, Metal Handheld Mic Compatible with Karaoke Machine/Speaker/Amp/Mixer for Karaoke Singing, Speech, Wedding, Stage and Outdoor Activity</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3047,10 +3049,10 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>67466.41</v>
+        <v>71919.81</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>41.0</v>
+        <v>47.0</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>0.0</v>
@@ -3059,21 +3061,21 @@
         <v>0.0</v>
       </c>
       <c r="I74" s="1" t="n">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
       <c r="J74" s="1" t="n">
-        <v>29.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Audio Array AM-W22_V2 | Latest 2026 Edition Wireless Microphone for Camera/iPhone/Android/iPad/Laptop, Lav Mic with Charging Case, AI Noise Reduction, 50H Battery, 230ft Range, for Recording, YouTube</t>
+          <t>Audio Array AM-W23 Magnetic Wieless Mic with Charging Pouch 2026 Edition 24Bit/ 48Khz, iPhone/Android/iPad/Laptop, AI Noise Reduction, 50H Battery, 230ft Range for Recording, Vlogging</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3087,10 +3089,10 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>67423.99</v>
+        <v>71747.25</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>23.0</v>
+        <v>29.0</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>0.0</v>
@@ -3099,26 +3101,26 @@
         <v>0.0</v>
       </c>
       <c r="I75" s="1" t="n">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
       <c r="J75" s="1" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Audio Array AM-C11X XLR Dynamic Microphone | Studio-quality Audio Output | Cardioid Polar Pattern | Premium Metal Build | 2 Meter XLR cable | for Streaming, Gaming, Podcasting, Singing | 2 Yr Warranty</t>
+          <t>TONOR Wireless Microphone Isolation Shield, Mic Sound Absorbing Foam Reflector for Any Condenser Recording Equipment Studio (Black)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3127,10 +3129,10 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>67388.12</v>
+        <v>69980.44</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>22.0</v>
+        <v>32.0</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>0.0</v>
@@ -3139,21 +3141,21 @@
         <v>0.0</v>
       </c>
       <c r="I76" s="1" t="n">
-        <v>23.0</v>
+        <v>32.0</v>
       </c>
       <c r="J76" s="1" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Audio Array AA-19WL RGB Low Profile Boomarm Stand with Riser | 71cm reach &amp; 20 RGB lighting effects &amp; Built-In Cable Management | Matte finish with Flexible adjustments | 2Kg Weight Capacity | White</t>
+          <t>Audio Array Wired Voice Amplifier for Teachers 2026 Edition | Bluetooth 5.3 | Mic for Teaching with 10W Speaker, Tour Guides | 10Hrs Battery Life |1 Click Monitoring | TWS Connectivity AM-W47 Wired</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3167,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>63292.37</v>
+        <v>69852.42</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>15.0</v>
+        <v>69.0</v>
       </c>
       <c r="G77" s="2" t="n">
         <v>0.0</v>
@@ -3179,21 +3181,21 @@
         <v>0.0</v>
       </c>
       <c r="I77" s="1" t="n">
-        <v>16.0</v>
+        <v>68.0</v>
       </c>
       <c r="J77" s="1" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Audio Array AM-C6 USB Plug &amp; Play Condenser Microphone Kit | with pop-Filter &amp; Shock Mount | 3.5 mm No Latency Monitoring, Volume Control &amp; Mute Button | Gaming, Podcasting &amp; Streaming</t>
+          <t>Audio Array AM-W22_v2 Latest 2026 Edition Wireless Microphone for Camera/iPhone/Android/iPad/Laptop, Lav Mic with Charging Case, AI Noise Reduction, 50H Battery, 230ft Range, for Recording, YouTube</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3207,10 +3209,10 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>62677.06</v>
+        <v>67423.99</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>39.0</v>
+        <v>23.0</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>0.0</v>
@@ -3219,26 +3221,26 @@
         <v>0.0</v>
       </c>
       <c r="I78" s="1" t="n">
-        <v>39.0</v>
+        <v>23.0</v>
       </c>
       <c r="J78" s="1" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Audio Array AA-03 Double Layer Professional Pop Filter | Flexible 360° Free Angle Adjustable, Durable Windshield | Metal Gooseneck Stabilizing Arm Holder with 32cm Arm Length | Suitable for Recording.</t>
+          <t>TONOR TD510 Dynamic Microphone, USB/XLR PC Microphone for Podcast, Recording, Live Streaming &amp; Gaming, XLR Cardioid Studio Mic Music Voice-Over with Quick Mute, Headphone Output, Volume Control</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3247,10 +3249,10 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>60284.54</v>
+        <v>67209.26</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>144.0</v>
+        <v>20.0</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>0.0</v>
@@ -3259,21 +3261,21 @@
         <v>0.0</v>
       </c>
       <c r="I79" s="1" t="n">
-        <v>145.0</v>
+        <v>22.0</v>
       </c>
       <c r="J79" s="1" t="n">
-        <v>12.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Audio Array Podcast Bundle with USB Condenser Mic Kit, Audio Interface |192kHz/24bit Studio Quality, Plug &amp; Play, Phantom Power, Real-Time Monitoring for Recording, Streaming &amp; Podcasting - PB-08</t>
+          <t>Audio Array AM-W33 UHF Metal Solo Wireless Microphone Set | 2000mAh 6-8 Hours Battery Backup | Range up to 50M | Karaoke Singing, Wedding, DJ, Church | PA System, Amplifier, Mixer, Party Box</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3287,10 +3289,10 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>59312.75</v>
+        <v>65805.39</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>0.0</v>
@@ -3299,21 +3301,21 @@
         <v>0.0</v>
       </c>
       <c r="I80" s="1" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="J80" s="1" t="n">
-        <v>4.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Audio Array AM-Pro12 12-Channel HYBRID USB Mixer 12 channel analog+2 digital 48kHz/16bit,128DSP Fx, Built-In Compressor, 4Group Buses, Inserts,+24dBu Balanced XLR Outs For Live, Studio &amp; Broadcast</t>
+          <t>Audio Array Pro Podcasting Bundle | Audio Interface with 48V Phantom Power &amp; Dual USB/XLR Touch-Control Mics | 192kHz/24bit, Mute, Monitor, Volume Control | Recording, Streaming &amp; Podcasting - PB-04</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3327,10 +3329,10 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>58472.04</v>
+        <v>65682.72</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>0.0</v>
@@ -3339,26 +3341,26 @@
         <v>0.0</v>
       </c>
       <c r="I81" s="1" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="J81" s="1" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TONOR Dynamic Karaoke Microphone for Singing with 4.5m XLR Cable, Metal Handheld Mic Compatible with Karaoke Machine/Speaker/Amp/Mixer for Karaoke Singing, Speech, Wedding, Stage and Outdoor Activity</t>
+          <t>Audio Array AA-03 Double Layer Professional Pop Filter | Flexible 360° Free Angle Adjustable, Durable Windshield | Metal Gooseneck Stabilizing Arm Holder with 32cm Arm Length | Suitable for Recording.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3367,10 +3369,10 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>57400.89</v>
+        <v>62410.8</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>37.0</v>
+        <v>149.0</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>0.0</v>
@@ -3379,21 +3381,21 @@
         <v>0.0</v>
       </c>
       <c r="I82" s="1" t="n">
-        <v>37.0</v>
+        <v>151.0</v>
       </c>
       <c r="J82" s="1" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Audio Array AM-W24 2026 Edition Magnetic Wireless 5gm Mic with Slide Charging Case for iPhone/Android/iPad, AI Noise Reduction, 30H Battery, 200ft Range, Plug &amp; Play for Recording, Vlogging, Streaming</t>
+          <t>Audio Array AM-C11X XLR Dynamic Microphone | Studio-quality Audio Output | Cardioid Polar Pattern | Premium Metal Build | 2 Meter XLR cable | for Streaming, Gaming, Podcasting, Singing | 2 Yr Warranty</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3407,10 +3409,10 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>56326.2</v>
+        <v>61593.2</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>0.0</v>
@@ -3419,21 +3421,21 @@
         <v>0.0</v>
       </c>
       <c r="I83" s="1" t="n">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="J83" s="1" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Audio Array Pro Podcasting Bundle | Audio Interface with 48V Phantom Power &amp; Dual USB/XLR Touch-Control Mics | 192kHz/24bit, Mute, Monitor, Volume Control | Recording, Streaming &amp; Podcasting - PB-04</t>
+          <t>Audio Array AM-C6 USB Plug &amp; Play Condenser Microphone Kit | with pop-Filter &amp; Shock Mount | 3.5 mm No Latency Monitoring, Volume Control &amp; Mute Button | Gaming, Podcasting &amp; Streaming</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3447,10 +3449,10 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>54327.64</v>
+        <v>61247.4</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>5.0</v>
+        <v>38.0</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>0.0</v>
@@ -3459,21 +3461,21 @@
         <v>0.0</v>
       </c>
       <c r="I84" s="1" t="n">
-        <v>5.0</v>
+        <v>39.0</v>
       </c>
       <c r="J84" s="1" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Audio Array Singing Bundle | Condenser Mic with Boom Arm &amp; Sound Card V8 | Voice Effects, Reverb, Bluetooth | Ideal for Podcasting, Karaoke, Live Streaming, YouTube &amp; Singing - GB-03</t>
+          <t>Audio Array AA-19WL RGB Low Profile Boomarm Stand with Riser | 71cm reach &amp; 20 RGB lighting effects &amp; Built-In Cable Management | Matte finish with Flexible adjustments | 2Kg Weight Capacity | White</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3487,10 +3489,10 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>53966.06</v>
+        <v>59140.67</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>0.0</v>
@@ -3499,21 +3501,21 @@
         <v>0.0</v>
       </c>
       <c r="I85" s="1" t="n">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="J85" s="1" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Audio Array Wired Voice Amplifier 2026 Edition | Bluetooth 5.3 | Wired Headset Mic with 10W Speaker for Teachers, Tour Guides | 10Hrs Battery Life |1 Click Monitoring | TWS Connectivity AM-W47 Wired</t>
+          <t>Audio Array Professional Dynamic Bundle with Headphones &amp; Audio Interface - USB/XLR Dynamic Microphone, 24-bit/192kHz Interface, Boom Arm &amp; Semi-Open Headphones | Plug &amp; Play Podcast Kit - PB-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3527,10 +3529,10 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>50546.52</v>
+        <v>59099.15</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>50.0</v>
+        <v>6.0</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>0.0</v>
@@ -3539,21 +3541,23 @@
         <v>0.0</v>
       </c>
       <c r="I86" s="1" t="n">
-        <v>49.0</v>
-      </c>
-      <c r="J86" s="1" t="n">
-        <v>15.0</v>
+        <v>6.0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Audio Array Professional Dynamic Bundle with Headphones &amp; Audio Interface - USB/XLR Dynamic Microphone, 24-bit/192kHz Interface, Boom Arm &amp; Semi-Open Headphones | Plug &amp; Play Podcast Kit - PB-12</t>
+          <t>Audio Array Podcast Bundle with USB Condenser Mic Kit, Audio Interface |192kHz/24bit Studio Quality, Plug &amp; Play, Phantom Power, Real-Time Monitoring for Recording, Streaming &amp; Podcasting - PB-08</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3567,10 +3571,10 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>49269.49</v>
+        <v>58889.87</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>0.0</v>
@@ -3579,23 +3583,21 @@
         <v>0.0</v>
       </c>
       <c r="I87" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>10.0</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Audio Array AM-C42 Plug &amp; Play AI Noise Cancelling USB Condenser Microphone | Mute Button/Echo/Volume Knob | Kit with Boom Arm &amp; Pop Filter | Karaoke, Gaming, Streaming, Podcast | Mac/PC/Mobile</t>
+          <t>Audio Array AM-W24 2026 Edition Magnetic Wireless 5gm Mic with Slide Charging Case for iPhone/Android/iPad, AI Noise Reduction, 30H Battery, 200ft Range, Plug &amp; Play for Recording, Vlogging, Streaming</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3609,10 +3611,10 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>49170.49</v>
+        <v>56326.2</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="G88" s="2" t="n">
         <v>0.0</v>
@@ -3621,21 +3623,21 @@
         <v>0.0</v>
       </c>
       <c r="I88" s="1" t="n">
-        <v>24.0</v>
+        <v>35.0</v>
       </c>
       <c r="J88" s="1" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Audio Array AM-W13 UHF Wireless Premium Metal Microphone | 4+ Hours Receiver Battery Backup | Range up to 60m | Karaoke Singing, Wedding, DJ | Compatible with PA System, Amplifier, Mixer, Party Box</t>
+          <t>Audio Array Sound bar | Bluetooth Speaker Wireless 25W, Gaming RGB Lights, AUX, USB, FM &amp; TWS I Fast Charge Battery, Multiport Connectivity, for TV, Mobile, PC, Laptops, Tablets | Blue | SB-01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3649,10 +3651,10 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>47338.98</v>
+        <v>55834.23</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>26.0</v>
+        <v>54.0</v>
       </c>
       <c r="G89" s="2" t="n">
         <v>0.0</v>
@@ -3661,26 +3663,26 @@
         <v>0.0</v>
       </c>
       <c r="I89" s="1" t="n">
-        <v>26.0</v>
+        <v>52.0</v>
       </c>
       <c r="J89" s="1" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Audio Array AM-Mix10 10-Channel Hybrid USB Mixer with10 Analog+2 Digital Inputs, 48kHz/16-Bit DSP, Phantom Power, USB-C Powered, AUX Sends, Built-In FX, Balanced XLR Outputs for Live, Studio &amp; Podcast</t>
+          <t>White Mulberry Monitor Arm | Height Adjustable Monitor Arm Desk Mount for 15–32 Inch Screen | 10kg Load Capacity | VESA 75x75 &amp; 100x100 | Single Monitor Stand</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3689,10 +3691,10 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>46182.21</v>
+        <v>55795.51</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>5.0</v>
+        <v>41.0</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>0.0</v>
@@ -3701,26 +3703,26 @@
         <v>0.0</v>
       </c>
       <c r="I90" s="1" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="J90" s="1" t="n">
         <v>6.0</v>
-      </c>
-      <c r="J90" s="1" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DP2VVRND</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Stand for Table | Freestanding Height Adjustable Moniter Stand Black Monitor Mount for 17-32 Inch Screens |10kg Load | VESA 75x75/100x100 |</t>
+          <t>Audio Array AM-Mix10 10-Channel Hybrid USB Mixer with10 Analog+2 Digital Inputs, 48kHz/16-Bit DSP, Phantom Power, USB-C Powered, AUX Sends, Built-In FX, Balanced XLR Outputs for Live, Studio &amp; Podcast</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3729,10 +3731,10 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>45731.38</v>
+        <v>54655.94</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>27.0</v>
+        <v>6.0</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>0.0</v>
@@ -3741,21 +3743,21 @@
         <v>0.0</v>
       </c>
       <c r="I91" s="1" t="n">
-        <v>29.0</v>
+        <v>6.0</v>
       </c>
       <c r="J91" s="1" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Audio Array Complete Podcast Bundle | Dual USB/XLR Dynamic Microphones with Audio Interface 24bit / 192kHz|Metal Body|Pro Streaming &amp; Recording Kit for PC, Mac &amp; Mobile - PB-03</t>
+          <t>Audio Array AK-37 Black MIDI Keyboard 37 Velocity Sensitive Keys, Built-in Speakers, 200 Presets, Sustain &amp; Touch, Tempo, Octave/Transpose/Tune, Master Volume Knob, LED Display BT AA &amp; Type-C Power</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3769,10 +3771,10 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>45081.36</v>
+        <v>54036.24</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>0.0</v>
@@ -3781,26 +3783,26 @@
         <v>0.0</v>
       </c>
       <c r="I92" s="1" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="J92" s="1" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm | Height Adjustable Monitor Arm Desk Mount for 15–32 Inch Screen | 10kg Load Capacity | VESA 75x75 &amp; 100x100 | Single Monitor Stand</t>
+          <t>Audio Array AM-C42 Plug &amp; Play AI Noise Cancelling USB Condenser Microphone | Mute Button/Echo/Volume Knob | Kit with Boom Arm &amp; Pop Filter | Karaoke, Gaming, Streaming, Podcast | Mac/PC/Mobile</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3809,10 +3811,10 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>44954.87</v>
+        <v>47391.67</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>33.0</v>
+        <v>24.0</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>0.0</v>
@@ -3821,26 +3823,26 @@
         <v>0.0</v>
       </c>
       <c r="I93" s="1" t="n">
-        <v>28.0</v>
+        <v>24.0</v>
       </c>
       <c r="J93" s="1" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Audio Array SB-01 | Bluetooth Soundbar 25W, Gaming RGB Lights, AUX, Bluetooth, USB, FM &amp; TWS I Fast Charge Battery, Multiport Connectivity, BT Speaker for TV, Mobile, PC, Laptops, Tablets Black</t>
+          <t>TONOR Gaming Mic, USB Microphone for PC Computer, Cardioid Condenser Mic with Adjustable RGB Modes &amp; Brightness, Quick Mute, Gain Control, for Streaming, Podcasting, Recording, PS4/5 Desktop TC310</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3849,10 +3851,10 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>42028.33</v>
+        <v>46299.21</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>40.0</v>
+        <v>22.0</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>0.0</v>
@@ -3861,21 +3863,21 @@
         <v>0.0</v>
       </c>
       <c r="I94" s="1" t="n">
-        <v>36.0</v>
+        <v>21.0</v>
       </c>
       <c r="J94" s="1" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Audio Array AK-37 Black MIDI Keyboard 37 Velocity Sensitive Keys, Built-in Speakers, 200 Presets, Sustain &amp; Touch, Tempo, Octave/Transpose/Tune, Master Volume Knob, LED Display BT AA &amp; Type-C Power</t>
+          <t>Audio Array Complete Podcast Bundle | Dual USB/XLR Dynamic Microphones with Audio Interface 24bit / 192kHz|Metal Body|Pro Streaming &amp; Recording Kit for PC, Mac &amp; Mobile - PB-03</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3889,10 +3891,10 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>40480.32</v>
+        <v>45081.36</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
       <c r="G95" s="2" t="n">
         <v>0.0</v>
@@ -3901,26 +3903,26 @@
         <v>0.0</v>
       </c>
       <c r="I95" s="1" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="J95" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0DP2VVRND</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TONOR Gaming Mic, USB Microphone for PC Computer, Cardioid Condenser Mic with Adjustable RGB Modes &amp; Brightness, Quick Mute, Gain Control, for Streaming, Podcasting, Recording, PS4/5 Desktop TC310</t>
+          <t>White Mulberry Monitor Stand for Table | Freestanding Height Adjustable Moniter Stand Black Monitor Mount for 17-32 Inch Screens |10kg Load | VESA 75x75/100x100 |</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3929,10 +3931,10 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>37828.01</v>
+        <v>44045.79</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>0.0</v>
@@ -3941,21 +3943,21 @@
         <v>0.0</v>
       </c>
       <c r="I96" s="1" t="n">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="J96" s="1" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Audio Array AM-C41 Plug &amp; Play AI Noise Cancellation USB Condenser Microphone | Mute Button/Echo/Volume Knob | Kit with Tripod, Mic Cover | Gaming, Streaming, Podcast | Mac/PC/Laptop/Mobile</t>
+          <t>Audio Array AM-W13 UHF Wireless Premium Metal Microphone | 4+ Hours Receiver Battery Backup | Range up to 60m | Karaoke Singing, Wedding, DJ | Compatible with PA System, Amplifier, Mixer, Party Box</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3969,10 +3971,10 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>37704.13</v>
+        <v>42259.32</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>28.0</v>
+        <v>23.0</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>0.0</v>
@@ -3981,26 +3983,26 @@
         <v>0.0</v>
       </c>
       <c r="I97" s="1" t="n">
-        <v>27.0</v>
+        <v>23.0</v>
       </c>
       <c r="J97" s="1" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TONOR Microphone Arm Stand, TONOR Adjustable Suspension Boom Scissor Mic Stand with Pop , 3/8" to 5/8" Adapter, Mic Clip, Upgraded Heavy Duty Clamp for Blue Yeti Nano Snowball Ice and Other Mics(T20)</t>
+          <t>Audio Array AM-C41 Plug &amp; Play AI Noise Cancellation USB Condenser Microphone | Mute Button/Echo/Volume Knob | Kit with Tripod, Mic Cover | Gaming, Streaming, Podcast | Mac/PC/Laptop/Mobile</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4009,10 +4011,10 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>32910.14</v>
+        <v>40414.29</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>16.0</v>
+        <v>30.0</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>0.0</v>
@@ -4021,21 +4023,21 @@
         <v>0.0</v>
       </c>
       <c r="I98" s="1" t="n">
-        <v>17.0</v>
+        <v>29.0</v>
       </c>
       <c r="J98" s="1" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Audio Array Streaming Bundle Kit | USB Condenser Mic &amp; RGB Sound Card with Phantom Power, Voice Effects, Real-Time Monitoring | for Podcasting, Gaming, YouTube &amp; Live Streaming - GB-05</t>
+          <t>Audio Array Professional Recording Bundle with BT Soundcard – USB Condenser Microphone, Studio Headphones | Cardioid Mic, Noise Reduction &amp; 6 Sound Modes for Streaming Recording &amp; Podcasting - PB-14</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4049,10 +4051,10 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>32027.1</v>
+        <v>39617.02</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>0.0</v>
@@ -4061,21 +4063,21 @@
         <v>0.0</v>
       </c>
       <c r="I99" s="1" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="J99" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Audio Array AM-C3a Unidirectional Dynamic Handheld Karaoke Microphone | 20Hz - 20kHz Response | Karaoke Singing, Public Meetings, Studio Recording, Live Sound, Party (no Cable Included)</t>
+          <t>Audio Array All in 1 Pro Bundle | Condenser Mic with USB Bluetooth Soundcard Mixer | Complete Setup for Streaming, Podcasting, Gaming, Singing &amp; Home Studio Recording - GB-02</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4089,10 +4091,10 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>31944.98</v>
+        <v>39142.34</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>49.0</v>
+        <v>12.0</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>0.0</v>
@@ -4101,21 +4103,21 @@
         <v>0.0</v>
       </c>
       <c r="I100" s="1" t="n">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="J100" s="1" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Audio Array Wireless Voice Amplifier 2026 Edition | Bluetooth 5.3 |10W Speaker With Wireless Mic | For Teachers, Tour Guides |10 Hrs Battery Life |1 Click Monitoring | TWS Connectivity AM-W47 Wireless</t>
+          <t>Audio Array AM-Pro12 12-Channel HYBRID USB Mixer 12 channel analog+2 digital 48kHz/16bit,128DSP Fx, Built-In Compressor, 4Group Buses, Inserts,+24dBu Balanced XLR Outs For Live, Studio &amp; Broadcast</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4129,10 +4131,10 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>29052.51</v>
+        <v>38981.36</v>
       </c>
       <c r="F101" s="1" t="n">
-        <v>18.0</v>
+        <v>2.0</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>0.0</v>
@@ -4141,26 +4143,26 @@
         <v>0.0</v>
       </c>
       <c r="I101" s="1" t="n">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="J101" s="1" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Audio Array AM-W17 Dual Wireless Lapel Mic|in-Built ANC, Plug N Play,Long Battery Life, Ultra-Low Latency,Upto 30M Range|Compatible with iPhone &amp; Android|Vlogging, Streaming, Teaching,YouTube, Black</t>
+          <t>TONOR Microphone Arm Stand, TONOR Adjustable Suspension Boom Scissor Mic Stand with Pop , 3/8" to 5/8" Adapter, Mic Clip, Upgraded Heavy Duty Clamp for Blue Yeti Nano Snowball Ice and Other Mics(T20)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4169,10 +4171,10 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>28682.23</v>
+        <v>37060.98</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>20.0</v>
+        <v>18.0</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>0.0</v>
@@ -4181,21 +4183,21 @@
         <v>0.0</v>
       </c>
       <c r="I102" s="1" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="J102" s="1" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Audio Array Ultimate Gaming Bundle | Condenser Mic with Boom Arm &amp; Sound Card | Streaming Kit for PC/Mobile with 14 FX, Voice Modes, Loopback, Real Time Monitoring |for YouTube &amp; Live Stream - GB-01</t>
+          <t>Audio Array Streaming Bundle Kit | USB Condenser Mic &amp; RGB Sound Card with Phantom Power, Voice Effects, Real-Time Monitoring | for Podcasting, Gaming, YouTube &amp; Live Streaming - GB-05</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4209,10 +4211,10 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>28021.18</v>
+        <v>36517.78</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G103" s="2" t="n">
         <v>0.0</v>
@@ -4221,7 +4223,7 @@
         <v>0.0</v>
       </c>
       <c r="I103" s="1" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J103" s="1" t="n">
         <v>2.0</v>
@@ -4230,12 +4232,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Audio Array AA-25 Handheld Microphone Interview Adapter for Wireless Lapel Microphones | Supports, Rode Go, DJI, Hollyland mics etc | Foam Cover with Built-in Cold Shoe Mount</t>
+          <t>Audio Array AM-W17 Dual Wireless Lapel Mic|in-Built ANC, Plug N Play,Long Battery Life, Ultra-Low Latency,Upto 30M Range|Compatible with iPhone &amp; Android|Vlogging, Streaming, Teaching,YouTube, Black</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4249,10 +4251,10 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>27667.83</v>
+        <v>35881.39</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>39.0</v>
+        <v>25.0</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>0.0</v>
@@ -4261,21 +4263,21 @@
         <v>0.0</v>
       </c>
       <c r="I104" s="1" t="n">
-        <v>40.0</v>
+        <v>24.0</v>
       </c>
       <c r="J104" s="1" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Audio Array AM-C40 Large Diaphragm USB Condenser Microphone Kit | Boom Arm &amp; Pop-Filter | 96kHz/24bit No Latency Headphone Monitoring with Mute &amp; Volume Control Knob | Singing, Podcasting &amp; Streaming</t>
+          <t>Audio Array Ultimate Gaming Bundle | Condenser Mic with Boom Arm &amp; Sound Card | Streaming Kit for PC/Mobile with 14 FX, Voice Modes, Loopback, Real Time Monitoring |for YouTube &amp; Live Stream - GB-01</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4289,10 +4291,10 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>27363.59</v>
+        <v>32330.49</v>
       </c>
       <c r="F105" s="1" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>0.0</v>
@@ -4301,7 +4303,7 @@
         <v>0.0</v>
       </c>
       <c r="I105" s="1" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="J105" s="1" t="n">
         <v>2.0</v>
@@ -4310,17 +4312,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TONOR G11 Conference USB Microphone, Omnidirectional Condenser PC Mic for Video Conference, Recording, Skype, Online Class, Court Reporter, Plug &amp; Play Compatible with Mac OS X Windows PC Computer</t>
+          <t>Audio Array AM-C3a Unidirectional Dynamic Handheld Karaoke Microphone | 20Hz - 20kHz Response | Karaoke Singing, Public Meetings, Studio Recording, Live Sound, Party (no Cable Included)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4329,10 +4331,10 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>25752.58</v>
+        <v>30744.98</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>12.0</v>
+        <v>47.0</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>0.0</v>
@@ -4341,23 +4343,21 @@
         <v>0.0</v>
       </c>
       <c r="I106" s="1" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>47.0</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <v>20.0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Audio Array AM-C4 USB Plug &amp; Play Condenser Microphone with Tripod, Pop-Filter &amp; Shock Mount | for Conference, Gaming, Podcasting, Voice Over, YouTube, Skype, Zoom &amp; Live Streaming on iOS,Windows</t>
+          <t>Audio Array Wireless Voice Amplifier 2026 Edition | Bluetooth 5.3 |10W Speaker With Wireless Mic | For Teachers, Tour Guides |10 Hrs Battery Life |1 Click Monitoring | TWS Connectivity AM-W47 Wireless</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>25744.03</v>
+        <v>30492.34</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>0.0</v>
@@ -4383,21 +4383,21 @@
         <v>0.0</v>
       </c>
       <c r="I107" s="1" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="J107" s="1" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Audio Array AM-W19 Wireless Lavalier Microphone|192kHz/24bit |AI Noise Cancellation for iPhone/Android, 32h Charging Case, Plug &amp; Play for Vlogging, Streaming, Meetings, Video Recording</t>
+          <t>Audio Array AA-25 Handheld Microphone Interview Adapter for Wireless Lapel Microphones | Supports, Rode Go, DJI, Hollyland mics etc | Foam Cover with Built-in Cold Shoe Mount</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25407.61</v>
+        <v>27043.25</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>15.0</v>
+        <v>38.0</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>0.0</v>
@@ -4423,7 +4423,7 @@
         <v>0.0</v>
       </c>
       <c r="I108" s="1" t="n">
-        <v>15.0</v>
+        <v>37.0</v>
       </c>
       <c r="J108" s="1" t="n">
         <v>6.0</v>
@@ -4432,12 +4432,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Audio Array AC-3XL Mic Cable 6.35mm Jack Male to XLR 3PIN Female Cord Wire | Microphone/Guitar Cable | Black, 1pc Pack (3 Meter/10 Feet)</t>
+          <t>Audio Array AM-W10 Professional Dual Wireless Lapel Mics | Upto 10hr Battery &amp; 100m Range | 2X Lapel mics, Type C Adapter for Easy Plug&amp;Play | Volume &amp; Mute Function | Vlogging, Streaming, YouTube</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4451,10 +4451,10 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>24869.19</v>
+        <v>26263.58</v>
       </c>
       <c r="F109" s="1" t="n">
-        <v>66.0</v>
+        <v>8.0</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>0.0</v>
@@ -4463,21 +4463,21 @@
         <v>0.0</v>
       </c>
       <c r="I109" s="1" t="n">
-        <v>66.0</v>
+        <v>8.0</v>
       </c>
       <c r="J109" s="1" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Audio Array AM-W16 Solo Wireless Lapel Over Ear Mic|in-Built ANC,Plug N Play,LongBattery Life,Ultra-Low Latency,Upto 30M Range|Compatible with iPhone&amp;Android|Vlogging,Streaming,Teaching,YouTube,Black</t>
+          <t>Audio Array AM-C4 USB Plug &amp; Play Condenser Microphone with Tripod, Pop-Filter &amp; Shock Mount | for Conference, Gaming, Podcasting, Voice Over, YouTube, Skype, Zoom &amp; Live Streaming on iOS,Windows</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>24858.66</v>
+        <v>25706.75</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="G110" s="2" t="n">
         <v>0.0</v>
@@ -4503,21 +4503,21 @@
         <v>0.0</v>
       </c>
       <c r="I110" s="1" t="n">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="J110" s="1" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Audio Array AM-C45 XLR/USB Pro RGB Dynamic Microphone Kit | 192kHz/24bit Studio Quality Output | Volume Control, Mute and Noise Cancellation | Realtime Monitoring for Streaming, Gaming &amp; podcasting</t>
+          <t>Audio Array AM-C40 Large Diaphragm USB Condenser Microphone Kit | Boom Arm &amp; Pop-Filter | 96kHz/24bit No Latency Headphone Monitoring with Mute &amp; Volume Control Knob | Singing, Podcasting &amp; Streaming</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>24061.87</v>
+        <v>25307.66</v>
       </c>
       <c r="F111" s="1" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>0.0</v>
@@ -4543,23 +4543,21 @@
         <v>0.0</v>
       </c>
       <c r="I111" s="1" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>13.0</v>
+      </c>
+      <c r="J111" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Audio Array Ultimate Podcast Bundle | Dynamic Microphone with USB/XLR Connectivity &amp; 24-Bit/192kHz Audio Interface | Ideal for Podcasting, Streaming, Voice Recording &amp; Content Creation - PB-01</t>
+          <t>Audio Array AM-W16 Solo Wireless Lapel Over Ear Mic|in-Built ANC,Plug N Play,LongBattery Life,Ultra-Low Latency,Upto 30M Range|Compatible with iPhone&amp;Android|Vlogging,Streaming,Teaching,YouTube,Black</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4573,10 +4571,10 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>23441.53</v>
+        <v>25133.04</v>
       </c>
       <c r="F112" s="1" t="n">
-        <v>3.0</v>
+        <v>22.0</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>0.0</v>
@@ -4585,21 +4583,21 @@
         <v>0.0</v>
       </c>
       <c r="I112" s="1" t="n">
-        <v>3.0</v>
+        <v>22.0</v>
       </c>
       <c r="J112" s="1" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Audio Array All in 1 Pro Bundle | Condenser Mic with USB Bluetooth Soundcard Mixer | Complete Setup for Streaming, Podcasting, Gaming, Singing &amp; Home Studio Recording - GB-02</t>
+          <t>Audio Array AA-20 Microphone Arm Stand | 81cm Reach | Premium light weight &amp; slick design | Flexible height &amp; position adjustments | 1kg Weight Capacity | 5/8" to 3/8" Screw Adapter | Cable Ties</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4613,10 +4611,10 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>22833.04</v>
+        <v>24310.16</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>0.0</v>
@@ -4625,21 +4623,21 @@
         <v>0.0</v>
       </c>
       <c r="I113" s="1" t="n">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="J113" s="1" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Audio Array AM-W10 Professional Dual Wireless Lapel Mics | Upto 10hr Battery &amp; 100m Range | 2X Lapel mics, Type C Adapter for Easy Plug&amp;Play | Volume &amp; Mute Function | Vlogging, Streaming, YouTube</t>
+          <t>Audio Array AM-C45 XLR/USB Pro RGB Dynamic Microphone Kit | 192kHz/24bit Studio Quality Output | Volume Control, Mute and Noise Cancellation | Realtime Monitoring for Streaming, Gaming &amp; podcasting</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4653,7 +4651,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>22789.0</v>
+        <v>24061.87</v>
       </c>
       <c r="F114" s="1" t="n">
         <v>7.0</v>
@@ -4665,26 +4663,26 @@
         <v>0.0</v>
       </c>
       <c r="I114" s="1" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J114" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Audio Array AM-Mix6 6-Channel Hybrid USB Audio Mixer with 6 Analog + 2 Digital Inputs, 48kHz/16-Bit, +50dB Mic Gain, PAD Switch, Dual AUX Sends,128 DSP FX, Balanced XLR Main Output, ≥102dB Max SPL</t>
+          <t>TONOR USB Microphone Kit, Streaming Podcast PC Cardioid Condenser Computer Mic for Gaming, YouTube Video, Recording Music, Voice Over, Studio Mic Bundle with Adjustment Arm Stand(TC40)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4693,10 +4691,10 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>21607.62</v>
+        <v>22476.25</v>
       </c>
       <c r="F115" s="1" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>0.0</v>
@@ -4705,21 +4703,21 @@
         <v>0.0</v>
       </c>
       <c r="I115" s="1" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="J115" s="1" t="n">
         <v>4.0</v>
-      </c>
-      <c r="J115" s="1" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Audio Array AM-C11X Pro XLR Podcast Mic Kit with Dynamic Microphone, 2m XLR Cable &amp; Adjustable Boom Arm | Studio-Quality Sound, 20Hz–20kHz, All-Metal Build for Podcasting, Streaming &amp; Recording</t>
+          <t>Audio Array AC-3XL Mic Cable 6.35mm Jack Male to XLR 3PIN Female Cord Wire | Microphone/Guitar Cable | Black, 1pc Pack (3 Meter/10 Feet)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4733,10 +4731,10 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>21350.85</v>
+        <v>22205.67</v>
       </c>
       <c r="F116" s="1" t="n">
-        <v>6.0</v>
+        <v>59.0</v>
       </c>
       <c r="G116" s="2" t="n">
         <v>0.0</v>
@@ -4745,21 +4743,21 @@
         <v>0.0</v>
       </c>
       <c r="I116" s="1" t="n">
-        <v>6.0</v>
+        <v>61.0</v>
       </c>
       <c r="J116" s="1" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Audio Array Professional Recording Bundle with BT Soundcard – USB Condenser Microphone, Studio Headphones | Cardioid Mic, Noise Reduction &amp; 6 Sound Modes for Streaming Recording &amp; Podcasting - PB-14</t>
+          <t>Audio Array AK-37 White MIDI Keyboard 37 Velocity Sensitive Keys, Built-in Speakers, 200 Presets, Sustain &amp; Touch, Tempo, Octave/Transpose/Tune, Master Volume Knob, LED Display BT AA &amp; Type-C Power</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4773,7 +4771,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>20977.18</v>
+        <v>20164.39</v>
       </c>
       <c r="F117" s="1" t="n">
         <v>6.0</v>
@@ -4787,21 +4785,19 @@
       <c r="I117" s="1" t="n">
         <v>6.0</v>
       </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="J117" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Audio Array AK-37 White MIDI Keyboard 37 Velocity Sensitive Keys, Built-in Speakers, 200 Presets, Sustain &amp; Touch, Tempo, Octave/Transpose/Tune, Master Volume Knob, LED Display BT AA &amp; Type-C Power</t>
+          <t>Audio Array Portable Karaoke Bundle | Dual Wireless UHF Microphones with Rechargeable Battery Receiver &amp; USB Plug n Play BT Soundcard Mixer | Ideal for Parties, Home Karaoke &amp; Live Singing - KB-01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4815,10 +4811,10 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>20164.39</v>
+        <v>19757.62</v>
       </c>
       <c r="F118" s="1" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G118" s="2" t="n">
         <v>0.0</v>
@@ -4827,21 +4823,23 @@
         <v>0.0</v>
       </c>
       <c r="I118" s="1" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="J118" s="1" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Audio Array Portable Karaoke Bundle | Dual Wireless UHF Microphones with Rechargeable Battery Receiver &amp; USB Plug n Play BT Soundcard Mixer | Ideal for Parties, Home Karaoke &amp; Live Singing - KB-01</t>
+          <t>Audio Array AI-06 Streaming Audio Mixer Sound Card | XLR, 1/4" &amp; line in | PC/Phone RGB Mixer with Volume Fader, Individual Control, Mute and Monitoring, 48V Phantom Power | Stream, Podcast &amp; Karaoke</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4855,10 +4853,10 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>19757.62</v>
+        <v>18782.37</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G119" s="2" t="n">
         <v>0.0</v>
@@ -4867,23 +4865,21 @@
         <v>0.0</v>
       </c>
       <c r="I119" s="1" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>7.0</v>
+      </c>
+      <c r="J119" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Audio Array AA-20 Microphone Arm Stand | 81cm Reach | Premium light weight &amp; slick design | Flexible height &amp; position adjustments | 1kg Weight Capacity | 5/8" to 3/8" Screw Adapter | Cable Ties</t>
+          <t>Audio Array AM-W19 Wireless Lavalier Microphone|192kHz/24bit |AI Noise Cancellation for iPhone/Android, 32h Charging Case, Plug &amp; Play for Vlogging, Streaming, Meetings, Video Recording</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4897,7 +4893,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>19397.46</v>
+        <v>18634.73</v>
       </c>
       <c r="F120" s="1" t="n">
         <v>11.0</v>
@@ -4909,26 +4905,26 @@
         <v>0.0</v>
       </c>
       <c r="I120" s="1" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="J120" s="1" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Audio Array AI-06 Streaming Audio Mixer Sound Card | XLR, 1/4" &amp; line in | PC/Phone RGB Mixer with Volume Fader, Individual Control, Mute and Monitoring, 48V Phantom Power | Stream, Podcast &amp; Karaoke</t>
+          <t>TONOR RGB USB Gaming Microphone Kit, Podcast Microphone for PC, One-tap Mute for Streaming, Cardioid Condenser Microphone for PS4/5 Gamer Youtuber, Studio Mic Bundle with Adjustment Arm Stand</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4937,10 +4933,10 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>18782.37</v>
+        <v>17752.53</v>
       </c>
       <c r="F121" s="1" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>0.0</v>
@@ -4949,7 +4945,7 @@
         <v>0.0</v>
       </c>
       <c r="I121" s="1" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="J121" s="1" t="n">
         <v>2.0</v>
@@ -4958,12 +4954,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TONOR RGB USB Gaming Microphone Kit, Podcast Microphone for PC, One-tap Mute for Streaming, Cardioid Condenser Microphone for PS4/5 Gamer Youtuber, Studio Mic Bundle with Adjustment Arm Stand</t>
+          <t>TONOR USB Dynamic Microphone for Podcast Gaming Mic with RGB for Recording, Live Streaming, YouTube, Singing, Studio, Tiktok Microfono with Quick Mute&amp; Stand Compatible with PC/Cellphone TypeC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4977,10 +4973,10 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>17752.53</v>
+        <v>16838.99</v>
       </c>
       <c r="F122" s="1" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>0.0</v>
@@ -4989,26 +4985,26 @@
         <v>0.0</v>
       </c>
       <c r="I122" s="1" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="J122" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TONOR USB Microphone Kit, Streaming Podcast PC Cardioid Condenser Computer Mic for Gaming, YouTube Video, Recording Music, Voice Over, Studio Mic Bundle with Adjustment Arm Stand(TC40)</t>
+          <t>Audio Array Complete Podcast Bundle | USB/XLR Dynamic Mic with Audio Interface 24bit/192kHz &amp; Boom Arm Stand | Professional Streaming &amp; Recording Kit for PC, Mac &amp; Mobile Devices - PB-02</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5017,10 +5013,10 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>16884.73</v>
+        <v>15591.52</v>
       </c>
       <c r="F123" s="1" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>0.0</v>
@@ -5029,26 +5025,28 @@
         <v>0.0</v>
       </c>
       <c r="I123" s="1" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="J123" s="1" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TONOR TM310 USB Conference Microphone for Laptop, Adjustable Computer PC Mic with Mute Button &amp; LED Indicator for Video Call Meeting, Mic for Desktop Zoom Skype YouTube, Plug-Play for MacOS Windows</t>
+          <t>Audio Array Ultimate Podcast Bundle | Dynamic Microphone with USB/XLR Connectivity &amp; 24-Bit/192kHz Audio Interface | Ideal for Podcasting, Streaming, Voice Recording &amp; Content Creation - PB-01</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5057,10 +5055,10 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>16688.15</v>
+        <v>15337.29</v>
       </c>
       <c r="F124" s="1" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>0.0</v>
@@ -5069,26 +5067,26 @@
         <v>0.0</v>
       </c>
       <c r="I124" s="1" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="J124" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TONOR USB Conference Microphone, 360 Omnidirectional PC Computer Condenser Mic with Mute Button for Online Meeting/Class, Zoom Call, Skype Chatting, Plug &amp; Play (TM20,Red)</t>
+          <t>Audio Array AM-Mix6 6-Channel Hybrid USB Audio Mixer with 6 Analog + 2 Digital Inputs, 48kHz/16-Bit, +50dB Mic Gain, PAD Switch, Dual AUX Sends,128 DSP FX, Balanced XLR Main Output, ≥102dB Max SPL</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5097,10 +5095,10 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>14994.91</v>
+        <v>14405.08</v>
       </c>
       <c r="F125" s="1" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>0.0</v>
@@ -5109,21 +5107,21 @@
         <v>0.0</v>
       </c>
       <c r="I125" s="1" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="J125" s="1" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Audio Array AM-Mix4 OTG 4-Channel 3 Out Hybrid USB Summing Audio Mixer (4 Analog + 2 Digital), 192kHz/24-Bit OTG, 99 DSP FX, Logarithmic Faders, Balanced XLR Out, Phantom Power, Hi-Z, 3-Band EQ</t>
+          <t>Audio Array AM-C11X Pro XLR Podcast Mic Kit with Dynamic Microphone, 2m XLR Cable &amp; Adjustable Boom Arm | Studio-Quality Sound, 20Hz–20kHz, All-Metal Build for Podcasting, Streaming &amp; Recording</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5137,10 +5135,10 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>13980.51</v>
+        <v>14233.91</v>
       </c>
       <c r="F126" s="1" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>0.0</v>
@@ -5149,10 +5147,10 @@
         <v>0.0</v>
       </c>
       <c r="I126" s="1" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="J126" s="1" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="127">
@@ -5198,17 +5196,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0DP3194QN</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm | Mechanical Spring Desk Mount for 17–45 Inch Single Screen | 16Kg Capacity | VESA 75x75 &amp; 100x100 | Adjustable Monitor Arm Desk Mount</t>
+          <t>TONOR RGB USB Microphone, Cardioid Condenser Computer PC Mic with Tripod Stand, Pop Filter, Shock Mount for Gaming, Streaming, Podcasting, YouTube, Twitch, Compatible with Laptop Desktop,TC30 with RGB</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>White Mulberry</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5217,10 +5215,10 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>12369.48</v>
+        <v>12706.8</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>0.0</v>
@@ -5229,26 +5227,26 @@
         <v>0.0</v>
       </c>
       <c r="I128" s="1" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="J128" s="1" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TONOR RGB USB Microphone, Cardioid Condenser Computer PC Mic with Tripod Stand, Pop Filter, Shock Mount for Gaming, Streaming, Podcasting, YouTube, Twitch, Compatible with Laptop Desktop,TC30 with RGB</t>
+          <t>Audio Array AM-C20 USB Microphone | Unique Tilt Stand &amp; one Touch Mute | Plug n Play, No Latency Cardioid Pickup | for PC, Smartphones, iOS | Gaming, Streaming, Podcasts, Twitch, YouTube, Discord</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5257,10 +5255,10 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>10589.0</v>
+        <v>12550.84</v>
       </c>
       <c r="F129" s="1" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G129" s="2" t="n">
         <v>0.0</v>
@@ -5269,21 +5267,21 @@
         <v>0.0</v>
       </c>
       <c r="I129" s="1" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="J129" s="1" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TONOR Cardioid Condenser Microphone, USB Computer Mic Kit with 24mm Diaphragm/Spider Shock Mount for Podcasting, Gaming, Streaming, YouTube, Voice Over, Studio/Home Recording, TC-2030</t>
+          <t>TONOR TM310 USB Conference Microphone for Laptop, Adjustable Computer PC Mic with Mute Button &amp; LED Indicator for Video Call Meeting, Mic for Desktop Zoom Skype YouTube, Plug-Play for MacOS Windows</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5297,10 +5295,10 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>10505.92</v>
+        <v>12494.93</v>
       </c>
       <c r="F130" s="1" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G130" s="2" t="n">
         <v>0.0</v>
@@ -5309,23 +5307,21 @@
         <v>0.0</v>
       </c>
       <c r="I130" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>6.0</v>
+      </c>
+      <c r="J130" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Audio Array AM-C41 Plug &amp; Play AI Noise Cancellation USB Condenser Microphone | Mute Button/Echo/Volume Knob | Kit with Tripod, Mic Cover | Gaming, Streaming, Podcast | Mac/PC/Laptop/Mobile</t>
+          <t>Audio Array AM-C37 Premium USB/XLR Dynamic Podcast Microphone | Volume, Mute Controls &amp; Headphone Monitoring | Premium Metal Build | 2 Meter USB Cable Included | 96kHz/24bit Studio Performance</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5339,10 +5335,10 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>9663.54</v>
+        <v>12160.18</v>
       </c>
       <c r="F131" s="1" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G131" s="2" t="n">
         <v>0.0</v>
@@ -5351,7 +5347,7 @@
         <v>0.0</v>
       </c>
       <c r="I131" s="1" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="J131" s="1" t="n">
         <v>1.0</v>
@@ -5360,12 +5356,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Audio Array AM-C20 USB Microphone | Unique Tilt Stand &amp; one Touch Mute | Plug n Play, No Latency Cardioid Pickup | for PC, Smartphones, iOS | Gaming, Streaming, Podcasts, Twitch, YouTube, Discord</t>
+          <t>Audio Array AM-C41 Plug &amp; Play AI Noise Cancellation USB Condenser Microphone | Mute Button/Echo/Volume Knob | Kit with Tripod, Mic Cover | Gaming, Streaming, Podcast | Mac/PC/Laptop/Mobile</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5379,7 +5375,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>9121.18</v>
+        <v>11018.62</v>
       </c>
       <c r="F132" s="1" t="n">
         <v>8.0</v>
@@ -5394,23 +5390,23 @@
         <v>8.0</v>
       </c>
       <c r="J132" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Audio Array AM-C37 Premium USB/XLR Dynamic Podcast Microphone | Volume, Mute Controls &amp; Headphone Monitoring | Premium Metal Build | 2 Meter USB Cable Included | 96kHz/24bit Studio Performance</t>
+          <t>Tonor Mic Arm Desk Mount, Low Profile Boom Arm, Microphone Arm, Adjustable Mic Stand with Desk Mount Clamp, Cable Management, 3/8’’ and 5/8’’ Screwadapter for Most Microphone, Black, T20LP</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5419,10 +5415,10 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>9110.18</v>
+        <v>11011.86</v>
       </c>
       <c r="F133" s="1" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>0.0</v>
@@ -5431,23 +5427,21 @@
         <v>0.0</v>
       </c>
       <c r="I133" s="1" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>6.0</v>
+      </c>
+      <c r="J133" s="1" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TONOR Professional Vocal Microphone for Singing, Dynamic Handheld Wired Karaoke Mic, Cardioid Studio Microfono with 4.5M XLR to 1/4" Cable, for Speakers/Mixer Machine/Amp/Speech/Karaoke and Outdoors</t>
+          <t>TONOR Cardioid Condenser Microphone, USB Computer Mic Kit with 24mm Diaphragm/Spider Shock Mount for Podcasting, Gaming, Streaming, YouTube, Voice Over, Studio/Home Recording, TC-2030</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5461,10 +5455,10 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>6015.26</v>
+        <v>10505.92</v>
       </c>
       <c r="F134" s="1" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>0.0</v>
@@ -5473,7 +5467,7 @@
         <v>0.0</v>
       </c>
       <c r="I134" s="1" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -5484,12 +5478,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Audio Array RGB Gaming Mic Bundle with USB/XLR Microphone, Boom Arm &amp; Sound Card Mixer | Streaming Mic Kit with Voice Effects, AI Noise Cancel, RGB Lights for Podcasting, Gaming &amp; Recording - PB-09</t>
+          <t>Audio Array AM-Mix4 OTG 4-Channel 3 Out Hybrid USB Summing Audio Mixer (4 Analog + 2 Digital), 192kHz/24-Bit OTG, 99 DSP FX, Logarithmic Faders, Balanced XLR Out, Phantom Power, Hi-Z, 3-Band EQ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5503,10 +5497,10 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>5416.58</v>
+        <v>9320.34</v>
       </c>
       <c r="F135" s="1" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>0.0</v>
@@ -5515,28 +5509,26 @@
         <v>0.0</v>
       </c>
       <c r="I135" s="1" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>2.0</v>
+      </c>
+      <c r="J135" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0DP3194QN</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TONOR USB Dynamic Microphone for Podcast Gaming Mic with RGB for Recording, Live Streaming, YouTube, Singing, Studio, Tiktok Microfono with Quick Mute&amp; Stand Compatible with PC/Cellphone TypeC</t>
+          <t>White Mulberry Monitor Arm | Mechanical Spring Desk Mount for 17–45 Inch Single Screen | 16Kg Capacity | VESA 75x75 &amp; 100x100 | Adjustable Monitor Arm Desk Mount</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>White Mulberry</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5545,7 +5537,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>4980.51</v>
+        <v>8895.75</v>
       </c>
       <c r="F136" s="1" t="n">
         <v>3.0</v>
@@ -5560,18 +5552,18 @@
         <v>3.0</v>
       </c>
       <c r="J136" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TONOR USB Microphone Kit, PC Podcast Recording Cardioid Condenser Computer Mic Set for Gaming, Streaming, Singing, Voice Over, YouTube, Studio Mic Bundle with Adjustable Arm Stand, TC30+</t>
+          <t>TONOR USB Microphone Computer Gaming Condenser Mic, Noise-Canceling Zero Latency Monitoring for Podcast/Recording/Livestreaming/Teleconferencing on PC/Mac/Android Device, Plug and Play, ORCA001</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5585,7 +5577,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>4744.07</v>
+        <v>6523.73</v>
       </c>
       <c r="F137" s="1" t="n">
         <v>2.0</v>
@@ -5599,21 +5591,19 @@
       <c r="I137" s="1" t="n">
         <v>2.0</v>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="J137" s="1" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Audio Array AM-W21 Wireless Microphone Kit | Built in Recording, Noise Reduction &amp; Echo | Smartphones, Cameras, Laptops | Dual-Channel Recording, 200 feet Transmission Range, 48-Hour Battery Life</t>
+          <t>Audio Array RGB Gaming Mic Bundle with USB/XLR Microphone, Boom Arm &amp; Sound Card Mixer | Streaming Mic Kit with Voice Effects, AI Noise Cancel, RGB Lights for Podcasting, Gaming &amp; Recording - PB-09</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5627,10 +5617,10 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>4675.7</v>
+        <v>5416.58</v>
       </c>
       <c r="F138" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>0.0</v>
@@ -5639,7 +5629,7 @@
         <v>0.0</v>
       </c>
       <c r="I138" s="1" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -5650,12 +5640,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tonor Mic Arm Desk Mount, Low Profile Boom Arm, Microphone Arm, Adjustable Mic Stand with Desk Mount Clamp, Cable Management, 3/8’’ and 5/8’’ Screwadapter for Most Microphone, Black, T20LP</t>
+          <t>TONOR USB Microphone Kit, PC Podcast Recording Cardioid Condenser Computer Mic Set for Gaming, Streaming, Singing, Voice Over, YouTube, Studio Mic Bundle with Adjustable Arm Stand, TC30+</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5669,7 +5659,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>3896.61</v>
+        <v>4744.07</v>
       </c>
       <c r="F139" s="1" t="n">
         <v>2.0</v>
@@ -5683,19 +5673,21 @@
       <c r="I139" s="1" t="n">
         <v>2.0</v>
       </c>
-      <c r="J139" s="1" t="n">
-        <v>1.0</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TONOR USB Microphone Computer Gaming Condenser Mic, Noise-Canceling Zero Latency Monitoring for Podcast/Recording/Livestreaming/Teleconferencing on PC/Mac/Android Device, Plug and Play, ORCA001</t>
+          <t>TONOR Professional Vocal Microphone for Singing, Dynamic Handheld Wired Karaoke Mic, Cardioid Studio Microfono with 4.5M XLR to 1/4" Cable, for Speakers/Mixer Machine/Amp/Speech/Karaoke and Outdoors</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5709,7 +5701,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>3304.24</v>
+        <v>3007.63</v>
       </c>
       <c r="F140" s="1" t="n">
         <v>1.0</v>
@@ -5732,17 +5724,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TONOR USB Gaming Microphone, RGB Streaming Microfono Set, PC Podcast Recording Computer Mic for PS4/5, Discord, Twitch, Cardioid Condenser Mic with Adjustable Boom Arm Stand TC30S+</t>
+          <t>Audio Array AM-W21 Wireless Microphone Kit | Built in Recording, Noise Reduction &amp; Echo | Smartphones, Cameras, Laptops | Dual-Channel Recording, 200 feet Transmission Range, 48-Hour Battery Life</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TONOR</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5765,8 +5757,10 @@
       <c r="I141" s="1" t="n">
         <v>1.0</v>
       </c>
-      <c r="J141" s="1" t="n">
-        <v>2.0</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -5854,17 +5848,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Audio Array AM-W46 Groove Wireless Bluetooth 5.3 Bookshelf Speaker 30W | 5400mAh upto 24h Long Battery | 3 EQ Modes | Stylish Premium Metal Body | Superior Bass Quality</t>
+          <t>TONOR USB Gaming Microphone, RGB Streaming Microfono Set, PC Podcast Recording Computer Mic for PS4/5, Discord, Twitch, Cardioid Condenser Mic with Adjustable Boom Arm Stand TC30S+</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5878,36 +5872,28 @@
       <c r="F144" s="1" t="n">
         <v>0.0</v>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G144" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I144" s="1" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="J144" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Audio Array Complete Podcast Bundle | USB/XLR Dynamic Mic with Audio Interface 24bit/192kHz &amp; Boom Arm Stand | Professional Streaming &amp; Recording Kit for PC, Mac &amp; Mobile Devices - PB-02</t>
+          <t>Audio Array AM-Pro8 8-Channel Hybrid USB Mixer 8 Analog+2 Digital Inputs, 48kHz/16-Bit, Built-In Compressor, 6AUX Sends, Group Buses, Insert Points,+24dBu Balanced Outputs for Live, Studio &amp; Broadcast</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5941,19 +5927,21 @@
           <t/>
         </is>
       </c>
-      <c r="J145" s="1" t="n">
-        <v>2.0</v>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Audio Array AI-04 2x2 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power Support | 24-bit/192kHz High Fidelity Recording | XLR/MIC/LINE inputs | Plug and Play-No Drivers | Metal Body | Black</t>
+          <t>Audio Array AM-C30 Metal RGB Professional USB Microphone | One-Touch Mute, Gain &amp; No-Latency Monitoring Controls | Shock Mount and Tripod | for PC/Mobile, Gaming, Streaming, Podcasting &amp; Voiceover</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5996,12 +5984,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Audio Array AM-Pro8 8-Channel Hybrid USB Mixer 8 Analog+2 Digital Inputs, 48kHz/16-Bit, Built-In Compressor, 6AUX Sends, Group Buses, Insert Points,+24dBu Balanced Outputs for Live, Studio &amp; Broadcast</t>
+          <t>Audio Array AI-04 2x2 Audio Interface | Premium Mic Pre-Amps | 48V Phantom Power Support | 24-bit/192kHz High Fidelity Recording | XLR/MIC/LINE inputs | Plug and Play-No Drivers | Metal Body | Black</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -6044,17 +6032,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BRKDLXCD</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Audio Array AM-C30 Metal RGB Professional USB Microphone | One-Touch Mute, Gain &amp; No-Latency Monitoring Controls | Shock Mount and Tripod | for PC/Mobile, Gaming, Streaming, Podcasting &amp; Voiceover</t>
+          <t>RGB Boom Arm, TONOR Adjustable Mic Stand with RGB Light for HyperX QuadCast/Blue Yeti/Shure SM7B/Rode NT1, Rotatable Suspension Boom Scissor Stand for Gaming Streaming Podcasting YouTube Recording T90</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>TONOR</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -6063,10 +6051,10 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.0</v>
+        <v>-6947.46</v>
       </c>
       <c r="F148" s="1" t="n">
-        <v>0.0</v>
+        <v>-2.0</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -6084,54 +6072,6 @@
         </is>
       </c>
       <c r="J148" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>B0BRKDLXCD</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>RGB Boom Arm, TONOR Adjustable Mic Stand with RGB Light for HyperX QuadCast/Blue Yeti/Shure SM7B/Rode NT1, Rotatable Suspension Boom Scissor Stand for Gaming Streaming Podcasting YouTube Recording T90</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>TONOR</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>-6947.46</v>
-      </c>
-      <c r="F149" s="1" t="n">
-        <v>-2.0</v>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +424,52 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Product Title</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Store Code</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Ordered Revenue</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Ordered Units</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Shipped Revenue</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Shipped COGS</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Shipped Units</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Customer Returns</t>
         </is>
@@ -505,10 +493,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1638979.36</v>
+        <v>6030085.73</v>
       </c>
       <c r="F3" t="n">
-        <v>403</v>
+        <v>1478</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>409</v>
+        <v>1489</v>
       </c>
       <c r="J3" t="n">
-        <v>78</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +529,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1572303.32</v>
+        <v>5661283.31</v>
       </c>
       <c r="F4" t="n">
-        <v>700</v>
+        <v>2513</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,16 +541,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>704</v>
+        <v>2518</v>
       </c>
       <c r="J4" t="n">
-        <v>131</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -577,10 +565,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>974696.8200000001</v>
+        <v>2618449.45</v>
       </c>
       <c r="F5" t="n">
-        <v>158</v>
+        <v>346</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,16 +577,16 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>160</v>
+        <v>346</v>
       </c>
       <c r="J5" t="n">
-        <v>39</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -613,10 +601,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>667654.3099999999</v>
+        <v>2268633.87</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>381</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>86</v>
+        <v>376</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +637,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>625092.25</v>
+        <v>2023673.8</v>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>466</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +649,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +673,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>450621.41</v>
+        <v>1519294.43</v>
       </c>
       <c r="F8" t="n">
-        <v>266</v>
+        <v>895</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>265</v>
+        <v>892</v>
       </c>
       <c r="J8" t="n">
-        <v>46</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +709,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>419731.19</v>
+        <v>1385000.81</v>
       </c>
       <c r="F9" t="n">
-        <v>180</v>
+        <v>591</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,16 +721,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>181</v>
+        <v>600</v>
       </c>
       <c r="J9" t="n">
-        <v>54</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -757,10 +745,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>268400.9</v>
+        <v>938360.23</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>319</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,16 +757,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>37</v>
+        <v>318</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -793,10 +781,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>218544.62</v>
+        <v>902182.76</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +793,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>68</v>
+        <v>281</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +817,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>212542.46</v>
+        <v>689420.78</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>212</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,16 +829,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -865,10 +853,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210277.02</v>
+        <v>624458.4500000001</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -901,10 +889,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>186422.01</v>
+        <v>591296.61</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -937,10 +925,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>176209.56</v>
+        <v>546822.1</v>
       </c>
       <c r="F15" t="n">
-        <v>130</v>
+        <v>408</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>129</v>
+        <v>408</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -973,10 +961,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>154213.57</v>
+        <v>519244.17</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1009,10 +997,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>131999.23</v>
+        <v>498079.72</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,10 +1009,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>42</v>
+        <v>191</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1033,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>111179.28</v>
+        <v>473999.55</v>
       </c>
       <c r="F18" t="n">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1045,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>85</v>
+        <v>351</v>
       </c>
       <c r="J18" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1069,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>110383.08</v>
+        <v>432957.34</v>
       </c>
       <c r="F19" t="n">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,16 +1081,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="J19" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1117,10 +1105,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>110303.42</v>
+        <v>393053.04</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,16 +1117,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>43</v>
+        <v>201</v>
       </c>
       <c r="J20" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1153,10 +1141,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>108007.8</v>
+        <v>366807.75</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1177,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>75645.84</v>
+        <v>342405.7</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>259</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,22 +1189,22 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1225,10 +1213,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>75485.52</v>
+        <v>339696.37</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,16 +1225,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1261,10 +1249,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>72050</v>
+        <v>334453.09</v>
       </c>
       <c r="F24" t="n">
-        <v>131</v>
+        <v>706</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>132</v>
+        <v>711</v>
       </c>
       <c r="J24" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1297,10 +1285,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71733.95</v>
+        <v>235604.96</v>
       </c>
       <c r="F25" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,16 +1297,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="J25" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1333,10 +1321,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>71135.60000000001</v>
+        <v>232254.96</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>232</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1333,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>233</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,10 +1357,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>68294.02</v>
+        <v>228191.18</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,22 +1369,22 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1405,10 +1393,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>67783.03999999999</v>
+        <v>227097.54</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>119</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1441,10 +1429,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>66046.5</v>
+        <v>223895.73</v>
       </c>
       <c r="F29" t="n">
-        <v>65</v>
+        <v>403</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1441,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1465,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>64400</v>
+        <v>220101.48</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>204</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,22 +1477,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>205</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1513,10 +1501,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>64043.96</v>
+        <v>208468.92</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,22 +1513,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1549,10 +1537,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>62870.49</v>
+        <v>190907.63</v>
       </c>
       <c r="F32" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,22 +1549,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1585,10 +1573,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>60986.44</v>
+        <v>189106.13</v>
       </c>
       <c r="F33" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,16 +1585,16 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="J33" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1621,10 +1609,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>55922.02</v>
+        <v>178543.11</v>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,16 +1621,16 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1657,10 +1645,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53470.33</v>
+        <v>177760.99</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,16 +1657,16 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1693,10 +1681,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>52396.59</v>
+        <v>175828.82</v>
       </c>
       <c r="F36" t="n">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1729,10 +1717,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>50827.2</v>
+        <v>172683.86</v>
       </c>
       <c r="F37" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,22 +1729,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1765,10 +1753,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>50316.12</v>
+        <v>167702.67</v>
       </c>
       <c r="F38" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,16 +1765,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1801,10 +1789,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>47445.72</v>
+        <v>164294.13</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,22 +1801,22 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1837,10 +1825,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>46678.82</v>
+        <v>161704.25</v>
       </c>
       <c r="F40" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,16 +1837,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="J40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1861,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>40667.76</v>
+        <v>151356.73</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,22 +1873,22 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1909,10 +1897,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>39546.57</v>
+        <v>151303.39</v>
       </c>
       <c r="F42" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,22 +1909,22 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="J42" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1945,10 +1933,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>38122.92</v>
+        <v>149591.65</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>324</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,16 +1945,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>323</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1981,10 +1969,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>37791.21</v>
+        <v>148318.77</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,16 +1981,16 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2017,10 +2005,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37269.5</v>
+        <v>146502.56</v>
       </c>
       <c r="F45" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,22 +2017,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2053,10 +2041,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>34556.04</v>
+        <v>145156.67</v>
       </c>
       <c r="F46" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,22 +2053,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="J46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2089,10 +2077,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>34150.02</v>
+        <v>142404.15</v>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="J47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2125,10 +2113,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>33891.52</v>
+        <v>132107.61</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,22 +2125,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2161,10 +2149,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33881.34</v>
+        <v>130115.24</v>
       </c>
       <c r="F49" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,22 +2161,22 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2197,10 +2185,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>32710.16</v>
+        <v>119612.69</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,16 +2197,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2221,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32196.62</v>
+        <v>118677.44</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,22 +2233,22 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2269,10 +2257,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>30844.91</v>
+        <v>117680.97</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,16 +2269,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2305,10 +2293,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>30483</v>
+        <v>110546.69</v>
       </c>
       <c r="F53" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,22 +2305,22 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2341,10 +2329,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>30251.7</v>
+        <v>109031.44</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,16 +2341,16 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2365,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29089.01</v>
+        <v>108172.88</v>
       </c>
       <c r="F55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,16 +2377,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2413,10 +2401,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>28967.76</v>
+        <v>107149.16</v>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2449,10 +2437,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>28322.89</v>
+        <v>102405.84</v>
       </c>
       <c r="F57" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,16 +2449,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2473,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>27875.4</v>
+        <v>99069.45</v>
       </c>
       <c r="F58" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2485,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,28 +2509,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>25319.47</v>
+        <v>98762.72</v>
       </c>
       <c r="F59" t="n">
+        <v>70</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>71</v>
+      </c>
+      <c r="J59" t="n">
         <v>23</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>23</v>
-      </c>
-      <c r="J59" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,28 +2545,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>23044.07</v>
+        <v>98303.22</v>
       </c>
       <c r="F60" t="n">
+        <v>97</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>95</v>
+      </c>
+      <c r="J60" t="n">
         <v>8</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2593,10 +2581,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>22115.85</v>
+        <v>98299.98000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,16 +2593,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2629,10 +2617,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21200.69</v>
+        <v>91333.84</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2629,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2653,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>20333.88</v>
+        <v>87389.8</v>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,16 +2665,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2701,10 +2689,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>20333.88</v>
+        <v>83450.03</v>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2713,16 +2701,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2725,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>18969.51</v>
+        <v>80756.64</v>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,22 +2737,22 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2773,10 +2761,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>18743.23</v>
+        <v>79550.75999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,16 +2773,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2809,28 +2797,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>17795.76</v>
+        <v>79400</v>
       </c>
       <c r="F67" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>8</v>
+      </c>
+      <c r="J67" t="n">
         <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2833,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>16309.3</v>
+        <v>78111.85000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2845,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2869,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>15928.8</v>
+        <v>75277.91</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,16 +2881,16 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2917,10 +2905,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>15461.85</v>
+        <v>73209.18000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,22 +2917,22 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2953,10 +2941,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>15417.78</v>
+        <v>71813.64</v>
       </c>
       <c r="F71" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,16 +2953,16 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2989,10 +2977,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>14614.4</v>
+        <v>70532.98</v>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,16 +2989,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3025,10 +3013,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>14569.5</v>
+        <v>67978.55</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3025,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3049,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>14066.1</v>
+        <v>67847.98</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,22 +3061,22 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3097,10 +3085,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>13934.76</v>
+        <v>67777.89999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,16 +3097,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3121,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>13726.26</v>
+        <v>65223.71</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,10 +3157,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>13555.92</v>
+        <v>65072.03</v>
       </c>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3181,16 +3169,16 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3205,10 +3193,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>12950.89</v>
+        <v>61593.19</v>
       </c>
       <c r="F78" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3217,22 +3205,22 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3241,10 +3229,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>12705.94</v>
+        <v>55451.64</v>
       </c>
       <c r="F79" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,10 +3265,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>12577.14</v>
+        <v>54804.05</v>
       </c>
       <c r="F80" t="n">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,16 +3277,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>134</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3301,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>12452.52</v>
+        <v>54770.41</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3337,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12285.64</v>
+        <v>54327.64</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3385,10 +3373,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11858.48</v>
+        <v>53474.08</v>
       </c>
       <c r="F83" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3385,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
+        <v>28</v>
+      </c>
+      <c r="J83" t="n">
         <v>9</v>
-      </c>
-      <c r="J83" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3409,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>11858.46</v>
+        <v>53436.39999999999</v>
       </c>
       <c r="F84" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3421,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3445,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11480.47</v>
+        <v>52938.08</v>
       </c>
       <c r="F85" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,22 +3457,22 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3493,10 +3481,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10677.96</v>
+        <v>50720.33</v>
       </c>
       <c r="F86" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,22 +3493,22 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3529,10 +3517,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10676.28</v>
+        <v>50264.36</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,16 +3529,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3565,10 +3553,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>10674.56</v>
+        <v>47444.92</v>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,16 +3565,16 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
+        <v>15</v>
+      </c>
+      <c r="J88" t="n">
         <v>5</v>
-      </c>
-      <c r="J88" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3601,10 +3589,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10078.83</v>
+        <v>47027.14999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3616,19 +3604,19 @@
         <v>8</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3637,7 +3625,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>9488.120000000001</v>
+        <v>45081.36</v>
       </c>
       <c r="F90" t="n">
         <v>4</v>
@@ -3649,16 +3637,16 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3673,10 +3661,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>9150</v>
+        <v>43451.64</v>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,22 +3673,22 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J91" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3709,10 +3697,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>8894.049999999999</v>
+        <v>41940.71999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,16 +3709,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3733,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>8880.48</v>
+        <v>41640.73</v>
       </c>
       <c r="F93" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,16 +3745,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J93" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,10 +3769,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>8641.530000000001</v>
+        <v>38981.36</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3793,22 +3781,22 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3817,10 +3805,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>8471.200000000001</v>
+        <v>37791.21</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3838,7 +3826,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3853,10 +3841,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>8130.48</v>
+        <v>37313.54</v>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3865,16 +3853,16 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J96" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3889,10 +3877,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>7990.66</v>
+        <v>36603.36</v>
       </c>
       <c r="F97" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,16 +3889,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3925,10 +3913,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6777.96</v>
+        <v>36332.95</v>
       </c>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3937,22 +3925,22 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3961,10 +3949,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6226.26</v>
+        <v>33720.31</v>
       </c>
       <c r="F99" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,16 +3961,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3985,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5761.02</v>
+        <v>33111.86</v>
       </c>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4033,10 +4021,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5716.1</v>
+        <v>32884.8</v>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4033,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,34 +4057,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5197.46</v>
+        <v>31772.87</v>
       </c>
       <c r="F102" t="n">
+        <v>7</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>7</v>
+      </c>
+      <c r="J102" t="n">
         <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4105,10 +4093,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5082.2</v>
+        <v>30834.72</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,16 +4105,16 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4141,10 +4129,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4827.96</v>
+        <v>27419.48</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,16 +4141,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4165,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4575.42</v>
+        <v>27274.55</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,22 +4177,22 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4213,10 +4201,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4235.6</v>
+        <v>25630.25</v>
       </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4225,16 +4213,16 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4249,10 +4237,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3903.64</v>
+        <v>23892.37</v>
       </c>
       <c r="F107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4261,16 +4249,16 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4285,10 +4273,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3568.64</v>
+        <v>23255.11</v>
       </c>
       <c r="F108" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4297,22 +4285,22 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4321,10 +4309,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3388.98</v>
+        <v>22829.65</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -4342,7 +4330,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4357,10 +4345,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3388.98</v>
+        <v>22488.11</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,16 +4357,16 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4381,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3385.6</v>
+        <v>22115.85</v>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4429,10 +4417,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3304.24</v>
+        <v>21268.64</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,16 +4429,16 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4453,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2710.16</v>
+        <v>21200.69</v>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,16 +4465,16 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4501,10 +4489,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2710.16</v>
+        <v>21072.06</v>
       </c>
       <c r="F114" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J114" t="n">
         <v>2</v>
@@ -4522,13 +4510,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4537,10 +4525,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2477.97</v>
+        <v>19905.91</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,16 +4537,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4561,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2414.41</v>
+        <v>19825.44</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
         <v>2</v>
@@ -4594,7 +4582,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4609,10 +4597,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2372.04</v>
+        <v>19680.49</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,16 +4609,16 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4633,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2286.44</v>
+        <v>17795.76</v>
       </c>
       <c r="F118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -4666,13 +4654,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4681,10 +4669,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2236.44</v>
+        <v>17752.53</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4693,22 +4681,22 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,10 +4705,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1863.56</v>
+        <v>16942.4</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,16 +4717,16 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4753,10 +4741,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1863.56</v>
+        <v>15690.68</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,16 +4753,16 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4789,10 +4777,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1694.07</v>
+        <v>15591.52</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -4801,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4810,7 +4798,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4825,10 +4813,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1609.32</v>
+        <v>15246.6</v>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4837,16 +4825,16 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,10 +4849,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1355.08</v>
+        <v>13934.76</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4873,22 +4861,22 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4897,10 +4885,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>13728.78</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4909,22 +4897,22 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4933,10 +4921,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>12160.18</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4945,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J126" t="n">
         <v>1</v>
@@ -4954,7 +4942,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4969,10 +4957,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>11407.62</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4981,16 +4969,16 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5005,10 +4993,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>10505.94</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5026,7 +5014,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5041,10 +5029,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>9835.77</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5053,9 +5041,693 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J129" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>B089FVQD3Z</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>9488.120000000001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>B0G53LZNY3</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>9320.34</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>B0FJ2HZCVN</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>7626.27</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>B07TSN2H9D</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6947.45</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>2</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>B09Z5Q194D</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6523.73</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>B0GW96SHSK</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>B0FN7FYZM3</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>5416.58</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>B0BPMBMN3S</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5197.46</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>B0DFMQCGT1</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>5019.5</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>2</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>B0GW8Z556N</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3903.64</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>4</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>B0CFKZ72N7</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>3007.63</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>B0GW8R2RYM</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2710.16</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>B0BRCR2QQ7</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2372.04</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>B0C4YT43Z3</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1863.56</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>B0C4YTNJG7</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>B0BLKCDRNB</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>1355.08</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>B0BLK8DNPD</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>464.02</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>B0BG8CJXHH</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>B0BRKDLXCD</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>-6947.46</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[23/03/26 - 20/06/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[30/03/26 - 27/06/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6030085.73</v>
+        <v>5977215.36</v>
       </c>
       <c r="F3" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1489</v>
+        <v>1467</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5661283.31</v>
+        <v>5744261.53</v>
       </c>
       <c r="F4" t="n">
-        <v>2513</v>
+        <v>2548</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -541,10 +541,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2518</v>
+        <v>2532</v>
       </c>
       <c r="J4" t="n">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5">
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2618449.45</v>
+        <v>2572028.31</v>
       </c>
       <c r="F5" t="n">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -577,10 +577,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="J5" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2268633.87</v>
+        <v>2470895.85</v>
       </c>
       <c r="F6" t="n">
-        <v>381</v>
+        <v>412</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -613,10 +613,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="J6" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2023673.8</v>
+        <v>2154327.23</v>
       </c>
       <c r="F7" t="n">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -649,10 +649,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="J7" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1519294.43</v>
+        <v>1521537.52</v>
       </c>
       <c r="F8" t="n">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -685,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="J8" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9">
@@ -709,28 +709,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1385000.81</v>
+        <v>1392965.12</v>
       </c>
       <c r="F9" t="n">
+        <v>593</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>591</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>600</v>
-      </c>
       <c r="J9" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>938360.23</v>
+        <v>900742.99</v>
       </c>
       <c r="F10" t="n">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -757,16 +757,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="J10" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>902182.76</v>
+        <v>871429.8100000001</v>
       </c>
       <c r="F11" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -793,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J12" t="n">
         <v>28</v>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>624458.4500000001</v>
+        <v>654878.78</v>
       </c>
       <c r="F13" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>591296.61</v>
+        <v>608244.09</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>546822.1</v>
+        <v>577651.5</v>
       </c>
       <c r="F15" t="n">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="J15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>519244.17</v>
+        <v>545822.67</v>
       </c>
       <c r="F16" t="n">
-        <v>162</v>
+        <v>402</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>165</v>
+        <v>398</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>498079.72</v>
+        <v>489015.31</v>
       </c>
       <c r="F17" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1009,16 +1009,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J17" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>473999.55</v>
+        <v>483829.77</v>
       </c>
       <c r="F18" t="n">
-        <v>353</v>
+        <v>151</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1045,10 +1045,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>351</v>
+        <v>147</v>
       </c>
       <c r="J18" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>432957.34</v>
+        <v>428776.86</v>
       </c>
       <c r="F19" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1081,16 +1081,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="J19" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>393053.04</v>
+        <v>427391.64</v>
       </c>
       <c r="F20" t="n">
-        <v>201</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1117,16 +1117,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="J20" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>366807.75</v>
+        <v>388055.57</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1153,16 +1153,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>342405.7</v>
+        <v>338264.3</v>
       </c>
       <c r="F22" t="n">
-        <v>259</v>
+        <v>709</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>257</v>
+        <v>707</v>
       </c>
       <c r="J22" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23">
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>339696.37</v>
+        <v>337409.94</v>
       </c>
       <c r="F23" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1225,16 +1225,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>334453.09</v>
+        <v>333504.85</v>
       </c>
       <c r="F24" t="n">
-        <v>706</v>
+        <v>252</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>711</v>
+        <v>255</v>
       </c>
       <c r="J24" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>235604.96</v>
+        <v>255175.28</v>
       </c>
       <c r="F25" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1297,16 +1297,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>232254.96</v>
+        <v>239845.73</v>
       </c>
       <c r="F26" t="n">
-        <v>232</v>
+        <v>432</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1333,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>233</v>
+        <v>430</v>
       </c>
       <c r="J26" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228191.18</v>
+        <v>236897.39</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J27" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>227097.54</v>
+        <v>228961.1</v>
       </c>
       <c r="F28" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1405,16 +1405,16 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223895.73</v>
+        <v>225201.53</v>
       </c>
       <c r="F29" t="n">
-        <v>403</v>
+        <v>225</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1441,16 +1441,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>400</v>
+        <v>224</v>
       </c>
       <c r="J29" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220101.48</v>
+        <v>214822.32</v>
       </c>
       <c r="F30" t="n">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1477,16 +1477,16 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>205</v>
+        <v>99</v>
       </c>
       <c r="J30" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>208468.92</v>
+        <v>212015.07</v>
       </c>
       <c r="F31" t="n">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1513,16 +1513,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>99</v>
+        <v>195</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>190907.63</v>
+        <v>206333.91</v>
       </c>
       <c r="F32" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1549,16 +1549,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>189106.13</v>
+        <v>201643.96</v>
       </c>
       <c r="F33" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1585,16 +1585,16 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J33" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>178543.11</v>
+        <v>192749.33</v>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1621,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>177760.99</v>
+        <v>190470.31</v>
       </c>
       <c r="F35" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>175828.82</v>
+        <v>168818.66</v>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1693,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>172683.86</v>
+        <v>166837.25</v>
       </c>
       <c r="F37" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1729,22 +1729,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>167702.67</v>
+        <v>162989.71</v>
       </c>
       <c r="F38" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1765,16 +1765,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J38" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1789,34 +1789,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>164294.13</v>
+        <v>158397.64</v>
       </c>
       <c r="F39" t="n">
+        <v>111</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>110</v>
+      </c>
+      <c r="J39" t="n">
         <v>31</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>31</v>
-      </c>
-      <c r="J39" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>161704.25</v>
+        <v>155962.72</v>
       </c>
       <c r="F40" t="n">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1837,16 +1837,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="J40" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>151356.73</v>
+        <v>154649.91</v>
       </c>
       <c r="F41" t="n">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="J41" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>151303.39</v>
+        <v>153956.86</v>
       </c>
       <c r="F42" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
         <v>13</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>149591.65</v>
+        <v>150522.14</v>
       </c>
       <c r="F43" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1945,16 +1945,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J43" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>148318.77</v>
+        <v>149749.83</v>
       </c>
       <c r="F44" t="n">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1981,10 +1981,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="J44" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -2005,10 +2005,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>146502.56</v>
+        <v>149637.3</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J45" t="n">
         <v>3</v>
@@ -2026,13 +2026,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>145156.67</v>
+        <v>147046.11</v>
       </c>
       <c r="F46" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2053,22 +2053,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="J46" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>142404.15</v>
+        <v>142739</v>
       </c>
       <c r="F47" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>132107.61</v>
+        <v>139500.79</v>
       </c>
       <c r="F48" t="n">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>13</v>
+        <v>118</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>130115.24</v>
+        <v>132107.61</v>
       </c>
       <c r="F49" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2161,16 +2161,16 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>119612.69</v>
+        <v>129073.32</v>
       </c>
       <c r="F50" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2197,22 +2197,22 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="J50" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>118677.44</v>
+        <v>128083.01</v>
       </c>
       <c r="F51" t="n">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2233,16 +2233,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="J51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>117680.97</v>
+        <v>127369.42</v>
       </c>
       <c r="F52" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2269,22 +2269,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J52" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2293,10 +2293,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>110546.69</v>
+        <v>126822.13</v>
       </c>
       <c r="F53" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2305,22 +2305,22 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>109031.44</v>
+        <v>125894.04</v>
       </c>
       <c r="F54" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2341,16 +2341,16 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>108172.88</v>
+        <v>120713.63</v>
       </c>
       <c r="F55" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2377,16 +2377,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>107149.16</v>
+        <v>119641.32</v>
       </c>
       <c r="F56" t="n">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2413,16 +2413,16 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102405.84</v>
+        <v>104830.47</v>
       </c>
       <c r="F57" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2449,16 +2449,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J57" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>99069.45</v>
+        <v>100838.9</v>
       </c>
       <c r="F58" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2485,16 +2485,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J58" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>98762.72</v>
+        <v>98427.96000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2521,16 +2521,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="J59" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>98303.22</v>
+        <v>98299.98000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>98299.98000000001</v>
+        <v>95316.03999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2593,16 +2593,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>91333.84</v>
+        <v>89637.25999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2629,16 +2629,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
+        <v>65</v>
+      </c>
+      <c r="J62" t="n">
         <v>24</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>87389.8</v>
+        <v>89483.89999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2665,16 +2665,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="J63" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>83450.03</v>
+        <v>88490.64999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2701,16 +2701,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="J64" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>80756.64</v>
+        <v>82857.68000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2737,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>79550.75999999999</v>
+        <v>82219.39999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2773,16 +2773,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>79400</v>
+        <v>80315.26000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2809,16 +2809,16 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>78111.85000000001</v>
+        <v>76937.06</v>
       </c>
       <c r="F68" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2845,16 +2845,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>75277.91</v>
+        <v>75880.59</v>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2881,16 +2881,16 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>73209.18000000001</v>
+        <v>73921.96000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>71813.64</v>
+        <v>73883.89999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2953,22 +2953,22 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>70532.98</v>
+        <v>71049.12</v>
       </c>
       <c r="F72" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2989,10 +2989,10 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>67978.55</v>
+        <v>67893.81</v>
       </c>
       <c r="F73" t="n">
         <v>28</v>
@@ -3025,22 +3025,22 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>67847.98</v>
+        <v>67777.89999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3061,22 +3061,22 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>67777.89999999999</v>
+        <v>66127.91</v>
       </c>
       <c r="F75" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3097,16 +3097,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65223.71</v>
+        <v>65827.95</v>
       </c>
       <c r="F76" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3133,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>65072.03</v>
+        <v>65223.7</v>
       </c>
       <c r="F77" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3169,16 +3169,16 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>61593.19</v>
+        <v>64840.36</v>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3205,16 +3205,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>55451.64</v>
+        <v>61516.64999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3241,16 +3241,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>54804.05</v>
+        <v>58472.04</v>
       </c>
       <c r="F80" t="n">
-        <v>131</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>54770.41</v>
+        <v>57766.04</v>
       </c>
       <c r="F81" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="J81" t="n">
         <v>4</v>
@@ -3322,13 +3322,13 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>54327.64</v>
+        <v>54770.41</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53474.08</v>
+        <v>53535.41</v>
       </c>
       <c r="F83" t="n">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3385,16 +3385,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="J83" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53436.39999999999</v>
+        <v>52105.02</v>
       </c>
       <c r="F84" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3421,16 +3421,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>52938.08</v>
+        <v>50833.9</v>
       </c>
       <c r="F85" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3457,22 +3457,22 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>50720.33</v>
+        <v>49639.88</v>
       </c>
       <c r="F86" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3493,22 +3493,22 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>50264.36</v>
+        <v>49223.71</v>
       </c>
       <c r="F87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3529,16 +3529,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>47444.92</v>
+        <v>48777.94</v>
       </c>
       <c r="F88" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3565,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89">
@@ -3604,13 +3604,13 @@
         <v>8</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>45081.36</v>
+        <v>45960.23</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3637,16 +3637,16 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>43451.64</v>
+        <v>45818.50999999999</v>
       </c>
       <c r="F91" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3673,16 +3673,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="J91" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>41940.71999999999</v>
+        <v>45081.36</v>
       </c>
       <c r="F92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -3718,7 +3718,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>41640.73</v>
+        <v>41178.78</v>
       </c>
       <c r="F93" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3745,16 +3745,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3769,10 +3769,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>38981.36</v>
+        <v>40498.27</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3781,16 +3781,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3805,34 +3805,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>37791.21</v>
+        <v>35744.88</v>
       </c>
       <c r="F95" t="n">
+        <v>21</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>21</v>
+      </c>
+      <c r="J95" t="n">
         <v>6</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>6</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>37313.54</v>
+        <v>34985.56</v>
       </c>
       <c r="F96" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3853,16 +3853,16 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J96" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>36603.36</v>
+        <v>34955.56</v>
       </c>
       <c r="F97" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3889,16 +3889,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J97" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>36332.95</v>
+        <v>34323.77</v>
       </c>
       <c r="F98" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3925,16 +3925,16 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="J98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>33720.31</v>
+        <v>33467.84</v>
       </c>
       <c r="F99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3961,22 +3961,22 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3985,10 +3985,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>33111.86</v>
+        <v>33319.46</v>
       </c>
       <c r="F100" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>32884.8</v>
+        <v>32400.82</v>
       </c>
       <c r="F101" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4033,10 +4033,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="J101" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102">
@@ -4078,13 +4078,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>30834.72</v>
+        <v>31617.49</v>
       </c>
       <c r="F103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4105,16 +4105,16 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>27419.48</v>
+        <v>31248.3</v>
       </c>
       <c r="F104" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4141,16 +4141,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J104" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4165,10 +4165,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>27274.55</v>
+        <v>26058.22</v>
       </c>
       <c r="F105" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4177,10 +4177,10 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>25630.25</v>
+        <v>24914.89</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4213,16 +4213,16 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J106" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>23892.37</v>
+        <v>24487.97</v>
       </c>
       <c r="F107" t="n">
         <v>7</v>
@@ -4252,13 +4252,13 @@
         <v>7</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23255.11</v>
+        <v>23892.37</v>
       </c>
       <c r="F108" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4285,22 +4285,22 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>22829.65</v>
+        <v>22662.73</v>
       </c>
       <c r="F109" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4321,10 +4321,10 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110">
@@ -4357,16 +4357,16 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4381,10 +4381,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>22115.85</v>
+        <v>20560.16</v>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4393,22 +4393,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>21268.64</v>
+        <v>19905.91</v>
       </c>
       <c r="F112" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4429,16 +4429,16 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J112" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>21200.69</v>
+        <v>19825.44</v>
       </c>
       <c r="F113" t="n">
         <v>6</v>
@@ -4468,19 +4468,19 @@
         <v>6</v>
       </c>
       <c r="J113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21072.06</v>
+        <v>18594.05</v>
       </c>
       <c r="F114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4501,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J114" t="n">
         <v>2</v>
@@ -4510,13 +4510,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>19905.91</v>
+        <v>17795.76</v>
       </c>
       <c r="F115" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4537,22 +4537,22 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>19825.44</v>
+        <v>17752.53</v>
       </c>
       <c r="F116" t="n">
         <v>6</v>
@@ -4582,13 +4582,13 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>19680.49</v>
+        <v>16836.46</v>
       </c>
       <c r="F117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4609,16 +4609,16 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17795.76</v>
+        <v>15690.68</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -4654,13 +4654,13 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>17752.53</v>
+        <v>15591.52</v>
       </c>
       <c r="F119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4681,10 +4681,10 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>16942.4</v>
+        <v>14824.6</v>
       </c>
       <c r="F120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J120" t="n">
         <v>2</v>
@@ -4726,13 +4726,13 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>15690.68</v>
+        <v>14088.97</v>
       </c>
       <c r="F121" t="n">
+        <v>5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5</v>
+      </c>
+      <c r="J121" t="n">
         <v>4</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>4</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>15591.52</v>
+        <v>14066.1</v>
       </c>
       <c r="F122" t="n">
         <v>2</v>
@@ -4792,19 +4792,19 @@
         <v>2</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>15246.6</v>
+        <v>13894.91</v>
       </c>
       <c r="F123" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4825,16 +4825,16 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>13934.76</v>
+        <v>12160.18</v>
       </c>
       <c r="F124" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4861,22 +4861,22 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>13728.78</v>
+        <v>11860.15</v>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4897,16 +4897,16 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4921,28 +4921,28 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>12160.18</v>
+        <v>10967.78</v>
       </c>
       <c r="F126" t="n">
+        <v>8</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>8</v>
+      </c>
+      <c r="J126" t="n">
         <v>4</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>4</v>
-      </c>
-      <c r="J126" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>11407.62</v>
+        <v>10505.94</v>
       </c>
       <c r="F127" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4969,16 +4969,16 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4993,28 +4993,28 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>10505.94</v>
+        <v>10164.4</v>
       </c>
       <c r="F128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>6</v>
+      </c>
+      <c r="J128" t="n">
         <v>3</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>4</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>9835.77</v>
+        <v>9953.4</v>
       </c>
       <c r="F129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5041,22 +5041,22 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>9488.120000000001</v>
+        <v>9835.77</v>
       </c>
       <c r="F130" t="n">
         <v>4</v>
@@ -5077,16 +5077,16 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>9320.34</v>
+        <v>9121.18</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5113,16 +5113,16 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>7626.27</v>
+        <v>8641.530000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -5158,13 +5158,13 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6947.45</v>
+        <v>7626.27</v>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5185,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -5194,13 +5194,13 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6523.73</v>
+        <v>5416.58</v>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -5221,16 +5221,16 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5761.02</v>
+        <v>5197.46</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5257,22 +5257,22 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5416.58</v>
+        <v>4744.07</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5296,13 +5296,13 @@
         <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5197.46</v>
+        <v>3903.64</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5329,22 +5329,22 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5019.5</v>
+        <v>3219.49</v>
       </c>
       <c r="F138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5365,22 +5365,22 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3903.64</v>
+        <v>3007.63</v>
       </c>
       <c r="F139" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5401,22 +5401,22 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3007.63</v>
+        <v>2710.16</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5437,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5461,10 +5461,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2710.16</v>
+        <v>2477.97</v>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -5482,13 +5482,13 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2372.04</v>
+        <v>1863.56</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5512,13 +5512,13 @@
         <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -544,7 +544,7 @@
         <v>2532</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>591</v>
       </c>
       <c r="J9" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -1336,7 +1336,7 @@
         <v>430</v>
       </c>
       <c r="J26" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27">
@@ -2128,7 +2128,7 @@
         <v>118</v>
       </c>
       <c r="J48" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49">

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,57 +431,57 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[30/03/26 - 27/06/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[20/04/26 - 18/07/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Product Title</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Store Code</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Ordered Revenue</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Ordered Units</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Shipped Revenue</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Shipped COGS</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Shipped Units</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Customer Returns</t>
         </is>
@@ -493,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5977215.36</v>
+        <v>4555470.16</v>
       </c>
       <c r="F3" t="n">
-        <v>1465</v>
+        <v>1116</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -505,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1467</v>
+        <v>1113</v>
       </c>
       <c r="J3" t="n">
-        <v>362</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4">
@@ -529,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5744261.53</v>
+        <v>4091860.94</v>
       </c>
       <c r="F4" t="n">
-        <v>2548</v>
+        <v>1814</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -541,16 +553,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2532</v>
+        <v>1830</v>
       </c>
       <c r="J4" t="n">
-        <v>485</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -565,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2572028.31</v>
+        <v>2547355.1</v>
       </c>
       <c r="F5" t="n">
-        <v>339</v>
+        <v>413</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -577,16 +589,16 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>338</v>
+        <v>409</v>
       </c>
       <c r="J5" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -601,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2470895.85</v>
+        <v>2292037.54</v>
       </c>
       <c r="F6" t="n">
-        <v>412</v>
+        <v>303</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -613,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>407</v>
+        <v>301</v>
       </c>
       <c r="J6" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -637,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2154327.23</v>
+        <v>1807296.09</v>
       </c>
       <c r="F7" t="n">
-        <v>495</v>
+        <v>409</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -649,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>486</v>
+        <v>395</v>
       </c>
       <c r="J7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -673,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1521537.52</v>
+        <v>1360749.11</v>
       </c>
       <c r="F8" t="n">
-        <v>898</v>
+        <v>806</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -685,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>899</v>
+        <v>802</v>
       </c>
       <c r="J8" t="n">
-        <v>171</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
@@ -709,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1392965.12</v>
+        <v>1265157.62</v>
       </c>
       <c r="F9" t="n">
-        <v>593</v>
+        <v>538</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -721,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>591</v>
+        <v>544</v>
       </c>
       <c r="J9" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -745,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>900742.99</v>
+        <v>802450.49</v>
       </c>
       <c r="F10" t="n">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -757,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="J10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -781,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>871429.8100000001</v>
+        <v>656173.03</v>
       </c>
       <c r="F11" t="n">
-        <v>297</v>
+        <v>123</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -793,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>298</v>
+        <v>122</v>
       </c>
       <c r="J11" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -817,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>689420.78</v>
+        <v>628936.6900000001</v>
       </c>
       <c r="F12" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -829,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="J12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -853,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>654878.78</v>
+        <v>558281.39</v>
       </c>
       <c r="F13" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -865,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="J13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -889,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>608244.09</v>
+        <v>547790.58</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>413</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -901,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>72</v>
+        <v>401</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -925,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>577651.5</v>
+        <v>536567.5</v>
       </c>
       <c r="F15" t="n">
-        <v>429</v>
+        <v>185</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -937,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>429</v>
+        <v>184</v>
       </c>
       <c r="J15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -961,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>545822.67</v>
+        <v>498594.02</v>
       </c>
       <c r="F16" t="n">
-        <v>402</v>
+        <v>59</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -973,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>398</v>
+        <v>61</v>
       </c>
       <c r="J16" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -997,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>489015.31</v>
+        <v>440181.6</v>
       </c>
       <c r="F17" t="n">
-        <v>188</v>
+        <v>320</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1009,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>190</v>
+        <v>321</v>
       </c>
       <c r="J17" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1033,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>483829.77</v>
+        <v>329508.12</v>
       </c>
       <c r="F18" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1045,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J18" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1069,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>428776.86</v>
+        <v>320838.28</v>
       </c>
       <c r="F19" t="n">
-        <v>204</v>
+        <v>123</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1081,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="J19" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1105,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>427391.64</v>
+        <v>313881.51</v>
       </c>
       <c r="F20" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1117,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1141,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>388055.57</v>
+        <v>267102.58</v>
       </c>
       <c r="F21" t="n">
-        <v>198</v>
+        <v>541</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1153,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>198</v>
+        <v>545</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1177,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>338264.3</v>
+        <v>266250.7</v>
       </c>
       <c r="F22" t="n">
-        <v>709</v>
+        <v>201</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1189,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>707</v>
+        <v>199</v>
       </c>
       <c r="J22" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1213,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>337409.94</v>
+        <v>261657.77</v>
       </c>
       <c r="F23" t="n">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1225,16 +1237,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="J23" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1249,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>333504.85</v>
+        <v>242033.32</v>
       </c>
       <c r="F24" t="n">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1261,22 +1273,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>255</v>
+        <v>118</v>
       </c>
       <c r="J24" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1285,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>255175.28</v>
+        <v>239233.62</v>
       </c>
       <c r="F25" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1297,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="J25" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1321,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>239845.73</v>
+        <v>236826.31</v>
       </c>
       <c r="F26" t="n">
-        <v>432</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1333,22 +1345,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>430</v>
+        <v>43</v>
       </c>
       <c r="J26" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1357,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>236897.39</v>
+        <v>222638.16</v>
       </c>
       <c r="F27" t="n">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1369,22 +1381,22 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="J27" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1393,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228961.1</v>
+        <v>216158.49</v>
       </c>
       <c r="F28" t="n">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1405,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1429,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>225201.53</v>
+        <v>210225.99</v>
       </c>
       <c r="F29" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1441,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="J29" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1465,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>214822.32</v>
+        <v>201146.61</v>
       </c>
       <c r="F30" t="n">
-        <v>102</v>
+        <v>368</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1477,22 +1489,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="J30" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1501,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>212015.07</v>
+        <v>197527.27</v>
       </c>
       <c r="F31" t="n">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1513,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>195</v>
+        <v>75</v>
       </c>
       <c r="J31" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1537,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>206333.91</v>
+        <v>194187.97</v>
       </c>
       <c r="F32" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1549,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="J32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1573,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>201643.96</v>
+        <v>183638.82</v>
       </c>
       <c r="F33" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1585,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1609,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>192749.33</v>
+        <v>183497.53</v>
       </c>
       <c r="F34" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1621,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="J34" t="n">
         <v>26</v>
@@ -1630,7 +1642,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1645,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>190470.31</v>
+        <v>181575.71</v>
       </c>
       <c r="F35" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1657,16 +1669,16 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="J35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1681,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>168818.66</v>
+        <v>169374.54</v>
       </c>
       <c r="F36" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1693,16 +1705,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="J36" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1717,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>166837.25</v>
+        <v>167832.84</v>
       </c>
       <c r="F37" t="n">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1729,22 +1741,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>161</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1753,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>162989.71</v>
+        <v>165749.84</v>
       </c>
       <c r="F38" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1765,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1789,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>158397.64</v>
+        <v>155765.08</v>
       </c>
       <c r="F39" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1801,22 +1813,22 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="J39" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1825,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>155962.72</v>
+        <v>155328.84</v>
       </c>
       <c r="F40" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1837,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1861,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>154649.91</v>
+        <v>153073.42</v>
       </c>
       <c r="F41" t="n">
-        <v>39</v>
+        <v>136</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1873,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1897,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>153956.86</v>
+        <v>150159.81</v>
       </c>
       <c r="F42" t="n">
-        <v>29</v>
+        <v>323</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1909,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="J42" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1933,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>150522.14</v>
+        <v>135973.53</v>
       </c>
       <c r="F43" t="n">
-        <v>326</v>
+        <v>51</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1945,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>322</v>
+        <v>50</v>
       </c>
       <c r="J43" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1969,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>149749.83</v>
+        <v>135144.88</v>
       </c>
       <c r="F44" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1981,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2005,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>149637.3</v>
+        <v>133671.09</v>
       </c>
       <c r="F45" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2017,16 +2029,16 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2041,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>147046.11</v>
+        <v>132994.09</v>
       </c>
       <c r="F46" t="n">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2053,16 +2065,16 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="J46" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2077,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>142739</v>
+        <v>128788.79</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2089,22 +2101,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="J47" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2113,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>139500.79</v>
+        <v>120127.98</v>
       </c>
       <c r="F48" t="n">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2125,16 +2137,16 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="J48" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2149,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>132107.61</v>
+        <v>119133.37</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2161,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2185,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>129073.32</v>
+        <v>113401.66</v>
       </c>
       <c r="F50" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2197,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
         <v>10</v>
@@ -2206,13 +2218,13 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2221,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>128083.01</v>
+        <v>111497.36</v>
       </c>
       <c r="F51" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2233,22 +2245,22 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="J51" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2257,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>127369.42</v>
+        <v>108967.53</v>
       </c>
       <c r="F52" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2269,22 +2281,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2293,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>126822.13</v>
+        <v>104949.97</v>
       </c>
       <c r="F53" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2305,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2329,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>125894.04</v>
+        <v>104083.82</v>
       </c>
       <c r="F54" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2341,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2365,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>120713.63</v>
+        <v>97593.89999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2377,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
         <v>4</v>
@@ -2386,7 +2398,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2401,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>119641.32</v>
+        <v>94386.47</v>
       </c>
       <c r="F56" t="n">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2413,16 +2425,16 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2437,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>104830.47</v>
+        <v>89614.39</v>
       </c>
       <c r="F57" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2449,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="J57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2473,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100838.9</v>
+        <v>84535.95</v>
       </c>
       <c r="F58" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2485,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>98427.96000000001</v>
+        <v>81702.5</v>
       </c>
       <c r="F59" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2521,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -2545,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>98299.98000000001</v>
+        <v>81266.92999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2557,22 +2569,22 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2581,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>95316.03999999999</v>
+        <v>81197.39999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2593,16 +2605,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2617,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>89637.25999999999</v>
+        <v>71679.60000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2629,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2653,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>89483.89999999999</v>
+        <v>71679.59999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2665,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2689,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>88490.64999999999</v>
+        <v>70211.84</v>
       </c>
       <c r="F64" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2701,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2725,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>82857.68000000001</v>
+        <v>69570.35000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2737,22 +2749,22 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="J65" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2761,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>82219.39999999999</v>
+        <v>65530.44</v>
       </c>
       <c r="F66" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2773,16 +2785,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2797,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>80315.26000000001</v>
+        <v>62847.37</v>
       </c>
       <c r="F67" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2809,22 +2821,22 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2833,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>76937.06</v>
+        <v>60821.19</v>
       </c>
       <c r="F68" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2845,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2869,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>75880.59</v>
+        <v>58387.29</v>
       </c>
       <c r="F69" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2881,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2905,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>73921.96000000001</v>
+        <v>57188.93</v>
       </c>
       <c r="F70" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2917,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2941,7 +2953,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>73883.89999999999</v>
+        <v>55197.4</v>
       </c>
       <c r="F71" t="n">
         <v>17</v>
@@ -2956,19 +2968,19 @@
         <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2977,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>71049.12</v>
+        <v>54240.7</v>
       </c>
       <c r="F72" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2989,16 +3001,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3013,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>67893.81</v>
+        <v>53333.91</v>
       </c>
       <c r="F73" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3025,22 +3037,22 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3049,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>67777.89999999999</v>
+        <v>53142.41</v>
       </c>
       <c r="F74" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3061,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3085,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>66127.91</v>
+        <v>50226.24</v>
       </c>
       <c r="F75" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3097,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3121,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65827.95</v>
+        <v>47258.34</v>
       </c>
       <c r="F76" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3133,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J76" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3157,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>65223.7</v>
+        <v>45667.77</v>
       </c>
       <c r="F77" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3169,16 +3181,16 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3193,10 +3205,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>64840.36</v>
+        <v>44389.78</v>
       </c>
       <c r="F78" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3205,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3229,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>61516.64999999999</v>
+        <v>44045.73</v>
       </c>
       <c r="F79" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3241,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3265,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>58472.04</v>
+        <v>43016.13</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3277,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3301,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>57766.04</v>
+        <v>42145.73</v>
       </c>
       <c r="F81" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3313,22 +3325,22 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3337,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>54770.41</v>
+        <v>40887.3</v>
       </c>
       <c r="F82" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3349,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="J82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3373,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53535.41</v>
+        <v>39811.87</v>
       </c>
       <c r="F83" t="n">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3385,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3409,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>52105.02</v>
+        <v>38833.11</v>
       </c>
       <c r="F84" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3421,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3445,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>50833.9</v>
+        <v>36603.36</v>
       </c>
       <c r="F85" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3457,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3481,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>49639.88</v>
+        <v>36475.4</v>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3493,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J86" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3517,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>49223.71</v>
+        <v>35617.55</v>
       </c>
       <c r="F87" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3529,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3553,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>48777.94</v>
+        <v>35332.1</v>
       </c>
       <c r="F88" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3565,16 +3577,16 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="J88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3589,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>47027.14999999999</v>
+        <v>33871.16</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3601,16 +3613,16 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3625,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>45960.23</v>
+        <v>33558.45</v>
       </c>
       <c r="F90" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3637,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J90" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3661,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>45818.50999999999</v>
+        <v>33545.82</v>
       </c>
       <c r="F91" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3673,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J91" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3697,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>45081.36</v>
+        <v>31902.57</v>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3709,22 +3721,22 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3733,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>41178.78</v>
+        <v>31891.48</v>
       </c>
       <c r="F93" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3745,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3769,10 +3781,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>40498.27</v>
+        <v>30161.02</v>
       </c>
       <c r="F94" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3781,16 +3793,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3805,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>35744.88</v>
+        <v>29532.51</v>
       </c>
       <c r="F95" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3817,22 +3829,22 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J95" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3841,10 +3853,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>34985.56</v>
+        <v>28047.45</v>
       </c>
       <c r="F96" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3853,16 +3865,16 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>34955.56</v>
+        <v>27739.81</v>
       </c>
       <c r="F97" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3889,16 +3901,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3913,10 +3925,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>34323.77</v>
+        <v>23641.52</v>
       </c>
       <c r="F98" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3925,16 +3937,16 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3949,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>33467.84</v>
+        <v>22029.67</v>
       </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3961,22 +3973,22 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3985,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>33319.46</v>
+        <v>21938.12</v>
       </c>
       <c r="F100" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3997,22 +4009,22 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J100" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4021,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>32400.82</v>
+        <v>20606.75</v>
       </c>
       <c r="F101" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4033,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J101" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4057,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>31772.87</v>
+        <v>20545.52</v>
       </c>
       <c r="F102" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4069,22 +4081,22 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4093,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>31617.49</v>
+        <v>20330.51</v>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4105,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4129,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>31248.3</v>
+        <v>20206.76</v>
       </c>
       <c r="F104" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4141,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4165,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26058.22</v>
+        <v>18550.01</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4177,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4201,10 +4213,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>24914.89</v>
+        <v>17962.71</v>
       </c>
       <c r="F106" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4213,16 +4225,16 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4237,10 +4249,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>24487.97</v>
+        <v>17795.76</v>
       </c>
       <c r="F107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4249,10 +4261,10 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -4273,10 +4285,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23892.37</v>
+        <v>16944.9</v>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4285,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J108" t="n">
         <v>2</v>
@@ -4294,7 +4306,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4309,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>22662.73</v>
+        <v>16604.26</v>
       </c>
       <c r="F109" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4321,22 +4333,22 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4345,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>22488.11</v>
+        <v>16477.1</v>
       </c>
       <c r="F110" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4357,16 +4369,16 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4381,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>20560.16</v>
+        <v>16160.15</v>
       </c>
       <c r="F111" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4393,22 +4405,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4417,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>19905.91</v>
+        <v>15581.39</v>
       </c>
       <c r="F112" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4429,16 +4441,16 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4453,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>19825.44</v>
+        <v>13506.78</v>
       </c>
       <c r="F113" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4465,22 +4477,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4489,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>18594.05</v>
+        <v>13216.96</v>
       </c>
       <c r="F114" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4501,22 +4513,22 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4525,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>17795.76</v>
+        <v>12605.1</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4537,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -4546,13 +4558,13 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>17752.53</v>
+        <v>12103.42</v>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4573,16 +4585,16 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4597,7 +4609,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>16836.46</v>
+        <v>12096.29</v>
       </c>
       <c r="F117" t="n">
         <v>8</v>
@@ -4609,16 +4621,16 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4633,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>15690.68</v>
+        <v>11355.08</v>
       </c>
       <c r="F118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4645,16 +4657,16 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4669,7 +4681,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>15591.52</v>
+        <v>9597.459999999999</v>
       </c>
       <c r="F119" t="n">
         <v>2</v>
@@ -4684,19 +4696,19 @@
         <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4705,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>14824.6</v>
+        <v>8641.530000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4717,22 +4729,22 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4741,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>14088.97</v>
+        <v>7626.27</v>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4753,22 +4765,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4777,7 +4789,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>14066.1</v>
+        <v>6862.71</v>
       </c>
       <c r="F122" t="n">
         <v>2</v>
@@ -4792,19 +4804,19 @@
         <v>2</v>
       </c>
       <c r="J122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4813,10 +4825,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>13894.91</v>
+        <v>6778.81</v>
       </c>
       <c r="F123" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4825,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -4834,7 +4846,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4849,10 +4861,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>12160.18</v>
+        <v>6775.4</v>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4861,16 +4873,16 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4885,10 +4897,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>11860.15</v>
+        <v>6438.98</v>
       </c>
       <c r="F125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4897,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>1</v>
@@ -4906,7 +4918,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4921,10 +4933,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>10967.78</v>
+        <v>6184.75</v>
       </c>
       <c r="F126" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4933,16 +4945,16 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4957,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>10505.94</v>
+        <v>6104.5</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4969,16 +4981,16 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4993,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>10164.4</v>
+        <v>5716.1</v>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5005,22 +5017,22 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5029,10 +5041,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>9953.4</v>
+        <v>5591.52</v>
       </c>
       <c r="F129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5041,16 +5053,16 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5065,10 +5077,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>9835.77</v>
+        <v>5590.68</v>
       </c>
       <c r="F130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5077,16 +5089,16 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5101,10 +5113,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>9121.18</v>
+        <v>5507.63</v>
       </c>
       <c r="F131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5113,16 +5125,16 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5137,34 +5149,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>8641.530000000001</v>
+        <v>5377.95</v>
       </c>
       <c r="F132" t="n">
+        <v>4</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>4</v>
+      </c>
+      <c r="J132" t="n">
         <v>3</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>3</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5173,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>7626.27</v>
+        <v>4744.07</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5185,22 +5197,22 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5209,10 +5221,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5416.58</v>
+        <v>4744.06</v>
       </c>
       <c r="F134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -5221,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -5230,7 +5242,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5245,10 +5257,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5197.46</v>
+        <v>3929.65</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5257,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
         <v>1</v>
@@ -5266,13 +5278,13 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5281,7 +5293,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4744.07</v>
+        <v>3727.12</v>
       </c>
       <c r="F136" t="n">
         <v>2</v>
@@ -5293,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>1</v>
@@ -5302,7 +5314,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5317,10 +5329,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3903.64</v>
+        <v>3388.98</v>
       </c>
       <c r="F137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5329,22 +5341,22 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5353,10 +5365,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3219.49</v>
+        <v>3388.14</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5365,22 +5377,22 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5389,10 +5401,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3007.63</v>
+        <v>3388.12</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5401,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -5410,7 +5422,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5425,10 +5437,10 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2710.16</v>
+        <v>2477.97</v>
       </c>
       <c r="F140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5437,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -5446,7 +5458,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5461,7 +5473,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2477.97</v>
+        <v>1863.56</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -5482,7 +5494,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5497,7 +5509,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1863.56</v>
+        <v>1694.07</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5518,7 +5530,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5533,10 +5545,10 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1863.56</v>
+        <v>1618.05</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -5545,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -5554,13 +5566,13 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5569,10 +5581,10 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5581,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -5590,7 +5602,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5605,34 +5617,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1355.08</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
         <v>1</v>
-      </c>
-      <c r="G145" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0C8JDHLX9</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5641,10 +5653,10 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>464.02</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -5653,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -5662,13 +5674,13 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5698,7 +5710,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0BRKDLXCD</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5713,10 +5725,10 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>-6947.46</v>
+        <v>-3007.63</v>
       </c>
       <c r="F148" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[20/04/26 - 18/07/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[27/04/26 - 25/07/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4555470.16</v>
+        <v>6251827.27</v>
       </c>
       <c r="F3" t="n">
-        <v>1116</v>
+        <v>1535</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1113</v>
+        <v>1532</v>
       </c>
       <c r="J3" t="n">
-        <v>241</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4091860.94</v>
+        <v>5697993.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1814</v>
+        <v>2530</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1830</v>
+        <v>2522</v>
       </c>
       <c r="J4" t="n">
-        <v>366</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2547355.1</v>
+        <v>3489136.68</v>
       </c>
       <c r="F5" t="n">
-        <v>413</v>
+        <v>574</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>409</v>
+        <v>568</v>
       </c>
       <c r="J5" t="n">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2292037.54</v>
+        <v>3139993.48</v>
       </c>
       <c r="F6" t="n">
-        <v>303</v>
+        <v>417</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>301</v>
+        <v>418</v>
       </c>
       <c r="J6" t="n">
-        <v>68</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1807296.09</v>
+        <v>2531146.73</v>
       </c>
       <c r="F7" t="n">
-        <v>409</v>
+        <v>574</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>395</v>
+        <v>558</v>
       </c>
       <c r="J7" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1360749.11</v>
+        <v>1857238.71</v>
       </c>
       <c r="F8" t="n">
-        <v>806</v>
+        <v>1099</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>802</v>
+        <v>1088</v>
       </c>
       <c r="J8" t="n">
-        <v>136</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1265157.62</v>
+        <v>1678334.61</v>
       </c>
       <c r="F9" t="n">
-        <v>538</v>
+        <v>714</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>544</v>
+        <v>708</v>
       </c>
       <c r="J9" t="n">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>802450.49</v>
+        <v>1119691.38</v>
       </c>
       <c r="F10" t="n">
-        <v>253</v>
+        <v>355</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>251</v>
+        <v>356</v>
       </c>
       <c r="J10" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>656173.03</v>
+        <v>857156.2000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>628936.6900000001</v>
+        <v>832758.6900000001</v>
       </c>
       <c r="F12" t="n">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="J12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>558281.39</v>
+        <v>806123.73</v>
       </c>
       <c r="F13" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="J13" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>547790.58</v>
+        <v>796416.47</v>
       </c>
       <c r="F14" t="n">
-        <v>413</v>
+        <v>273</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>401</v>
+        <v>271</v>
       </c>
       <c r="J14" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>536567.5</v>
+        <v>754788.27</v>
       </c>
       <c r="F15" t="n">
-        <v>185</v>
+        <v>568</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>184</v>
+        <v>568</v>
       </c>
       <c r="J15" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498594.02</v>
+        <v>682812.71</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>440181.6</v>
+        <v>603663.72</v>
       </c>
       <c r="F17" t="n">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>321</v>
+        <v>433</v>
       </c>
       <c r="J17" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>329508.12</v>
+        <v>469893.33</v>
       </c>
       <c r="F18" t="n">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="J18" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>320838.28</v>
+        <v>459912</v>
       </c>
       <c r="F19" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="J19" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>313881.51</v>
+        <v>453381.14</v>
       </c>
       <c r="F20" t="n">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>97</v>
+        <v>218</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>267102.58</v>
+        <v>386126.62</v>
       </c>
       <c r="F21" t="n">
-        <v>541</v>
+        <v>797</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>545</v>
+        <v>794</v>
       </c>
       <c r="J21" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>266250.7</v>
+        <v>369111.16</v>
       </c>
       <c r="F22" t="n">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,22 +1201,22 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J22" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>261657.77</v>
+        <v>364696.18</v>
       </c>
       <c r="F23" t="n">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,22 +1237,22 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>173</v>
+        <v>278</v>
       </c>
       <c r="J23" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>242033.32</v>
+        <v>338849.1</v>
       </c>
       <c r="F24" t="n">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,22 +1273,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="J24" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>239233.62</v>
+        <v>310128.9</v>
       </c>
       <c r="F25" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>236826.31</v>
+        <v>309411.96</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222638.16</v>
+        <v>294720.94</v>
       </c>
       <c r="F27" t="n">
         <v>130</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>216158.49</v>
+        <v>285845.74</v>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>523</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,22 +1417,22 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>521</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>210225.99</v>
+        <v>285712.83</v>
       </c>
       <c r="F29" t="n">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="J29" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>201146.61</v>
+        <v>276660.02</v>
       </c>
       <c r="F30" t="n">
-        <v>368</v>
+        <v>101</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,22 +1489,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>363</v>
+        <v>102</v>
       </c>
       <c r="J30" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>197527.27</v>
+        <v>273488.83</v>
       </c>
       <c r="F31" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>194187.97</v>
+        <v>270389.85</v>
       </c>
       <c r="F32" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>183638.82</v>
+        <v>254105.68</v>
       </c>
       <c r="F33" t="n">
-        <v>66</v>
+        <v>245</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="J33" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>183497.53</v>
+        <v>229624.32</v>
       </c>
       <c r="F34" t="n">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="J34" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>181575.71</v>
+        <v>226974.03</v>
       </c>
       <c r="F35" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,22 +1669,22 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="J35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>169374.54</v>
+        <v>220146.78</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,10 +1705,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="J36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>167832.84</v>
+        <v>219395.46</v>
       </c>
       <c r="F37" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>165749.84</v>
+        <v>210483.53</v>
       </c>
       <c r="F38" t="n">
-        <v>16</v>
+        <v>455</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>449</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>155765.08</v>
+        <v>207678.83</v>
       </c>
       <c r="F39" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,16 +1813,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="J39" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>155328.84</v>
+        <v>205105.57</v>
       </c>
       <c r="F40" t="n">
-        <v>50</v>
+        <v>185</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>153073.42</v>
+        <v>199512.45</v>
       </c>
       <c r="F41" t="n">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="J41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150159.81</v>
+        <v>194623.69</v>
       </c>
       <c r="F42" t="n">
-        <v>323</v>
+        <v>46</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>322</v>
+        <v>48</v>
       </c>
       <c r="J42" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>135973.53</v>
+        <v>191762.52</v>
       </c>
       <c r="F43" t="n">
-        <v>51</v>
+        <v>192</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>193</v>
       </c>
       <c r="J43" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>135144.88</v>
+        <v>185635.55</v>
       </c>
       <c r="F44" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J44" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>133671.09</v>
+        <v>185409.16</v>
       </c>
       <c r="F45" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>132994.09</v>
+        <v>185107.65</v>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
         <v>9</v>
@@ -2074,13 +2074,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>128788.79</v>
+        <v>180276.28</v>
       </c>
       <c r="F47" t="n">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,22 +2101,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="J47" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>120127.98</v>
+        <v>175302.81</v>
       </c>
       <c r="F48" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,16 +2137,16 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="J48" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>119133.37</v>
+        <v>171656.72</v>
       </c>
       <c r="F49" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="J49" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>113401.66</v>
+        <v>168833.07</v>
       </c>
       <c r="F50" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="J50" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>111497.36</v>
+        <v>168281.13</v>
       </c>
       <c r="F51" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>108967.53</v>
+        <v>167864.34</v>
       </c>
       <c r="F52" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>104949.97</v>
+        <v>164062.6</v>
       </c>
       <c r="F53" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="J53" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>104083.82</v>
+        <v>151021.08</v>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="J54" t="n">
         <v>3</v>
@@ -2362,7 +2362,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>97593.89999999999</v>
+        <v>146832.96</v>
       </c>
       <c r="F55" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,22 +2389,22 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>94386.47</v>
+        <v>131342.31</v>
       </c>
       <c r="F56" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,16 +2425,16 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="J56" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2449,22 +2449,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>89614.39</v>
+        <v>122267.03</v>
       </c>
       <c r="F57" t="n">
+        <v>23</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>23</v>
+      </c>
+      <c r="J57" t="n">
         <v>9</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>84535.95</v>
+        <v>118133.99</v>
       </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>81702.5</v>
+        <v>117514.43</v>
       </c>
       <c r="F59" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>81266.92999999999</v>
+        <v>113691.36</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,22 +2569,22 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>81197.39999999999</v>
+        <v>112949.12</v>
       </c>
       <c r="F61" t="n">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,16 +2605,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c r="J61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>71679.60000000001</v>
+        <v>110674.54</v>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>71679.59999999999</v>
+        <v>102747.46</v>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>70211.84</v>
+        <v>102737.94</v>
       </c>
       <c r="F64" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>69570.35000000001</v>
+        <v>97622.00999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,22 +2749,22 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>65530.44</v>
+        <v>95316.03999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,22 +2785,22 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>62847.37</v>
+        <v>93516.10000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,22 +2821,22 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J67" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>60821.19</v>
+        <v>91001.66</v>
       </c>
       <c r="F68" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J68" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>58387.29</v>
+        <v>89614.39</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>57188.93</v>
+        <v>89595.67</v>
       </c>
       <c r="F70" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>55197.4</v>
+        <v>89229.67</v>
       </c>
       <c r="F71" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>54240.7</v>
+        <v>87010.08</v>
       </c>
       <c r="F72" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53333.91</v>
+        <v>79794.03</v>
       </c>
       <c r="F73" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53142.41</v>
+        <v>79145.72</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>50226.24</v>
+        <v>77877.97</v>
       </c>
       <c r="F75" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>47258.34</v>
+        <v>74753.44</v>
       </c>
       <c r="F76" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="J76" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>45667.77</v>
+        <v>69477.98</v>
       </c>
       <c r="F77" t="n">
         <v>16</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
         <v>4</v>
@@ -3190,7 +3190,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>44389.78</v>
+        <v>67822.85000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3217,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>44045.73</v>
+        <v>64898.24000000001</v>
       </c>
       <c r="F79" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,28 +3277,28 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>43016.13</v>
+        <v>60006.73</v>
       </c>
       <c r="F80" t="n">
+        <v>84</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>84</v>
+      </c>
+      <c r="J80" t="n">
         <v>11</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>10</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>42145.73</v>
+        <v>59905.05</v>
       </c>
       <c r="F81" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
         <v>3</v>
@@ -3334,7 +3334,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>40887.3</v>
+        <v>59505.92</v>
       </c>
       <c r="F82" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J82" t="n">
         <v>7</v>
@@ -3370,7 +3370,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>39811.87</v>
+        <v>58073.69</v>
       </c>
       <c r="F83" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>38833.11</v>
+        <v>57844.77</v>
       </c>
       <c r="F84" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J84" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>36603.36</v>
+        <v>56305.75</v>
       </c>
       <c r="F85" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>36475.4</v>
+        <v>54285.65</v>
       </c>
       <c r="F86" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>35617.55</v>
+        <v>53883.05</v>
       </c>
       <c r="F87" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>35332.1</v>
+        <v>52193.18</v>
       </c>
       <c r="F88" t="n">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,22 +3577,22 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33871.16</v>
+        <v>52183.97</v>
       </c>
       <c r="F89" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,16 +3613,16 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>33558.45</v>
+        <v>50267.03</v>
       </c>
       <c r="F90" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>33545.82</v>
+        <v>47433.86</v>
       </c>
       <c r="F91" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>31902.57</v>
+        <v>47252.57</v>
       </c>
       <c r="F92" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,22 +3721,22 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J92" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>31891.48</v>
+        <v>46039.82</v>
       </c>
       <c r="F93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>30161.02</v>
+        <v>45754.2</v>
       </c>
       <c r="F94" t="n">
         <v>10</v>
@@ -3796,13 +3796,13 @@
         <v>10</v>
       </c>
       <c r="J94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>29532.51</v>
+        <v>43797.49</v>
       </c>
       <c r="F95" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,22 +3829,22 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>28047.45</v>
+        <v>43359.28</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>27739.81</v>
+        <v>41124.52</v>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,16 +3901,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3925,28 +3925,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>23641.52</v>
+        <v>39764.39</v>
       </c>
       <c r="F98" t="n">
+        <v>22</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>21</v>
+      </c>
+      <c r="J98" t="n">
         <v>3</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>22029.67</v>
+        <v>39738.17</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>21938.12</v>
+        <v>35617.55</v>
       </c>
       <c r="F100" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J100" t="n">
         <v>3</v>
@@ -4018,13 +4018,13 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>20606.75</v>
+        <v>34502.55</v>
       </c>
       <c r="F101" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>20545.52</v>
+        <v>31617.49</v>
       </c>
       <c r="F102" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>20330.51</v>
+        <v>30687.27</v>
       </c>
       <c r="F103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J103" t="n">
         <v>1</v>
@@ -4126,13 +4126,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>20206.76</v>
+        <v>30500.83</v>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>18550.01</v>
+        <v>28417.51</v>
       </c>
       <c r="F105" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>17962.71</v>
+        <v>28047.45</v>
       </c>
       <c r="F106" t="n">
         <v>4</v>
@@ -4228,19 +4228,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4249,28 +4249,28 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>17795.76</v>
+        <v>26344.92</v>
       </c>
       <c r="F107" t="n">
+        <v>13</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>13</v>
+      </c>
+      <c r="J107" t="n">
         <v>1</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4285,28 +4285,28 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>16944.9</v>
+        <v>24754.77</v>
       </c>
       <c r="F108" t="n">
+        <v>17</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>18</v>
+      </c>
+      <c r="J108" t="n">
         <v>5</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>5</v>
-      </c>
-      <c r="J108" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>16604.26</v>
+        <v>23641.52</v>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,10 +4333,10 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>16477.1</v>
+        <v>23593.19</v>
       </c>
       <c r="F110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>16160.15</v>
+        <v>22877.98</v>
       </c>
       <c r="F111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,16 +4405,16 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>15581.39</v>
+        <v>22452.54</v>
       </c>
       <c r="F112" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J112" t="n">
         <v>1</v>
@@ -4450,7 +4450,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13506.78</v>
+        <v>20736.48</v>
       </c>
       <c r="F113" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="J113" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>13216.96</v>
+        <v>19825.44</v>
       </c>
       <c r="F114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" t="n">
         <v>1</v>
@@ -4522,13 +4522,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>12605.1</v>
+        <v>19336.42</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,16 +4549,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>12103.42</v>
+        <v>19222.88</v>
       </c>
       <c r="F116" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,22 +4585,22 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J116" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>12096.29</v>
+        <v>18958.5</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>11355.08</v>
+        <v>18148.34</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
         <v>1</v>
@@ -4666,7 +4666,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>9597.459999999999</v>
+        <v>17795.76</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>8641.530000000001</v>
+        <v>14729.66</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>7626.27</v>
+        <v>14088.97</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,22 +4765,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6862.71</v>
+        <v>13557.62</v>
       </c>
       <c r="F122" t="n">
         <v>2</v>
@@ -4810,7 +4810,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6778.81</v>
+        <v>11694.07</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -4846,7 +4846,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6775.4</v>
+        <v>11522.03</v>
       </c>
       <c r="F124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -4882,13 +4882,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6438.98</v>
+        <v>9597.459999999999</v>
       </c>
       <c r="F125" t="n">
         <v>2</v>
@@ -4918,7 +4918,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6184.75</v>
+        <v>9519.469999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4945,16 +4945,16 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6104.5</v>
+        <v>9025.43</v>
       </c>
       <c r="F127" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4981,16 +4981,16 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5716.1</v>
+        <v>7628.22</v>
       </c>
       <c r="F128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J128" t="n">
         <v>2</v>
@@ -5026,13 +5026,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5591.52</v>
+        <v>7626.27</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5062,13 +5062,13 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5590.68</v>
+        <v>7116.110000000001</v>
       </c>
       <c r="F130" t="n">
         <v>3</v>
@@ -5089,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5113,28 +5113,28 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5507.63</v>
+        <v>6862.71</v>
       </c>
       <c r="F131" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>2</v>
+      </c>
+      <c r="J131" t="n">
         <v>1</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0BLKF46QG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5377.95</v>
+        <v>6834.74</v>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5161,22 +5161,22 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4744.07</v>
+        <v>6775.4</v>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5197,16 +5197,16 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4744.06</v>
+        <v>6438.98</v>
       </c>
       <c r="F134" t="n">
         <v>2</v>
@@ -5236,13 +5236,13 @@
         <v>2</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3929.65</v>
+        <v>5590.68</v>
       </c>
       <c r="F135" t="n">
         <v>3</v>
@@ -5269,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3727.12</v>
+        <v>5590.68</v>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3388.98</v>
+        <v>5416.58</v>
       </c>
       <c r="F137" t="n">
         <v>1</v>
@@ -5350,7 +5350,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5365,34 +5365,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3388.14</v>
+        <v>5082.19</v>
       </c>
       <c r="F138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>3</v>
+      </c>
+      <c r="J138" t="n">
         <v>2</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>2</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3388.12</v>
+        <v>4744.06</v>
       </c>
       <c r="F139" t="n">
         <v>2</v>
@@ -5422,7 +5422,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5437,28 +5437,28 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2477.97</v>
+        <v>3929.65</v>
       </c>
       <c r="F140" t="n">
+        <v>3</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>3</v>
+      </c>
+      <c r="J140" t="n">
         <v>1</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1863.56</v>
+        <v>3388.98</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1694.07</v>
+        <v>3388.14</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -5530,13 +5530,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1618.05</v>
+        <v>3007.63</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -5566,13 +5566,13 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>2477.97</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>2011.86</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>1</v>
@@ -5638,13 +5638,13 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1990.68</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -5665,16 +5665,16 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1863.56</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -5710,36 +5710,216 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1694.07</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>B0GW8VBCBL</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>1618.05</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>B0BLKCSJ7Z</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1016.1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>B0BLK8DNPD</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>464.02</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>B0C8JDHLX9</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
           <t>Tonor</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>-3007.63</v>
-      </c>
-      <c r="F148" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[27/04/26 - 25/07/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[04/05/26 - 01/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6251827.27</v>
+        <v>6159861.03</v>
       </c>
       <c r="F3" t="n">
-        <v>1535</v>
+        <v>1515</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1532</v>
+        <v>1515</v>
       </c>
       <c r="J3" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5697993.33</v>
+        <v>5659283.41</v>
       </c>
       <c r="F4" t="n">
-        <v>2530</v>
+        <v>2514</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2522</v>
+        <v>2502</v>
       </c>
       <c r="J4" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3489136.68</v>
+        <v>3557222.3</v>
       </c>
       <c r="F5" t="n">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J5" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3139993.48</v>
+        <v>3139993.39</v>
       </c>
       <c r="F6" t="n">
         <v>417</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="J6" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2531146.73</v>
+        <v>2693021.16</v>
       </c>
       <c r="F7" t="n">
-        <v>574</v>
+        <v>608</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>558</v>
+        <v>592</v>
       </c>
       <c r="J7" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1857238.71</v>
+        <v>1850462.39</v>
       </c>
       <c r="F8" t="n">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="J8" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1678334.61</v>
+        <v>1801775.32</v>
       </c>
       <c r="F9" t="n">
-        <v>714</v>
+        <v>766</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>708</v>
+        <v>762</v>
       </c>
       <c r="J9" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1119691.38</v>
+        <v>1133416.84</v>
       </c>
       <c r="F10" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J10" t="n">
         <v>41</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>857156.2000000001</v>
+        <v>915577.3300000001</v>
       </c>
       <c r="F11" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="J11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>832758.6900000001</v>
+        <v>893765.49</v>
       </c>
       <c r="F12" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="J12" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>806123.73</v>
+        <v>884127.23</v>
       </c>
       <c r="F13" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>796416.47</v>
+        <v>798178.24</v>
       </c>
       <c r="F14" t="n">
-        <v>273</v>
+        <v>604</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>271</v>
+        <v>598</v>
       </c>
       <c r="J14" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>754788.27</v>
+        <v>784233.51</v>
       </c>
       <c r="F15" t="n">
-        <v>568</v>
+        <v>269</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>568</v>
+        <v>266</v>
       </c>
       <c r="J15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>682812.71</v>
+        <v>699760.1699999999</v>
       </c>
       <c r="F16" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>603663.72</v>
+        <v>609561.1799999999</v>
       </c>
       <c r="F17" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J17" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>469893.33</v>
+        <v>474559.14</v>
       </c>
       <c r="F18" t="n">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="J18" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>459912</v>
+        <v>472461.14</v>
       </c>
       <c r="F19" t="n">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="J19" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>453381.14</v>
+        <v>430936.58</v>
       </c>
       <c r="F20" t="n">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="J20" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>386126.62</v>
+        <v>400470.54</v>
       </c>
       <c r="F21" t="n">
-        <v>797</v>
+        <v>821</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>794</v>
+        <v>816</v>
       </c>
       <c r="J21" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>369111.16</v>
+        <v>386377.46</v>
       </c>
       <c r="F22" t="n">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>182</v>
+        <v>287</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>364696.18</v>
+        <v>369297.59</v>
       </c>
       <c r="F23" t="n">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,16 +1237,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>278</v>
+        <v>180</v>
       </c>
       <c r="J23" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>338849.1</v>
+        <v>344817</v>
       </c>
       <c r="F24" t="n">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,22 +1273,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="J24" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>310128.9</v>
+        <v>336394.03</v>
       </c>
       <c r="F25" t="n">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>309411.96</v>
+        <v>328824.29</v>
       </c>
       <c r="F26" t="n">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>294720.94</v>
+        <v>305807.72</v>
       </c>
       <c r="F27" t="n">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>285845.74</v>
+        <v>299685.4</v>
       </c>
       <c r="F28" t="n">
-        <v>523</v>
+        <v>90</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>521</v>
+        <v>87</v>
       </c>
       <c r="J28" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>285712.83</v>
+        <v>298757.75</v>
       </c>
       <c r="F29" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="J29" t="n">
         <v>32</v>
@@ -1462,7 +1462,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>276660.02</v>
+        <v>292548.04</v>
       </c>
       <c r="F30" t="n">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="J30" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>273488.83</v>
+        <v>281125.35</v>
       </c>
       <c r="F31" t="n">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>270389.85</v>
+        <v>279455.78</v>
       </c>
       <c r="F32" t="n">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="J32" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>254105.68</v>
+        <v>269966.13</v>
       </c>
       <c r="F33" t="n">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>243</v>
+        <v>36</v>
       </c>
       <c r="J33" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229624.32</v>
+        <v>268248</v>
       </c>
       <c r="F34" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,16 +1633,16 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="J34" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>226974.03</v>
+        <v>262071.66</v>
       </c>
       <c r="F35" t="n">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="J35" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220146.78</v>
+        <v>245562.05</v>
       </c>
       <c r="F36" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="J36" t="n">
         <v>10</v>
@@ -1714,7 +1714,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219395.46</v>
+        <v>242210.69</v>
       </c>
       <c r="F37" t="n">
-        <v>218</v>
+        <v>91</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="J37" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>210483.53</v>
+        <v>241798.63</v>
       </c>
       <c r="F38" t="n">
-        <v>455</v>
+        <v>115</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>449</v>
+        <v>114</v>
       </c>
       <c r="J38" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>207678.83</v>
+        <v>223045.4</v>
       </c>
       <c r="F39" t="n">
-        <v>67</v>
+        <v>482</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,16 +1813,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>67</v>
+        <v>475</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>205105.57</v>
+        <v>219002.57</v>
       </c>
       <c r="F40" t="n">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>180</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>199512.45</v>
+        <v>207724.61</v>
       </c>
       <c r="F41" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="J41" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>194623.69</v>
+        <v>203869.29</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J42" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>191762.52</v>
+        <v>198191.14</v>
       </c>
       <c r="F43" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="J43" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185635.55</v>
+        <v>194623.69</v>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J44" t="n">
         <v>19</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185409.16</v>
+        <v>186595.6</v>
       </c>
       <c r="F45" t="n">
         <v>18</v>
@@ -2038,13 +2038,13 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185107.65</v>
+        <v>185189.84</v>
       </c>
       <c r="F46" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
+        <v>76</v>
+      </c>
+      <c r="J46" t="n">
         <v>20</v>
-      </c>
-      <c r="J46" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>180276.28</v>
+        <v>183701.48</v>
       </c>
       <c r="F47" t="n">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,16 +2101,16 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>72</v>
+        <v>182</v>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>175302.81</v>
+        <v>181589.74</v>
       </c>
       <c r="F48" t="n">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="J48" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>171656.72</v>
+        <v>181039.72</v>
       </c>
       <c r="F49" t="n">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="J49" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>168833.07</v>
+        <v>180975.39</v>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="J50" t="n">
         <v>18</v>
@@ -2218,7 +2218,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>168281.13</v>
+        <v>173863</v>
       </c>
       <c r="F51" t="n">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>167864.34</v>
+        <v>163183.84</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>164062.6</v>
+        <v>162097.47</v>
       </c>
       <c r="F53" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J53" t="n">
         <v>19</v>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>151021.08</v>
+        <v>157799.04</v>
       </c>
       <c r="F54" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>146832.96</v>
+        <v>150815.16</v>
       </c>
       <c r="F55" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J55" t="n">
         <v>8</v>
@@ -2398,13 +2398,13 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>131342.31</v>
+        <v>149105.76</v>
       </c>
       <c r="F56" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,22 +2425,22 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="J56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>122267.03</v>
+        <v>130360.94</v>
       </c>
       <c r="F57" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="J57" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>118133.99</v>
+        <v>118453.37</v>
       </c>
       <c r="F58" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,10 +2497,10 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="J58" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -2536,13 +2536,13 @@
         <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>113691.36</v>
+        <v>115841.5</v>
       </c>
       <c r="F60" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>112949.12</v>
+        <v>109840.24</v>
       </c>
       <c r="F61" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,16 +2605,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>110674.54</v>
+        <v>106252.61</v>
       </c>
       <c r="F62" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102747.46</v>
+        <v>104828.78</v>
       </c>
       <c r="F63" t="n">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="J63" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -2701,28 +2701,28 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102737.94</v>
+        <v>100959.11</v>
       </c>
       <c r="F64" t="n">
+        <v>74</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>75</v>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>74</v>
-      </c>
       <c r="J64" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>97622.00999999999</v>
+        <v>99313.56999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>95316.03999999999</v>
+        <v>95633.91</v>
       </c>
       <c r="F66" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,22 +2785,22 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>93516.10000000001</v>
+        <v>91713.46000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>91001.66</v>
+        <v>91333.84</v>
       </c>
       <c r="F68" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,22 +2857,22 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>89614.39</v>
+        <v>90458.48</v>
       </c>
       <c r="F69" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,16 +2893,16 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>89595.67</v>
+        <v>89614.39</v>
       </c>
       <c r="F70" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>89229.67</v>
+        <v>89321.16</v>
       </c>
       <c r="F71" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>87010.08</v>
+        <v>86920.24000000001</v>
       </c>
       <c r="F72" t="n">
         <v>40</v>
@@ -3001,16 +3001,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>79794.03</v>
+        <v>83221.14</v>
       </c>
       <c r="F73" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>79145.72</v>
+        <v>74600.81</v>
       </c>
       <c r="F74" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>77877.97</v>
+        <v>71028.76000000001</v>
       </c>
       <c r="F75" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,10 +3109,10 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>74753.44</v>
+        <v>70182.22</v>
       </c>
       <c r="F76" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,10 +3145,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J76" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>69477.98</v>
+        <v>69508.48999999999</v>
       </c>
       <c r="F77" t="n">
         <v>16</v>
@@ -3184,13 +3184,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>67822.85000000001</v>
+        <v>68160.10000000001</v>
       </c>
       <c r="F78" t="n">
         <v>21</v>
@@ -3217,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>64898.24000000001</v>
+        <v>67330.33</v>
       </c>
       <c r="F79" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>60006.73</v>
+        <v>65043.17</v>
       </c>
       <c r="F80" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J80" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>59905.05</v>
+        <v>58387.29</v>
       </c>
       <c r="F81" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>59505.92</v>
+        <v>57684.76</v>
       </c>
       <c r="F82" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>58073.69</v>
+        <v>56419.57000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>57844.77</v>
+        <v>54684.71</v>
       </c>
       <c r="F84" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>56305.75</v>
+        <v>53591.48</v>
       </c>
       <c r="F85" t="n">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>54285.65</v>
+        <v>53345.59</v>
       </c>
       <c r="F86" t="n">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53883.05</v>
+        <v>52224.57</v>
       </c>
       <c r="F87" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>52193.18</v>
+        <v>51706.86</v>
       </c>
       <c r="F88" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,22 +3577,22 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J88" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>52183.97</v>
+        <v>50833.05</v>
       </c>
       <c r="F89" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,16 +3613,16 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J89" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>50267.03</v>
+        <v>50499.12</v>
       </c>
       <c r="F90" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,10 +3649,10 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -3730,7 +3730,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>46039.82</v>
+        <v>45584.72</v>
       </c>
       <c r="F93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>45754.2</v>
+        <v>44119.55</v>
       </c>
       <c r="F94" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3793,16 +3793,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>43797.49</v>
+        <v>43719.53</v>
       </c>
       <c r="F95" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J95" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>41124.52</v>
+        <v>40955.02</v>
       </c>
       <c r="F97" t="n">
         <v>23</v>
@@ -3901,10 +3901,10 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
@@ -3925,28 +3925,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>39764.39</v>
+        <v>40742.36</v>
       </c>
       <c r="F98" t="n">
+        <v>23</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
         <v>22</v>
       </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>21</v>
-      </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>39738.17</v>
+        <v>40672.87</v>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J99" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>35617.55</v>
+        <v>40667.77</v>
       </c>
       <c r="F100" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>34502.55</v>
+        <v>38968.67</v>
       </c>
       <c r="F101" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J101" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>31617.49</v>
+        <v>35617.55</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J102" t="n">
         <v>3</v>
@@ -4090,13 +4090,13 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>30687.27</v>
+        <v>35080.5</v>
       </c>
       <c r="F103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,16 +4117,16 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>30500.83</v>
+        <v>31617.49</v>
       </c>
       <c r="F104" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>28417.51</v>
+        <v>31283.91</v>
       </c>
       <c r="F105" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J105" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>28047.45</v>
+        <v>29178.52</v>
       </c>
       <c r="F106" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4225,16 +4225,16 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>26344.92</v>
+        <v>28569.47</v>
       </c>
       <c r="F107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4261,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
@@ -4270,13 +4270,13 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>24754.77</v>
+        <v>28377.98</v>
       </c>
       <c r="F108" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>23641.52</v>
+        <v>27546.21</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,22 +4333,22 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>23593.19</v>
+        <v>27027.96</v>
       </c>
       <c r="F110" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,16 +4369,16 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>22877.98</v>
+        <v>23641.52</v>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,22 +4405,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>22452.54</v>
+        <v>23593.19</v>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J112" t="n">
         <v>1</v>
@@ -4450,7 +4450,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>20736.48</v>
+        <v>22555.06</v>
       </c>
       <c r="F113" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,16 +4477,16 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J113" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>19825.44</v>
+        <v>21000.03</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,16 +4513,16 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>19336.42</v>
+        <v>20065.29</v>
       </c>
       <c r="F115" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,16 +4549,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J115" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>19222.88</v>
+        <v>19825.44</v>
       </c>
       <c r="F116" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,10 +4585,10 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -4624,13 +4624,13 @@
         <v>9</v>
       </c>
       <c r="J117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>18148.34</v>
+        <v>17795.76</v>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,16 +4657,16 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4681,34 +4681,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>17795.76</v>
+        <v>16946.62</v>
       </c>
       <c r="F119" t="n">
+        <v>3</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3</v>
+      </c>
+      <c r="J119" t="n">
         <v>1</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>14729.66</v>
+        <v>15793.22</v>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,16 +4729,16 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>14088.97</v>
+        <v>14729.66</v>
       </c>
       <c r="F121" t="n">
         <v>5</v>
@@ -4768,19 +4768,19 @@
         <v>5</v>
       </c>
       <c r="J121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4789,22 +4789,22 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>13557.62</v>
+        <v>13978.8</v>
       </c>
       <c r="F122" t="n">
+        <v>5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>5</v>
+      </c>
+      <c r="J122" t="n">
         <v>2</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>2</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -4882,7 +4882,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4897,28 +4897,28 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>9597.459999999999</v>
+        <v>10675.66</v>
       </c>
       <c r="F125" t="n">
+        <v>14</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>14</v>
+      </c>
+      <c r="J125" t="n">
         <v>2</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>2</v>
-      </c>
-      <c r="J125" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>9519.469999999999</v>
+        <v>9597.459999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4945,22 +4945,22 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>9025.43</v>
+        <v>9488.15</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4981,16 +4981,16 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0C55MY66L</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>7628.22</v>
+        <v>9025.43</v>
       </c>
       <c r="F128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,10 +5017,10 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5062,7 +5062,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>7116.110000000001</v>
+        <v>7116.09</v>
       </c>
       <c r="F130" t="n">
         <v>3</v>
@@ -5092,7 +5092,7 @@
         <v>3</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5206,13 +5206,13 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6438.98</v>
+        <v>6758.46</v>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -5233,22 +5233,22 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5590.68</v>
+        <v>6438.98</v>
       </c>
       <c r="F135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>2</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
+        <v>2</v>
+      </c>
+      <c r="J136" t="n">
         <v>1</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5416.58</v>
+        <v>5590.68</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5350,7 +5350,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5082.19</v>
+        <v>5416.58</v>
       </c>
       <c r="F138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5377,22 +5377,22 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4744.06</v>
+        <v>5082.19</v>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5413,16 +5413,16 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3929.65</v>
+        <v>4483.05</v>
       </c>
       <c r="F140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5449,16 +5449,16 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3388.98</v>
+        <v>4151.69</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -5494,7 +5494,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3388.14</v>
+        <v>3929.65</v>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5521,22 +5521,22 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3007.63</v>
+        <v>3388.98</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2477.97</v>
+        <v>3388.14</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -5602,13 +5602,13 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B0CFKZ72N7</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2011.86</v>
+        <v>3007.63</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -5632,13 +5632,13 @@
         <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1990.68</v>
+        <v>2477.97</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
@@ -5668,13 +5668,13 @@
         <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1863.56</v>
+        <v>2032.2</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0CBCB9S14</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1694.07</v>
+        <v>2011.86</v>
       </c>
       <c r="F148" t="n">
         <v>1</v>
@@ -5740,13 +5740,13 @@
         <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1618.05</v>
+        <v>1863.56</v>
       </c>
       <c r="F149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1016.1</v>
+        <v>1694.07</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>464.02</v>
+        <v>1618.05</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -5854,13 +5854,13 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5890,13 +5890,13 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0C8JDHLX9</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5920,6 +5920,78 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>B0FLYJFC22</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>B0GW8ZQRFK</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[04/05/26 - 01/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[10/07/26 - 08/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6159861.03</v>
+        <v>1832890.96</v>
       </c>
       <c r="F3" t="n">
-        <v>1515</v>
+        <v>453</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1515</v>
+        <v>451</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5659283.41</v>
+        <v>1410387.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2514</v>
+        <v>616</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,16 +553,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2502</v>
+        <v>622</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3557222.3</v>
+        <v>1292697.72</v>
       </c>
       <c r="F5" t="n">
-        <v>583</v>
+        <v>286</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,16 +589,16 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>569</v>
+        <v>284</v>
       </c>
       <c r="J5" t="n">
-        <v>118</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3139993.39</v>
+        <v>1258042.67</v>
       </c>
       <c r="F6" t="n">
-        <v>417</v>
+        <v>229</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="J6" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2693021.16</v>
+        <v>848516.9300000001</v>
       </c>
       <c r="F7" t="n">
-        <v>608</v>
+        <v>112</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,16 +661,16 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>592</v>
+        <v>118</v>
       </c>
       <c r="J7" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1850462.39</v>
+        <v>661132.27</v>
       </c>
       <c r="F8" t="n">
-        <v>1095</v>
+        <v>277</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1100</v>
+        <v>282</v>
       </c>
       <c r="J8" t="n">
-        <v>187</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1801775.32</v>
+        <v>618511.4300000001</v>
       </c>
       <c r="F9" t="n">
-        <v>766</v>
+        <v>366</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,16 +733,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>762</v>
+        <v>366</v>
       </c>
       <c r="J9" t="n">
-        <v>210</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1133416.84</v>
+        <v>399495.94</v>
       </c>
       <c r="F10" t="n">
-        <v>359</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>360</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>915577.3300000001</v>
+        <v>369530.57</v>
       </c>
       <c r="F11" t="n">
-        <v>283</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>282</v>
+        <v>78</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>893765.49</v>
+        <v>369174.68</v>
       </c>
       <c r="F12" t="n">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>884127.23</v>
+        <v>321323.28</v>
       </c>
       <c r="F13" t="n">
-        <v>126</v>
+        <v>247</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="J13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>798178.24</v>
+        <v>251757.38</v>
       </c>
       <c r="F14" t="n">
-        <v>604</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>598</v>
+        <v>79</v>
       </c>
       <c r="J14" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>784233.51</v>
+        <v>250982.2</v>
       </c>
       <c r="F15" t="n">
-        <v>269</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>266</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>699760.1699999999</v>
+        <v>245971.65</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -988,13 +988,13 @@
         <v>83</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>609561.1799999999</v>
+        <v>245344.66</v>
       </c>
       <c r="F17" t="n">
-        <v>442</v>
+        <v>153</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>439</v>
+        <v>154</v>
       </c>
       <c r="J17" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>474559.14</v>
+        <v>216470.24</v>
       </c>
       <c r="F18" t="n">
-        <v>226</v>
+        <v>154</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="J18" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>472461.14</v>
+        <v>210316.96</v>
       </c>
       <c r="F19" t="n">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>430936.58</v>
+        <v>205746.6</v>
       </c>
       <c r="F20" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>400470.54</v>
+        <v>201650.87</v>
       </c>
       <c r="F21" t="n">
-        <v>821</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>816</v>
+        <v>44</v>
       </c>
       <c r="J21" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>386377.46</v>
+        <v>193301.62</v>
       </c>
       <c r="F22" t="n">
-        <v>291</v>
+        <v>194</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="J22" t="n">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>369297.59</v>
+        <v>182765.13</v>
       </c>
       <c r="F23" t="n">
-        <v>181</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="J23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>344817</v>
+        <v>179292.96</v>
       </c>
       <c r="F24" t="n">
-        <v>226</v>
+        <v>114</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,22 +1273,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="J24" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>336394.03</v>
+        <v>175693.35</v>
       </c>
       <c r="F25" t="n">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>328824.29</v>
+        <v>168424.55</v>
       </c>
       <c r="F26" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="J26" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>305807.72</v>
+        <v>163823.75</v>
       </c>
       <c r="F27" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="J27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>299685.4</v>
+        <v>160884.98</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,22 +1417,22 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>298757.75</v>
+        <v>156250.31</v>
       </c>
       <c r="F29" t="n">
-        <v>162</v>
+        <v>316</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>161</v>
+        <v>297</v>
       </c>
       <c r="J29" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>292548.04</v>
+        <v>153353.78</v>
       </c>
       <c r="F30" t="n">
-        <v>283</v>
+        <v>114</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,22 +1489,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c r="J30" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>281125.35</v>
+        <v>140287.18</v>
       </c>
       <c r="F31" t="n">
-        <v>517</v>
+        <v>62</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>519</v>
+        <v>60</v>
       </c>
       <c r="J31" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>279455.78</v>
+        <v>134954.27</v>
       </c>
       <c r="F32" t="n">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="J32" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>269966.13</v>
+        <v>134061.07</v>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>268248</v>
+        <v>118387.33</v>
       </c>
       <c r="F34" t="n">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,16 +1633,16 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="J34" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>262071.66</v>
+        <v>118151.69</v>
       </c>
       <c r="F35" t="n">
-        <v>260</v>
+        <v>37</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,16 +1669,16 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>255</v>
+        <v>34</v>
       </c>
       <c r="J35" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>245562.05</v>
+        <v>114052.59</v>
       </c>
       <c r="F36" t="n">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,16 +1705,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>242210.69</v>
+        <v>102316.91</v>
       </c>
       <c r="F37" t="n">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,22 +1741,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>88</v>
+        <v>223</v>
       </c>
       <c r="J37" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>241798.63</v>
+        <v>96669.45</v>
       </c>
       <c r="F38" t="n">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,22 +1777,22 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="J38" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>223045.4</v>
+        <v>96028.89999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>482</v>
+        <v>38</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,16 +1813,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>475</v>
+        <v>40</v>
       </c>
       <c r="J39" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219002.57</v>
+        <v>90845.04000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>207724.61</v>
+        <v>90175.49000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>203869.29</v>
+        <v>88160.95</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>198191.14</v>
+        <v>83240.61</v>
       </c>
       <c r="F43" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="J43" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>194623.69</v>
+        <v>80921.20999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,16 +1993,16 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>186595.6</v>
+        <v>79805.88</v>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185189.84</v>
+        <v>76629.52</v>
       </c>
       <c r="F46" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>183701.48</v>
+        <v>76105.96000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>182</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>181589.74</v>
+        <v>74107.57000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>181039.72</v>
+        <v>71757.64</v>
       </c>
       <c r="F49" t="n">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>180975.39</v>
+        <v>71519.47</v>
       </c>
       <c r="F50" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>173863</v>
+        <v>69014.39999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>163183.84</v>
+        <v>65626.27</v>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>162097.47</v>
+        <v>63777.89999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>157799.04</v>
+        <v>63416.07</v>
       </c>
       <c r="F54" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>150815.16</v>
+        <v>58886.42999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>149105.76</v>
+        <v>58867.77999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,22 +2425,22 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>130360.94</v>
+        <v>55867.77</v>
       </c>
       <c r="F57" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="J57" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>118453.37</v>
+        <v>53087.42</v>
       </c>
       <c r="F58" t="n">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="J58" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>117514.43</v>
+        <v>51857.62</v>
       </c>
       <c r="F59" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>115841.5</v>
+        <v>48116.97</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>109840.24</v>
+        <v>45651.66</v>
       </c>
       <c r="F61" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,22 +2605,22 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106252.61</v>
+        <v>45275.41</v>
       </c>
       <c r="F62" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>104828.78</v>
+        <v>41200.75</v>
       </c>
       <c r="F63" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J63" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100959.11</v>
+        <v>40500.01</v>
       </c>
       <c r="F64" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>99313.56999999999</v>
+        <v>40298.28</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>95633.91</v>
+        <v>37836.42</v>
       </c>
       <c r="F66" t="n">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,16 +2785,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="J66" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>91713.46000000001</v>
+        <v>36593.96</v>
       </c>
       <c r="F67" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J67" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>91333.84</v>
+        <v>32993.22</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,22 +2857,22 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>90458.48</v>
+        <v>32963.61</v>
       </c>
       <c r="F69" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,16 +2893,16 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>89614.39</v>
+        <v>31348.28</v>
       </c>
       <c r="F70" t="n">
         <v>9</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>89321.16</v>
+        <v>30945.74</v>
       </c>
       <c r="F71" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>86920.24000000001</v>
+        <v>30617.8</v>
       </c>
       <c r="F72" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="J72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>83221.14</v>
+        <v>30546.43</v>
       </c>
       <c r="F73" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
         <v>4</v>
@@ -3046,7 +3046,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>74600.81</v>
+        <v>30330.47</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>71028.76000000001</v>
+        <v>30049.15</v>
       </c>
       <c r="F75" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J75" t="n">
         <v>7</v>
@@ -3118,7 +3118,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>70182.22</v>
+        <v>29643.22</v>
       </c>
       <c r="F76" t="n">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>69508.48999999999</v>
+        <v>29226.25</v>
       </c>
       <c r="F77" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3181,22 +3181,22 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>68160.10000000001</v>
+        <v>27275.43</v>
       </c>
       <c r="F78" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3217,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>67330.33</v>
+        <v>27199.14999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>65043.17</v>
+        <v>26772.87</v>
       </c>
       <c r="F80" t="n">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,28 +3313,28 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>58387.29</v>
+        <v>25316.29</v>
       </c>
       <c r="F81" t="n">
+        <v>6</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J81" t="n">
         <v>3</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>57684.76</v>
+        <v>25249.99</v>
       </c>
       <c r="F82" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J82" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>56419.57000000001</v>
+        <v>25161.84</v>
       </c>
       <c r="F83" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>54684.71</v>
+        <v>24571.12</v>
       </c>
       <c r="F84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3436,13 +3436,13 @@
         <v>17</v>
       </c>
       <c r="J84" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53591.48</v>
+        <v>23630.49</v>
       </c>
       <c r="F85" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53345.59</v>
+        <v>23538.95</v>
       </c>
       <c r="F86" t="n">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>52224.57</v>
+        <v>23492.39</v>
       </c>
       <c r="F87" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>51706.86</v>
+        <v>21820.28</v>
       </c>
       <c r="F88" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,22 +3577,22 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>50833.05</v>
+        <v>20669.53</v>
       </c>
       <c r="F89" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,16 +3613,16 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J89" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>50499.12</v>
+        <v>20257.63</v>
       </c>
       <c r="F90" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>47433.86</v>
+        <v>19695.74</v>
       </c>
       <c r="F91" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="J91" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>47252.57</v>
+        <v>19490.68</v>
       </c>
       <c r="F92" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>45584.72</v>
+        <v>18219.49</v>
       </c>
       <c r="F93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,22 +3757,22 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>44119.55</v>
+        <v>18043.24</v>
       </c>
       <c r="F94" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3793,22 +3793,22 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J94" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>43719.53</v>
+        <v>17825.39</v>
       </c>
       <c r="F95" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,22 +3829,22 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>43359.28</v>
+        <v>17718.81</v>
       </c>
       <c r="F96" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>40955.02</v>
+        <v>16605.92</v>
       </c>
       <c r="F97" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,16 +3901,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>40742.36</v>
+        <v>16459.66</v>
       </c>
       <c r="F98" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3937,16 +3937,16 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>40672.87</v>
+        <v>15274.58</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>40667.77</v>
+        <v>14861.86</v>
       </c>
       <c r="F100" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>38968.67</v>
+        <v>14829.1</v>
       </c>
       <c r="F101" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>35617.55</v>
+        <v>14066.1</v>
       </c>
       <c r="F102" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>35080.5</v>
+        <v>13425.43</v>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,22 +4117,22 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>31617.49</v>
+        <v>12600.02</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>31283.91</v>
+        <v>12369.49</v>
       </c>
       <c r="F105" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>29178.52</v>
+        <v>12073.72</v>
       </c>
       <c r="F106" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4225,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>28569.47</v>
+        <v>11842.38</v>
       </c>
       <c r="F107" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4261,16 +4261,16 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>28377.98</v>
+        <v>11030.5</v>
       </c>
       <c r="F108" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>27546.21</v>
+        <v>9658.48</v>
       </c>
       <c r="F109" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,22 +4333,22 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>27027.96</v>
+        <v>9566.93</v>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>23641.52</v>
+        <v>9182.200000000001</v>
       </c>
       <c r="F111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,22 +4405,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>23593.19</v>
+        <v>8981.360000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,16 +4441,16 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>22555.06</v>
+        <v>8758.469999999999</v>
       </c>
       <c r="F113" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,16 +4477,16 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21000.03</v>
+        <v>8700</v>
       </c>
       <c r="F114" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,22 +4513,22 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>20065.29</v>
+        <v>8586.76</v>
       </c>
       <c r="F115" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,16 +4549,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="J115" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>19825.44</v>
+        <v>8059.309999999999</v>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,22 +4585,22 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>18958.5</v>
+        <v>7925.42</v>
       </c>
       <c r="F117" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>17795.76</v>
+        <v>7411.88</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,22 +4657,22 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4681,34 +4681,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>16946.62</v>
+        <v>6777.96</v>
       </c>
       <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
         <v>3</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>3</v>
-      </c>
-      <c r="J119" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>15793.22</v>
+        <v>6438.99</v>
       </c>
       <c r="F120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>14729.66</v>
+        <v>5590.68</v>
       </c>
       <c r="F121" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,22 +4765,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>13978.8</v>
+        <v>5507.63</v>
       </c>
       <c r="F122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -4801,22 +4801,22 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>11694.07</v>
+        <v>5083.9</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -4846,7 +4846,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>11522.03</v>
+        <v>5082.21</v>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>10675.66</v>
+        <v>5041.53</v>
       </c>
       <c r="F125" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4909,16 +4909,16 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>9597.459999999999</v>
+        <v>4914.41</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4945,22 +4945,22 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>9488.15</v>
+        <v>4912.71</v>
       </c>
       <c r="F127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4981,22 +4981,22 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0C55MY66L</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>9025.43</v>
+        <v>4744.08</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,16 +5017,16 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>7626.27</v>
+        <v>4660.16</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -5062,13 +5062,13 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5077,34 +5077,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>7116.09</v>
+        <v>4571.16</v>
       </c>
       <c r="F130" t="n">
+        <v>6</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>6</v>
+      </c>
+      <c r="J130" t="n">
         <v>3</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>3</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6862.71</v>
+        <v>4483.05</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>1</v>
@@ -5134,7 +5134,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0BLKF46QG</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6834.74</v>
+        <v>4066.95</v>
       </c>
       <c r="F132" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5161,16 +5161,16 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6775.4</v>
+        <v>3897.46</v>
       </c>
       <c r="F133" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6758.46</v>
+        <v>3727.12</v>
       </c>
       <c r="F134" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -5233,22 +5233,22 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6438.98</v>
+        <v>3303.38</v>
       </c>
       <c r="F135" t="n">
         <v>2</v>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5590.68</v>
+        <v>3211.02</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5590.68</v>
+        <v>3048.3</v>
       </c>
       <c r="F137" t="n">
         <v>3</v>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -5350,13 +5350,13 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5416.58</v>
+        <v>2965.26</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -5380,13 +5380,13 @@
         <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5082.19</v>
+        <v>2880.5</v>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5413,16 +5413,16 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4483.05</v>
+        <v>2795.760000000002</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -5452,13 +5452,13 @@
         <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4151.69</v>
+        <v>2710.16</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3929.65</v>
+        <v>2404.24</v>
       </c>
       <c r="F142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5521,22 +5521,22 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3388.98</v>
+        <v>1927.97</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -5566,7 +5566,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3388.14</v>
+        <v>1863.56</v>
       </c>
       <c r="F144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -5593,22 +5593,22 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0CFKZ72N7</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3007.63</v>
+        <v>1694.07</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2477.97</v>
+        <v>1694.07</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
@@ -5674,7 +5674,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2032.2</v>
+        <v>1355.08</v>
       </c>
       <c r="F147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -5710,13 +5710,13 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0CBCB9S14</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2011.86</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>1</v>
@@ -5746,7 +5746,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1863.56</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -5782,13 +5782,13 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0C8JDHLX9</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0BLKCDRNB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1618.05</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -5845,16 +5845,16 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5890,13 +5890,13 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5926,7 +5926,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5956,13 +5956,13 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5992,6 +5992,42 @@
         <v>0</v>
       </c>
       <c r="J155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>B0FLYHJ6DK</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[10/07/26 - 08/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[17/07/26 - 15/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1832890.96</v>
+        <v>1851902.99</v>
       </c>
       <c r="F3" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J3" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1410387.91</v>
+        <v>1462362.77</v>
       </c>
       <c r="F4" t="n">
-        <v>616</v>
+        <v>655</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="J4" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1292697.72</v>
+        <v>1456540.37</v>
       </c>
       <c r="F5" t="n">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="J5" t="n">
         <v>33</v>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1258042.67</v>
+        <v>1299670.86</v>
       </c>
       <c r="F6" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J6" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>848516.9300000001</v>
+        <v>866305.84</v>
       </c>
       <c r="F7" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="J7" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>661132.27</v>
+        <v>698312.72</v>
       </c>
       <c r="F8" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>618511.4300000001</v>
+        <v>553560.7</v>
       </c>
       <c r="F9" t="n">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="J9" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>399495.94</v>
+        <v>495449.38</v>
       </c>
       <c r="F10" t="n">
+        <v>72</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>57</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>50</v>
-      </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>369530.57</v>
+        <v>353383.91</v>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>369174.68</v>
+        <v>332155.3</v>
       </c>
       <c r="F12" t="n">
-        <v>116</v>
+        <v>264</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="J12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>321323.28</v>
+        <v>317572.95</v>
       </c>
       <c r="F13" t="n">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="J13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>251757.38</v>
+        <v>267094.67</v>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>250982.2</v>
+        <v>265420.75</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>245971.65</v>
+        <v>263039.87</v>
       </c>
       <c r="F16" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>245344.66</v>
+        <v>260606.8</v>
       </c>
       <c r="F17" t="n">
-        <v>153</v>
+        <v>32</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>216470.24</v>
+        <v>231163.8</v>
       </c>
       <c r="F18" t="n">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210316.96</v>
+        <v>219334.98</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,16 +1093,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>155</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205746.6</v>
+        <v>214576.41</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>201650.87</v>
+        <v>207991.34</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>193301.62</v>
+        <v>207210.16</v>
       </c>
       <c r="F22" t="n">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>183</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>182765.13</v>
+        <v>183596.56</v>
       </c>
       <c r="F23" t="n">
+        <v>57</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>56</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>54</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>179292.96</v>
+        <v>178882.7</v>
       </c>
       <c r="F24" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>175693.35</v>
+        <v>173119.48</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="J25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>168424.55</v>
+        <v>163304.22</v>
       </c>
       <c r="F26" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="J26" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>163823.75</v>
+        <v>160414.84</v>
       </c>
       <c r="F27" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>160884.98</v>
+        <v>157384.32</v>
       </c>
       <c r="F28" t="n">
-        <v>76</v>
+        <v>334</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>156250.31</v>
+        <v>141217.8</v>
       </c>
       <c r="F29" t="n">
-        <v>316</v>
+        <v>45</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>297</v>
+        <v>40</v>
       </c>
       <c r="J29" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>153353.78</v>
+        <v>140223</v>
       </c>
       <c r="F30" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,22 +1489,22 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="J30" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>140287.18</v>
+        <v>140060.13</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>134954.27</v>
+        <v>138856.02</v>
       </c>
       <c r="F32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>134061.07</v>
+        <v>126266.11</v>
       </c>
       <c r="F33" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,16 +1597,16 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J33" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>118387.33</v>
+        <v>120916</v>
       </c>
       <c r="F34" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,22 +1633,22 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="J34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>118151.69</v>
+        <v>107175.44</v>
       </c>
       <c r="F35" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>114052.59</v>
+        <v>105778.03</v>
       </c>
       <c r="F36" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,16 +1705,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="J36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102316.91</v>
+        <v>104349.23</v>
       </c>
       <c r="F37" t="n">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,22 +1741,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>223</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>96669.45</v>
+        <v>101147.58</v>
       </c>
       <c r="F38" t="n">
-        <v>58</v>
+        <v>221</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,22 +1777,22 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="J38" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>96028.89999999999</v>
+        <v>100447.38</v>
       </c>
       <c r="F39" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,22 +1813,22 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>90845.04000000001</v>
+        <v>97515.31</v>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,22 +1849,22 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J40" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>90175.49000000001</v>
+        <v>89847.53999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>88160.95</v>
+        <v>85579.63</v>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>83240.61</v>
+        <v>81963.35000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>80921.20999999999</v>
+        <v>75484.74000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,16 +1993,16 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>79805.88</v>
+        <v>75418.74000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,16 +2029,16 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>76629.52</v>
+        <v>74393.98</v>
       </c>
       <c r="F46" t="n">
-        <v>70</v>
+        <v>143</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="J46" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>76105.96000000001</v>
+        <v>72023.73999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,22 +2101,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>74107.57000000001</v>
+        <v>70134.8</v>
       </c>
       <c r="F48" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,16 +2137,16 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>71757.64</v>
+        <v>69617.75</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,16 +2173,16 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>71519.47</v>
+        <v>67775.41</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>69014.39999999999</v>
+        <v>65926.25</v>
       </c>
       <c r="F51" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>65626.27</v>
+        <v>65426.21</v>
       </c>
       <c r="F52" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>63777.89999999999</v>
+        <v>64262.66</v>
       </c>
       <c r="F53" t="n">
         <v>16</v>
@@ -2326,7 +2326,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>63416.07</v>
+        <v>63452.53</v>
       </c>
       <c r="F54" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="J54" t="n">
         <v>5</v>
@@ -2362,7 +2362,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>58886.42999999999</v>
+        <v>54978.91</v>
       </c>
       <c r="F55" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>58867.77999999999</v>
+        <v>50421.19</v>
       </c>
       <c r="F56" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,16 +2425,16 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>55867.77</v>
+        <v>50401.7</v>
       </c>
       <c r="F57" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J57" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53087.42</v>
+        <v>50135.58</v>
       </c>
       <c r="F58" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>51857.62</v>
+        <v>49288.95</v>
       </c>
       <c r="F59" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>48116.97</v>
+        <v>47299.99</v>
       </c>
       <c r="F60" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>45651.66</v>
+        <v>44482.2</v>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J61" t="n">
         <v>3</v>
@@ -2614,13 +2614,13 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>45275.41</v>
+        <v>44467.82</v>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41200.75</v>
+        <v>43263.54</v>
       </c>
       <c r="F63" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J63" t="n">
         <v>2</v>
@@ -2686,13 +2686,13 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>40500.01</v>
+        <v>41421.18</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>40298.28</v>
+        <v>41383.89</v>
       </c>
       <c r="F65" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>37836.42</v>
+        <v>36898.13</v>
       </c>
       <c r="F66" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>36593.96</v>
+        <v>35746.56</v>
       </c>
       <c r="F67" t="n">
         <v>29</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>32993.22</v>
+        <v>35605.05</v>
       </c>
       <c r="F68" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>32963.61</v>
+        <v>35501.69999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,22 +2893,22 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>31348.28</v>
+        <v>35103.4</v>
       </c>
       <c r="F70" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>30945.74</v>
+        <v>33984.66</v>
       </c>
       <c r="F71" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>30617.8</v>
+        <v>32452.52999999999</v>
       </c>
       <c r="F72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>30546.43</v>
+        <v>31829.64</v>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>30330.47</v>
+        <v>30363.56</v>
       </c>
       <c r="F74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>30049.15</v>
+        <v>29144.03</v>
       </c>
       <c r="F75" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="J75" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>29643.22</v>
+        <v>28503.38</v>
       </c>
       <c r="F76" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
+        <v>17</v>
+      </c>
+      <c r="J76" t="n">
         <v>8</v>
-      </c>
-      <c r="J76" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>29226.25</v>
+        <v>28402.73</v>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3181,22 +3181,22 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3205,28 +3205,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>27275.43</v>
+        <v>28121.18</v>
       </c>
       <c r="F78" t="n">
+        <v>17</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>15</v>
       </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>12</v>
-      </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>27199.14999999999</v>
+        <v>26834.73</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>26772.87</v>
+        <v>26768.65</v>
       </c>
       <c r="F80" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>25316.29</v>
+        <v>25249.99</v>
       </c>
       <c r="F81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>3</v>
@@ -3334,7 +3334,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>25249.99</v>
+        <v>24177.9</v>
       </c>
       <c r="F82" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>25161.84</v>
+        <v>23380.51</v>
       </c>
       <c r="F83" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>24571.12</v>
+        <v>21467.79</v>
       </c>
       <c r="F84" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>23630.49</v>
+        <v>21444.94</v>
       </c>
       <c r="F85" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23538.95</v>
+        <v>20085.56</v>
       </c>
       <c r="F86" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>23492.39</v>
+        <v>19605.94</v>
       </c>
       <c r="F87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21820.28</v>
+        <v>19570.32</v>
       </c>
       <c r="F88" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,22 +3577,22 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="J88" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>20669.53</v>
+        <v>19490.68</v>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>20257.63</v>
+        <v>19198.29</v>
       </c>
       <c r="F90" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,22 +3649,22 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>19695.74</v>
+        <v>19008.44</v>
       </c>
       <c r="F91" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,22 +3685,22 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>19490.68</v>
+        <v>18382.24</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J92" t="n">
         <v>1</v>
@@ -3730,7 +3730,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>18219.49</v>
+        <v>17846.6</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3766,13 +3766,13 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>18043.24</v>
+        <v>17718.81</v>
       </c>
       <c r="F94" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>17825.39</v>
+        <v>17366.08</v>
       </c>
       <c r="F95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
@@ -3838,13 +3838,13 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>17718.81</v>
+        <v>16010.18</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>16605.92</v>
+        <v>15844.06</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,10 +3901,10 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16459.66</v>
+        <v>14326.02</v>
       </c>
       <c r="F98" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3940,13 +3940,13 @@
         <v>14</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>15274.58</v>
+        <v>13712.71</v>
       </c>
       <c r="F99" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,22 +3973,22 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>14861.86</v>
+        <v>13673.72</v>
       </c>
       <c r="F100" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>2</v>
@@ -4018,13 +4018,13 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>14829.1</v>
+        <v>13301.68</v>
       </c>
       <c r="F101" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>14066.1</v>
+        <v>13216.94</v>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,10 +4081,10 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>13425.43</v>
+        <v>12916.95</v>
       </c>
       <c r="F103" t="n">
         <v>8</v>
@@ -4126,13 +4126,13 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>12600.02</v>
+        <v>12877.97</v>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>12369.49</v>
+        <v>12575.42</v>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,22 +4189,22 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>12073.72</v>
+        <v>12488.96</v>
       </c>
       <c r="F106" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4225,16 +4225,16 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>11842.38</v>
+        <v>12053.4</v>
       </c>
       <c r="F107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4261,22 +4261,22 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>11030.5</v>
+        <v>10922.88</v>
       </c>
       <c r="F108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>9658.48</v>
+        <v>10315.97</v>
       </c>
       <c r="F109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -4342,13 +4342,13 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4357,28 +4357,28 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>9566.93</v>
+        <v>10269.46</v>
       </c>
       <c r="F110" t="n">
+        <v>6</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>7</v>
+      </c>
+      <c r="J110" t="n">
         <v>4</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>4</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,28 +4393,28 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>9182.200000000001</v>
+        <v>10093.22</v>
       </c>
       <c r="F111" t="n">
+        <v>6</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>6</v>
+      </c>
+      <c r="J111" t="n">
         <v>2</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" t="n">
-        <v>2</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4429,28 +4429,28 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>8981.360000000001</v>
+        <v>9851.700000000001</v>
       </c>
       <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5</v>
+      </c>
+      <c r="J112" t="n">
         <v>2</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>8758.469999999999</v>
+        <v>9828.82</v>
       </c>
       <c r="F113" t="n">
         <v>2</v>
@@ -4486,7 +4486,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>8700</v>
+        <v>9583.879999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,16 +4513,16 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>8586.76</v>
+        <v>9566.93</v>
       </c>
       <c r="F115" t="n">
         <v>4</v>
@@ -4549,16 +4549,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>8059.309999999999</v>
+        <v>9277.119999999999</v>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,22 +4585,22 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>7925.42</v>
+        <v>9250.860000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>7411.88</v>
+        <v>9002.549999999999</v>
       </c>
       <c r="F118" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,22 +4657,22 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6777.96</v>
+        <v>8981.360000000001</v>
       </c>
       <c r="F119" t="n">
         <v>2</v>
@@ -4696,19 +4696,19 @@
         <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6438.99</v>
+        <v>8896.599999999999</v>
       </c>
       <c r="F120" t="n">
         <v>2</v>
@@ -4732,19 +4732,19 @@
         <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5590.68</v>
+        <v>8364.42</v>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5507.63</v>
+        <v>7963.56</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -4801,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4810,13 +4810,13 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0CCVBQRFX</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5083.9</v>
+        <v>7925.42</v>
       </c>
       <c r="F123" t="n">
         <v>1</v>
@@ -4846,7 +4846,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,28 +4861,28 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5082.21</v>
+        <v>6729.63</v>
       </c>
       <c r="F124" t="n">
+        <v>9</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>9</v>
+      </c>
+      <c r="J124" t="n">
         <v>3</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>3</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5041.53</v>
+        <v>6650.02</v>
       </c>
       <c r="F125" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4909,16 +4909,16 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4914.41</v>
+        <v>5507.63</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -4954,13 +4954,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4912.71</v>
+        <v>5083.9</v>
       </c>
       <c r="F127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4990,13 +4990,13 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4744.08</v>
+        <v>5041.53</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4660.16</v>
+        <v>4483.05</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -5056,13 +5056,13 @@
         <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4571.16</v>
+        <v>4066.95</v>
       </c>
       <c r="F130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5089,16 +5089,16 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4483.05</v>
+        <v>3897.46</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
@@ -5128,19 +5128,19 @@
         <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4066.95</v>
+        <v>3219.5</v>
       </c>
       <c r="F132" t="n">
         <v>1</v>
@@ -5161,16 +5161,16 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0FTVS34SD</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3897.46</v>
+        <v>3218.64</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5200,13 +5200,13 @@
         <v>1</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3727.12</v>
+        <v>3218.64</v>
       </c>
       <c r="F134" t="n">
         <v>2</v>
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -5242,7 +5242,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3303.38</v>
+        <v>3211.02</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3211.02</v>
+        <v>3048.3</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -5314,13 +5314,13 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3048.3</v>
+        <v>2965.26</v>
       </c>
       <c r="F137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5341,22 +5341,22 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2965.26</v>
+        <v>2877.97</v>
       </c>
       <c r="F138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5377,16 +5377,16 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2880.5</v>
+        <v>2795.760000000002</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
@@ -5416,13 +5416,13 @@
         <v>1</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2795.760000000002</v>
+        <v>2625.42</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5449,16 +5449,16 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2710.16</v>
+        <v>2404.24</v>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -5494,13 +5494,13 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2404.24</v>
+        <v>1927.97</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5530,13 +5530,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1927.97</v>
+        <v>1863.56</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5674,7 +5674,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1355.08</v>
+        <v>1694.07</v>
       </c>
       <c r="F147" t="n">
         <v>1</v>
@@ -5710,13 +5710,13 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1312.71</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -5737,16 +5737,16 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5761,10 +5761,10 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1058.47</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -5782,13 +5782,13 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B0C8JDHLX9</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B0BLKCDRNB</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5848,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5926,7 +5926,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5956,78 +5956,6 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>B0FJ8T4WXM</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>B0FLYHJ6DK</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J154"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[17/07/26 - 15/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[24/07/26 - 22/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1851902.99</v>
+        <v>2051502.12</v>
       </c>
       <c r="F3" t="n">
-        <v>469</v>
+        <v>522</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="J3" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1462362.77</v>
+        <v>1769056.45</v>
       </c>
       <c r="F4" t="n">
-        <v>655</v>
+        <v>795</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>633</v>
+        <v>784</v>
       </c>
       <c r="J4" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1456540.37</v>
+        <v>1536908.27</v>
       </c>
       <c r="F5" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="J5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1299670.86</v>
+        <v>1320153.85</v>
       </c>
       <c r="F6" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="J6" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>866305.84</v>
+        <v>1058566.87</v>
       </c>
       <c r="F7" t="n">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="J7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>698312.72</v>
+        <v>711310.47</v>
       </c>
       <c r="F8" t="n">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="J8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>553560.7</v>
+        <v>601772.5600000001</v>
       </c>
       <c r="F9" t="n">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="J9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>495449.38</v>
+        <v>444650.22</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353383.91</v>
+        <v>414029.7</v>
       </c>
       <c r="F11" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>332155.3</v>
+        <v>395257.66</v>
       </c>
       <c r="F12" t="n">
-        <v>264</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>252</v>
+        <v>43</v>
       </c>
       <c r="J12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>317572.95</v>
+        <v>386918.01</v>
       </c>
       <c r="F13" t="n">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="J13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>267094.67</v>
+        <v>362850.17</v>
       </c>
       <c r="F14" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>265420.75</v>
+        <v>355181.46</v>
       </c>
       <c r="F15" t="n">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="J15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>263039.87</v>
+        <v>344047.07</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>279</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>56</v>
+        <v>279</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>260606.8</v>
+        <v>317009.84</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>231163.8</v>
+        <v>290400.36</v>
       </c>
       <c r="F18" t="n">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>215</v>
+        <v>289</v>
       </c>
       <c r="J18" t="n">
         <v>39</v>
@@ -1066,7 +1066,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219334.98</v>
+        <v>264699.13</v>
       </c>
       <c r="F19" t="n">
-        <v>161</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>214576.41</v>
+        <v>224193.56</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>207991.34</v>
+        <v>210219.6</v>
       </c>
       <c r="F21" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>207210.16</v>
+        <v>204603.22</v>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="J22" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>183596.56</v>
+        <v>185596.88</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,22 +1237,22 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>178882.7</v>
+        <v>178269.4</v>
       </c>
       <c r="F24" t="n">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>173119.48</v>
+        <v>178184.74</v>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J25" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>163304.22</v>
+        <v>171219.04</v>
       </c>
       <c r="F26" t="n">
-        <v>161</v>
+        <v>366</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>156</v>
+        <v>359</v>
       </c>
       <c r="J26" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>160414.84</v>
+        <v>167786.02</v>
       </c>
       <c r="F27" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>157384.32</v>
+        <v>166686.4</v>
       </c>
       <c r="F28" t="n">
-        <v>334</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>323</v>
+        <v>51</v>
       </c>
       <c r="J28" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>141217.8</v>
+        <v>166341.51</v>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>140223</v>
+        <v>152020.35</v>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>140060.13</v>
+        <v>150239.92</v>
       </c>
       <c r="F31" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,22 +1525,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>138856.02</v>
+        <v>124338.91</v>
       </c>
       <c r="F32" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>126266.11</v>
+        <v>119071.26</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,16 +1597,16 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>120916</v>
+        <v>114622.11</v>
       </c>
       <c r="F34" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J34" t="n">
         <v>11</v>
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>107175.44</v>
+        <v>110380.5</v>
       </c>
       <c r="F35" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J35" t="n">
         <v>8</v>
@@ -1678,13 +1678,13 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105778.03</v>
+        <v>109318.1</v>
       </c>
       <c r="F36" t="n">
-        <v>57</v>
+        <v>240</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,16 +1705,16 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>104349.23</v>
+        <v>106802.46</v>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,22 +1741,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>101147.58</v>
+        <v>105004.31</v>
       </c>
       <c r="F38" t="n">
-        <v>221</v>
+        <v>65</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>216</v>
+        <v>63</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100447.38</v>
+        <v>99317.87</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,22 +1813,22 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>97515.31</v>
+        <v>94661.08</v>
       </c>
       <c r="F40" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,22 +1849,22 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="J40" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>89847.53999999999</v>
+        <v>87994.05</v>
       </c>
       <c r="F41" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>85579.63</v>
+        <v>87788.97</v>
       </c>
       <c r="F42" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,22 +1921,22 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>81963.35000000001</v>
+        <v>87356.85000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,10 +1957,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="J43" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1981,34 +1981,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>75484.74000000001</v>
+        <v>83638.13</v>
       </c>
       <c r="F44" t="n">
+        <v>31</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>28</v>
       </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>26</v>
-      </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>75418.74000000001</v>
+        <v>82286.5</v>
       </c>
       <c r="F45" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,16 +2029,16 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>74393.98</v>
+        <v>82286.28999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,16 +2065,16 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="J46" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>72023.73999999999</v>
+        <v>81297.53</v>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,22 +2101,22 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>70134.8</v>
+        <v>79406.65000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,16 +2137,16 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="J48" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>69617.75</v>
+        <v>79226.27</v>
       </c>
       <c r="F49" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J49" t="n">
         <v>6</v>
@@ -2182,7 +2182,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,28 +2197,28 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>67775.41</v>
+        <v>75844.88</v>
       </c>
       <c r="F50" t="n">
+        <v>23</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>22</v>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>21</v>
-      </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>65926.25</v>
+        <v>70740.67</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>65426.21</v>
+        <v>70341.42</v>
       </c>
       <c r="F52" t="n">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="J52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>64262.66</v>
+        <v>67428.06999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>63452.53</v>
+        <v>67146.59</v>
       </c>
       <c r="F54" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>54978.91</v>
+        <v>66666.08</v>
       </c>
       <c r="F55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2413,28 +2413,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>50421.19</v>
+        <v>61687.28999999999</v>
       </c>
       <c r="F56" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>9</v>
+      </c>
+      <c r="J56" t="n">
         <v>3</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>50401.7</v>
+        <v>59217.78</v>
       </c>
       <c r="F57" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="J57" t="n">
         <v>7</v>
@@ -2470,7 +2470,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>50135.58</v>
+        <v>55946.65</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>49288.95</v>
+        <v>50421.19</v>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>47299.99</v>
+        <v>48333.86</v>
       </c>
       <c r="F60" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44482.2</v>
+        <v>48039.8</v>
       </c>
       <c r="F61" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,16 +2605,16 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>44467.82</v>
+        <v>46977.92</v>
       </c>
       <c r="F62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -2665,34 +2665,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43263.54</v>
+        <v>46016.94</v>
       </c>
       <c r="F63" t="n">
+        <v>14</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>13</v>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>12</v>
-      </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>41421.18</v>
+        <v>45052.51</v>
       </c>
       <c r="F64" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>41383.89</v>
+        <v>41535.55</v>
       </c>
       <c r="F65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2752,13 +2752,13 @@
         <v>12</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>36898.13</v>
+        <v>39176.27</v>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,16 +2785,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>35746.56</v>
+        <v>38844.07</v>
       </c>
       <c r="F67" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>35605.05</v>
+        <v>38667.79</v>
       </c>
       <c r="F68" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>35501.69999999999</v>
+        <v>38496.03</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,22 +2893,22 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>35103.4</v>
+        <v>38166.92</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,10 +2929,10 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33984.66</v>
+        <v>37869.4</v>
       </c>
       <c r="F71" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>32452.52999999999</v>
+        <v>37720.35</v>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,22 +3001,22 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>31829.64</v>
+        <v>36627.98</v>
       </c>
       <c r="F73" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>30363.56</v>
+        <v>36359.37</v>
       </c>
       <c r="F74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29144.03</v>
+        <v>35501.69999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>28503.38</v>
+        <v>31866.1</v>
       </c>
       <c r="F76" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>28402.73</v>
+        <v>31009.28</v>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3181,10 +3181,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>28121.18</v>
+        <v>29642.37</v>
       </c>
       <c r="F78" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3217,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>26834.73</v>
+        <v>27778.82</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>26768.65</v>
+        <v>27536.44</v>
       </c>
       <c r="F80" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>25249.99</v>
+        <v>25933.88</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,16 +3325,16 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>24177.9</v>
+        <v>24349.15</v>
       </c>
       <c r="F82" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -3370,13 +3370,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>23380.51</v>
+        <v>23846.58</v>
       </c>
       <c r="F83" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J83" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>21467.79</v>
+        <v>23527.11</v>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>21444.94</v>
+        <v>23445.75</v>
       </c>
       <c r="F85" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,16 +3469,16 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J85" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>20085.56</v>
+        <v>23095.75</v>
       </c>
       <c r="F86" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3505,16 +3505,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="J86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>19605.94</v>
+        <v>22447.46</v>
       </c>
       <c r="F87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,10 +3541,10 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>19570.32</v>
+        <v>21552.54</v>
       </c>
       <c r="F88" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,16 +3577,16 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>19490.68</v>
+        <v>21551.69</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>19198.29</v>
+        <v>21457.65</v>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>19008.44</v>
+        <v>21185.61</v>
       </c>
       <c r="F91" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,22 +3685,22 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>18382.24</v>
+        <v>19977.1</v>
       </c>
       <c r="F92" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>17846.6</v>
+        <v>19490.68</v>
       </c>
       <c r="F93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,16 +3757,16 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>17718.81</v>
+        <v>19008.44</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3793,22 +3793,22 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>17366.08</v>
+        <v>17846.6</v>
       </c>
       <c r="F95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>1</v>
@@ -3838,13 +3838,13 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>16010.18</v>
+        <v>17718.81</v>
       </c>
       <c r="F96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -3874,13 +3874,13 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>15844.06</v>
+        <v>16469.48</v>
       </c>
       <c r="F97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>14326.02</v>
+        <v>16094.95</v>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3937,16 +3937,16 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J98" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>13712.71</v>
+        <v>15844.06</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -3982,13 +3982,13 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>13673.72</v>
+        <v>15581.36</v>
       </c>
       <c r="F100" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,22 +4009,22 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>13301.68</v>
+        <v>15551.69</v>
       </c>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>13216.94</v>
+        <v>15216.12</v>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -4090,7 +4090,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>12916.95</v>
+        <v>14477.24</v>
       </c>
       <c r="F103" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,16 +4117,16 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>12877.97</v>
+        <v>14441.53</v>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,22 +4153,22 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>12575.42</v>
+        <v>13977.13</v>
       </c>
       <c r="F105" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,16 +4189,16 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>12488.96</v>
+        <v>13757.63</v>
       </c>
       <c r="F106" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -4234,7 +4234,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>12053.4</v>
+        <v>13555.92</v>
       </c>
       <c r="F107" t="n">
         <v>4</v>
@@ -4264,13 +4264,13 @@
         <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4285,34 +4285,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>10922.88</v>
+        <v>13502.55</v>
       </c>
       <c r="F108" t="n">
+        <v>3</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
         <v>1</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4321,28 +4321,28 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>10315.97</v>
+        <v>13234.72</v>
       </c>
       <c r="F109" t="n">
+        <v>7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6</v>
+      </c>
+      <c r="J109" t="n">
         <v>5</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>5</v>
-      </c>
-      <c r="J109" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>10269.46</v>
+        <v>12877.97</v>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,16 +4369,16 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>10093.22</v>
+        <v>12802.52</v>
       </c>
       <c r="F111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,22 +4405,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>9851.700000000001</v>
+        <v>12166.16</v>
       </c>
       <c r="F112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
         <v>2</v>
@@ -4450,7 +4450,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>9828.82</v>
+        <v>12053.4</v>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,16 +4477,16 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>9583.879999999999</v>
+        <v>10912.71</v>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,22 +4513,22 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>9566.93</v>
+        <v>9942.99</v>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -4558,7 +4558,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>9277.119999999999</v>
+        <v>9851.700000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,22 +4585,22 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>9250.860000000001</v>
+        <v>9828.82</v>
       </c>
       <c r="F117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>9002.549999999999</v>
+        <v>8896.599999999999</v>
       </c>
       <c r="F118" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4657,16 +4657,16 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8981.360000000001</v>
+        <v>8303.389999999999</v>
       </c>
       <c r="F119" t="n">
         <v>2</v>
@@ -4696,13 +4696,13 @@
         <v>2</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>8896.599999999999</v>
+        <v>8241.539999999999</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>8364.42</v>
+        <v>7961.88</v>
       </c>
       <c r="F121" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>7963.56</v>
+        <v>7624.58</v>
       </c>
       <c r="F122" t="n">
         <v>3</v>
@@ -4801,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>7925.42</v>
+        <v>7491.49</v>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6729.63</v>
+        <v>7194.900000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -4873,22 +4873,22 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6650.02</v>
+        <v>6246.620000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4909,22 +4909,22 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4933,22 +4933,22 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5507.63</v>
+        <v>5373.719999999999</v>
       </c>
       <c r="F126" t="n">
+        <v>3</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="n">
         <v>1</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>1</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5026,7 +5026,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4483.05</v>
+        <v>4912.71</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5053,16 +5053,16 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4066.95</v>
+        <v>4483.05</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -5092,13 +5092,13 @@
         <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0FTVS34SD</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3897.46</v>
+        <v>4066.95</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
@@ -5134,13 +5134,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3219.5</v>
+        <v>3991.52</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5161,16 +5161,16 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3218.64</v>
+        <v>3639.83</v>
       </c>
       <c r="F133" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5197,16 +5197,16 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3218.64</v>
+        <v>3388.14</v>
       </c>
       <c r="F134" t="n">
         <v>2</v>
@@ -5242,13 +5242,13 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3211.02</v>
+        <v>3261.86</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -5272,19 +5272,19 @@
         <v>1</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3048.3</v>
+        <v>3219.5</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2965.26</v>
+        <v>3218.64</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5341,16 +5341,16 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2877.97</v>
+        <v>3211.02</v>
       </c>
       <c r="F138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -5377,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2795.760000000002</v>
+        <v>3048.3</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
         <v>1</v>
@@ -5422,7 +5422,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2625.42</v>
+        <v>2795.760000000002</v>
       </c>
       <c r="F140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -5449,16 +5449,16 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2404.24</v>
+        <v>2667.79</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -5494,13 +5494,13 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1927.97</v>
+        <v>2404.24</v>
       </c>
       <c r="F142" t="n">
         <v>1</v>
@@ -5530,13 +5530,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1863.56</v>
+        <v>1927.97</v>
       </c>
       <c r="F143" t="n">
         <v>1</v>
@@ -5566,7 +5566,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5596,13 +5596,13 @@
         <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1694.07</v>
+        <v>1355.08</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1694.07</v>
+        <v>1058.47</v>
       </c>
       <c r="F146" t="n">
         <v>1</v>
@@ -5674,13 +5674,13 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -5710,7 +5710,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1312.71</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -5740,19 +5740,19 @@
         <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0BBL47VR5</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5761,22 +5761,22 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1058.47</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
         <v>1</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5854,7 +5854,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5890,7 +5890,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FN7DYB2M</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5917,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -5926,7 +5926,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -5956,6 +5956,42 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>B0FJ8T4WXM</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J155"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[24/07/26 - 22/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[31/07/26 - 29/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2051502.12</v>
+        <v>2271645.85</v>
       </c>
       <c r="F3" t="n">
-        <v>522</v>
+        <v>576</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>506</v>
+        <v>565</v>
       </c>
       <c r="J3" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1769056.45</v>
+        <v>1832713.37</v>
       </c>
       <c r="F4" t="n">
-        <v>795</v>
+        <v>824</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>784</v>
+        <v>826</v>
       </c>
       <c r="J4" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1536908.27</v>
+        <v>1525927.61</v>
       </c>
       <c r="F5" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,10 +589,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="J5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1320153.85</v>
+        <v>1304139.15</v>
       </c>
       <c r="F6" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>235</v>
       </c>
       <c r="J6" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1058566.87</v>
+        <v>1218718.65</v>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>711310.47</v>
+        <v>720086.58</v>
       </c>
       <c r="F8" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="J8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>601772.5600000001</v>
+        <v>625578.33</v>
       </c>
       <c r="F9" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,16 +733,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>444650.22</v>
+        <v>485204.3</v>
       </c>
       <c r="F10" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="J10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>414029.7</v>
+        <v>432289.14</v>
       </c>
       <c r="F11" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>395257.66</v>
+        <v>405598.49</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>386918.01</v>
+        <v>381195.85</v>
       </c>
       <c r="F13" t="n">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="J13" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>362850.17</v>
+        <v>354940.91</v>
       </c>
       <c r="F14" t="n">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>114</v>
+        <v>280</v>
       </c>
       <c r="J14" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>355181.46</v>
+        <v>352889.01</v>
       </c>
       <c r="F15" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -949,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>344047.07</v>
+        <v>332488.94</v>
       </c>
       <c r="F16" t="n">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,16 +985,16 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="J16" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>317009.84</v>
+        <v>317777.28</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>290400.36</v>
+        <v>314786.76</v>
       </c>
       <c r="F18" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,16 +1057,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>289</v>
+        <v>322</v>
       </c>
       <c r="J18" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0B4G5JG4P</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>264699.13</v>
+        <v>285079.8</v>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
@@ -1102,13 +1102,13 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B01ISNU3X4</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>224193.56</v>
+        <v>278159.87</v>
       </c>
       <c r="F20" t="n">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="J20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B0B4G5JG4P</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>210219.6</v>
+        <v>277022.62</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,22 +1165,22 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="J21" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>204603.22</v>
+        <v>233510.5</v>
       </c>
       <c r="F22" t="n">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="J22" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185596.88</v>
+        <v>198941.54</v>
       </c>
       <c r="F23" t="n">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,16 +1237,16 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>178269.4</v>
+        <v>185658.47</v>
       </c>
       <c r="F24" t="n">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="J24" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>178184.74</v>
+        <v>175280.22</v>
       </c>
       <c r="F25" t="n">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>62</v>
+        <v>374</v>
       </c>
       <c r="J25" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>171219.04</v>
+        <v>170496.18</v>
       </c>
       <c r="F26" t="n">
-        <v>366</v>
+        <v>129</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>359</v>
+        <v>131</v>
       </c>
       <c r="J26" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>167786.02</v>
+        <v>170177.07</v>
       </c>
       <c r="F27" t="n">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="J27" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>166686.4</v>
+        <v>165923.56</v>
       </c>
       <c r="F28" t="n">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,16 +1417,16 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>166341.51</v>
+        <v>157139.28</v>
       </c>
       <c r="F29" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>152020.35</v>
+        <v>136341.53</v>
       </c>
       <c r="F30" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150239.92</v>
+        <v>131179.72</v>
       </c>
       <c r="F31" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="J31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>124338.91</v>
+        <v>124407.58</v>
       </c>
       <c r="F32" t="n">
         <v>56</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J32" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>119071.26</v>
+        <v>122345.38</v>
       </c>
       <c r="F33" t="n">
-        <v>38</v>
+        <v>268</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>35</v>
+        <v>252</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>114622.11</v>
+        <v>122290.75</v>
       </c>
       <c r="F34" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="J34" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>110380.5</v>
+        <v>121053.36</v>
       </c>
       <c r="F35" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J35" t="n">
         <v>8</v>
@@ -1678,13 +1678,13 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>109318.1</v>
+        <v>118556.84</v>
       </c>
       <c r="F36" t="n">
-        <v>240</v>
+        <v>73</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,22 +1705,22 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>242</v>
+        <v>75</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106802.46</v>
+        <v>118349.23</v>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,22 +1741,22 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="J37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105004.31</v>
+        <v>115961</v>
       </c>
       <c r="F38" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>99317.87</v>
+        <v>100062.85</v>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,16 +1813,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>94661.08</v>
+        <v>98720.33</v>
       </c>
       <c r="F40" t="n">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,16 +1849,16 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>87994.05</v>
+        <v>94821.17000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>87788.97</v>
+        <v>93979.73000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,22 +1921,22 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>87356.85000000001</v>
+        <v>93244.83</v>
       </c>
       <c r="F43" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1981,34 +1981,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>83638.13</v>
+        <v>90077.00999999999</v>
       </c>
       <c r="F44" t="n">
+        <v>79</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>78</v>
+      </c>
+      <c r="J44" t="n">
         <v>31</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>28</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>82286.5</v>
+        <v>89979.61</v>
       </c>
       <c r="F45" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>82286.28999999999</v>
+        <v>82273.81</v>
       </c>
       <c r="F46" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,16 +2065,16 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>81297.53</v>
+        <v>80838.14999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,16 +2101,16 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="J47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>79406.65000000001</v>
+        <v>80144.91</v>
       </c>
       <c r="F48" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>79226.27</v>
+        <v>79829.72</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
         <v>6</v>
@@ -2182,7 +2182,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>75844.88</v>
+        <v>79226.25999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,16 +2209,16 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>70740.67</v>
+        <v>72826.33</v>
       </c>
       <c r="F51" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>70341.42</v>
+        <v>68867.89999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="J52" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>67428.06999999999</v>
+        <v>68141.42</v>
       </c>
       <c r="F53" t="n">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="J53" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>67146.59</v>
+        <v>66666.09</v>
       </c>
       <c r="F54" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2353,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>66666.08</v>
+        <v>66120.35000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="J55" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>61687.28999999999</v>
+        <v>65604.28</v>
       </c>
       <c r="F56" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
         <v>3</v>
@@ -2434,7 +2434,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>59217.78</v>
+        <v>65257.55</v>
       </c>
       <c r="F57" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>55946.65</v>
+        <v>62288.96</v>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>50421.19</v>
+        <v>54640.73</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>48333.86</v>
+        <v>54557.61</v>
       </c>
       <c r="F60" t="n">
         <v>12</v>
@@ -2569,16 +2569,16 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>48039.8</v>
+        <v>49943.17</v>
       </c>
       <c r="F61" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2605,22 +2605,22 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>46977.92</v>
+        <v>47809.34</v>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -2686,7 +2686,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>45052.51</v>
+        <v>44351.66</v>
       </c>
       <c r="F64" t="n">
         <v>11</v>
@@ -2713,16 +2713,16 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>41535.55</v>
+        <v>43624.4</v>
       </c>
       <c r="F65" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>39176.27</v>
+        <v>42055.93</v>
       </c>
       <c r="F66" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>38844.07</v>
+        <v>41848.3</v>
       </c>
       <c r="F67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
         <v>6</v>
@@ -2830,7 +2830,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>38667.79</v>
+        <v>39233</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="J68" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>38496.03</v>
+        <v>38877.04</v>
       </c>
       <c r="F69" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,22 +2893,22 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J69" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38166.92</v>
+        <v>37593.24</v>
       </c>
       <c r="F70" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37869.4</v>
+        <v>37570.36</v>
       </c>
       <c r="F71" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>37720.35</v>
+        <v>36579.63</v>
       </c>
       <c r="F72" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,22 +3001,22 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J72" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>36627.98</v>
+        <v>36359.37</v>
       </c>
       <c r="F73" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>36359.37</v>
+        <v>36009.32</v>
       </c>
       <c r="F74" t="n">
         <v>9</v>
@@ -3076,13 +3076,13 @@
         <v>9</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>35501.69999999999</v>
+        <v>35514.57</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>31866.1</v>
+        <v>35501.69999999999</v>
       </c>
       <c r="F76" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>31009.28</v>
+        <v>35456.76</v>
       </c>
       <c r="F77" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3181,16 +3181,16 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>29642.37</v>
+        <v>32201.7</v>
       </c>
       <c r="F78" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -3217,16 +3217,16 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>27778.82</v>
+        <v>31866.1</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>27536.44</v>
+        <v>31336.45</v>
       </c>
       <c r="F80" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,16 +3289,16 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>25933.88</v>
+        <v>24349.14</v>
       </c>
       <c r="F81" t="n">
         <v>8</v>
@@ -3328,13 +3328,13 @@
         <v>8</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>24349.15</v>
+        <v>24348.3</v>
       </c>
       <c r="F82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -3370,13 +3370,13 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>23846.58</v>
+        <v>23527.11</v>
       </c>
       <c r="F83" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>23527.11</v>
+        <v>22897.5</v>
       </c>
       <c r="F84" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>23445.75</v>
+        <v>22605.09</v>
       </c>
       <c r="F85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -3478,7 +3478,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23095.75</v>
+        <v>22544.9</v>
       </c>
       <c r="F86" t="n">
         <v>7</v>
@@ -3505,10 +3505,10 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3550,13 +3550,13 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21552.54</v>
+        <v>21644.04</v>
       </c>
       <c r="F88" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>21551.69</v>
+        <v>21551.68</v>
       </c>
       <c r="F89" t="n">
         <v>5</v>
@@ -3616,13 +3616,13 @@
         <v>5</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>21457.65</v>
+        <v>20745.77</v>
       </c>
       <c r="F90" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>21185.61</v>
+        <v>20056.77</v>
       </c>
       <c r="F91" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>19977.1</v>
+        <v>19490.68</v>
       </c>
       <c r="F92" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>19490.68</v>
+        <v>18604.26</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -3766,7 +3766,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>19008.44</v>
+        <v>17993.23</v>
       </c>
       <c r="F94" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3793,16 +3793,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>17846.6</v>
+        <v>17018.77</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,16 +3829,16 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3853,34 +3853,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>17718.81</v>
+        <v>16961.87</v>
       </c>
       <c r="F96" t="n">
+        <v>5</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" t="n">
         <v>2</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3889,34 +3889,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>16469.48</v>
+        <v>16868.66</v>
       </c>
       <c r="F97" t="n">
+        <v>24</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>24</v>
+      </c>
+      <c r="J97" t="n">
         <v>6</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>6</v>
-      </c>
-      <c r="J97" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16094.95</v>
+        <v>16135.6</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3937,10 +3937,10 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>15844.06</v>
+        <v>15844.07</v>
       </c>
       <c r="F99" t="n">
         <v>4</v>
@@ -3982,7 +3982,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>15581.36</v>
+        <v>15551.69</v>
       </c>
       <c r="F100" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>15551.69</v>
+        <v>15336.44</v>
       </c>
       <c r="F101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>15216.12</v>
+        <v>15131.35</v>
       </c>
       <c r="F102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>14477.24</v>
+        <v>15103.4</v>
       </c>
       <c r="F103" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,16 +4117,16 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>14441.53</v>
+        <v>14943.2</v>
       </c>
       <c r="F104" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,22 +4153,22 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4177,34 +4177,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>13977.13</v>
+        <v>14438.14</v>
       </c>
       <c r="F105" t="n">
+        <v>13</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>13</v>
+      </c>
+      <c r="J105" t="n">
         <v>7</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>6</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>13757.63</v>
+        <v>14131.34</v>
       </c>
       <c r="F106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4225,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>13555.92</v>
+        <v>13977.15</v>
       </c>
       <c r="F107" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4261,22 +4261,22 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>13502.55</v>
+        <v>13977.13</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>13234.72</v>
+        <v>13757.63</v>
       </c>
       <c r="F109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4336,13 +4336,13 @@
         <v>6</v>
       </c>
       <c r="J109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>12877.97</v>
+        <v>13555.92</v>
       </c>
       <c r="F110" t="n">
         <v>4</v>
@@ -4372,13 +4372,13 @@
         <v>4</v>
       </c>
       <c r="J110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>12802.52</v>
+        <v>13348.28</v>
       </c>
       <c r="F111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,22 +4405,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>12166.16</v>
+        <v>13271.18</v>
       </c>
       <c r="F112" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -4441,16 +4441,16 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>12053.4</v>
+        <v>11193.2</v>
       </c>
       <c r="F113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,22 +4477,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>10912.71</v>
+        <v>10877.96</v>
       </c>
       <c r="F114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
         <v>2</v>
@@ -4558,13 +4558,13 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>9851.700000000001</v>
+        <v>9794.130000000001</v>
       </c>
       <c r="F116" t="n">
         <v>5</v>
@@ -4594,7 +4594,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>9828.82</v>
+        <v>8896.599999999999</v>
       </c>
       <c r="F117" t="n">
         <v>2</v>
@@ -4630,7 +4630,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>8896.599999999999</v>
+        <v>8303.389999999999</v>
       </c>
       <c r="F118" t="n">
         <v>2</v>
@@ -4666,7 +4666,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0FTVS34SD</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4681,28 +4681,28 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8303.389999999999</v>
+        <v>8056.759999999999</v>
       </c>
       <c r="F119" t="n">
+        <v>6</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5</v>
+      </c>
+      <c r="J119" t="n">
         <v>2</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>2</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>8241.539999999999</v>
+        <v>7624.58</v>
       </c>
       <c r="F120" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4729,16 +4729,16 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J120" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>7961.88</v>
+        <v>6719.52</v>
       </c>
       <c r="F121" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,22 +4765,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>7624.58</v>
+        <v>6650.84</v>
       </c>
       <c r="F122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -4801,10 +4801,10 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>7491.49</v>
+        <v>5967.77</v>
       </c>
       <c r="F123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4837,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J123" t="n">
         <v>3</v>
@@ -4846,7 +4846,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>7194.900000000001</v>
+        <v>5373.719999999999</v>
       </c>
       <c r="F124" t="n">
         <v>3</v>
@@ -4873,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -4882,13 +4882,13 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6246.620000000001</v>
+        <v>5253.4</v>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4909,16 +4909,16 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5373.719999999999</v>
+        <v>5083.9</v>
       </c>
       <c r="F126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -4945,22 +4945,22 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0CCVBQRFX</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5083.9</v>
+        <v>5041.53</v>
       </c>
       <c r="F127" t="n">
         <v>1</v>
@@ -4990,7 +4990,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5041.53</v>
+        <v>4912.71</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5026,13 +5026,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4912.71</v>
+        <v>4128.82</v>
       </c>
       <c r="F129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5062,7 +5062,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0C4YSV3XL</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4483.05</v>
+        <v>4066.95</v>
       </c>
       <c r="F130" t="n">
         <v>1</v>
@@ -5092,13 +5092,13 @@
         <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4066.95</v>
+        <v>4022.87</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3991.52</v>
+        <v>3879.66</v>
       </c>
       <c r="F132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         <v>3</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -5242,7 +5242,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3261.86</v>
+        <v>3219.5</v>
       </c>
       <c r="F135" t="n">
         <v>1</v>
@@ -5278,13 +5278,13 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3219.5</v>
+        <v>3218.64</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3218.64</v>
+        <v>3211.02</v>
       </c>
       <c r="F137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -5350,7 +5350,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3211.02</v>
+        <v>2795.760000000002</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -5380,13 +5380,13 @@
         <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3048.3</v>
+        <v>2710.16</v>
       </c>
       <c r="F139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5413,22 +5413,22 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2795.760000000002</v>
+        <v>2450.84</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -5452,13 +5452,13 @@
         <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2667.79</v>
+        <v>2404.24</v>
       </c>
       <c r="F141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2404.24</v>
+        <v>2159.32</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5530,13 +5530,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,34 +5545,34 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1927.97</v>
+        <v>2032.2</v>
       </c>
       <c r="F143" t="n">
+        <v>2</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>2</v>
+      </c>
+      <c r="J143" t="n">
         <v>1</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1863.56</v>
+        <v>1927.97</v>
       </c>
       <c r="F144" t="n">
         <v>1</v>
@@ -5602,7 +5602,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1355.08</v>
+        <v>1863.56</v>
       </c>
       <c r="F145" t="n">
         <v>1</v>
@@ -5638,7 +5638,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1058.47</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -5710,7 +5710,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0C4YSV3XL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>1</v>
@@ -5746,13 +5746,13 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B0BBL47VR5</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5776,13 +5776,13 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -5854,7 +5854,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5890,7 +5890,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B0FN7DYB2M</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -5917,81 +5917,9 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>B0FJ2HZCVN</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>B0FJ8T4WXM</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/raw/returns/1p Returns.xlsx
+++ b/data/raw/returns/1p Returns.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Viewing Range=[31/07/26 - 29/08/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
+          <t>Viewing Range=[07/08/26 - 05/09/26]  Currency=[INR]  View By=[ASIN]  Distributor View=[Manufacturing]  Source=[SP-API]</t>
         </is>
       </c>
     </row>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2271645.85</v>
+        <v>2112530.6</v>
       </c>
       <c r="F3" t="n">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>565</v>
+        <v>532</v>
       </c>
       <c r="J3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1832713.37</v>
+        <v>1686225.15</v>
       </c>
       <c r="F4" t="n">
-        <v>824</v>
+        <v>760</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>826</v>
+        <v>759</v>
       </c>
       <c r="J4" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1525927.61</v>
+        <v>1470708.97</v>
       </c>
       <c r="F5" t="n">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -589,16 +589,16 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1304139.15</v>
+        <v>1203106.79</v>
       </c>
       <c r="F6" t="n">
-        <v>240</v>
+        <v>161</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>235</v>
+        <v>159</v>
       </c>
       <c r="J6" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1218718.65</v>
+        <v>1177802.52</v>
       </c>
       <c r="F7" t="n">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="J7" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>720086.58</v>
+        <v>717714.45</v>
       </c>
       <c r="F8" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="J8" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>625578.33</v>
+        <v>621803.73</v>
       </c>
       <c r="F9" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>485204.3</v>
+        <v>548298.38</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -769,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>432289.14</v>
+        <v>460502.54</v>
       </c>
       <c r="F11" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>405598.49</v>
+        <v>400571.43</v>
       </c>
       <c r="F12" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -841,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>381195.85</v>
+        <v>380690.9</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="J13" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>354940.91</v>
+        <v>363762.12</v>
       </c>
       <c r="F14" t="n">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -913,10 +913,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="J14" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>352889.01</v>
+        <v>361363.58</v>
       </c>
       <c r="F15" t="n">
         <v>43</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>332488.94</v>
+        <v>357865.22</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>317777.28</v>
+        <v>356412.96</v>
       </c>
       <c r="F17" t="n">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>314786.76</v>
+        <v>312594.34</v>
       </c>
       <c r="F18" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1057,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="J18" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>285079.8</v>
+        <v>304305.24</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>278159.87</v>
+        <v>267243.76</v>
       </c>
       <c r="F20" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>277022.62</v>
+        <v>225473.54</v>
       </c>
       <c r="F21" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1165,10 +1165,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>233510.5</v>
+        <v>209319.86</v>
       </c>
       <c r="F22" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>198941.54</v>
+        <v>204862.7</v>
       </c>
       <c r="F23" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1237,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185658.47</v>
+        <v>195269.49</v>
       </c>
       <c r="F24" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>57</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>175280.22</v>
+        <v>171829.22</v>
       </c>
       <c r="F25" t="n">
-        <v>374</v>
+        <v>130</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>374</v>
+        <v>131</v>
       </c>
       <c r="J25" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>170496.18</v>
+        <v>166117.53</v>
       </c>
       <c r="F26" t="n">
-        <v>129</v>
+        <v>356</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1345,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>131</v>
+        <v>351</v>
       </c>
       <c r="J26" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>170177.07</v>
+        <v>141460.84</v>
       </c>
       <c r="F27" t="n">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1381,22 +1381,22 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>165923.56</v>
+        <v>138777.16</v>
       </c>
       <c r="F28" t="n">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1417,22 +1417,22 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="J28" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>157139.28</v>
+        <v>126829.67</v>
       </c>
       <c r="F29" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="J29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>136341.53</v>
+        <v>124779.72</v>
       </c>
       <c r="F30" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1489,16 +1489,16 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>131179.72</v>
+        <v>124554.57</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>273</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1525,22 +1525,22 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>62</v>
+        <v>264</v>
       </c>
       <c r="J31" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>124407.58</v>
+        <v>123348.31</v>
       </c>
       <c r="F32" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>122345.38</v>
+        <v>122796.01</v>
       </c>
       <c r="F33" t="n">
-        <v>268</v>
+        <v>95</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1597,22 +1597,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>252</v>
+        <v>93</v>
       </c>
       <c r="J33" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>122290.75</v>
+        <v>119274.53</v>
       </c>
       <c r="F34" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1633,22 +1633,22 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0B4G763WS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>121053.36</v>
+        <v>118570.33</v>
       </c>
       <c r="F35" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1669,22 +1669,22 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>118556.84</v>
+        <v>116027.02</v>
       </c>
       <c r="F36" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1705,22 +1705,22 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="J36" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>118349.23</v>
+        <v>110387.33</v>
       </c>
       <c r="F37" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1741,16 +1741,16 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="J37" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0B4G763WS</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>115961</v>
+        <v>103208.45</v>
       </c>
       <c r="F38" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1780,19 +1780,19 @@
         <v>34</v>
       </c>
       <c r="J38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100062.85</v>
+        <v>100996.68</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1813,16 +1813,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="J39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>98720.33</v>
+        <v>99706.86</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J40" t="n">
         <v>3</v>
@@ -1858,7 +1858,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>94821.17000000001</v>
+        <v>97851.84</v>
       </c>
       <c r="F41" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1885,16 +1885,16 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>93979.73000000001</v>
+        <v>89396.59</v>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>93244.83</v>
+        <v>87704.23</v>
       </c>
       <c r="F43" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1957,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>90077.00999999999</v>
+        <v>87280.55</v>
       </c>
       <c r="F44" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1993,22 +1993,22 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="J44" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0CCV74CL7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>89979.61</v>
+        <v>86725.48</v>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>82273.81</v>
+        <v>83262.78</v>
       </c>
       <c r="F46" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2065,16 +2065,16 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>80838.14999999999</v>
+        <v>78160.06</v>
       </c>
       <c r="F47" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2101,16 +2101,16 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>80144.91</v>
+        <v>70579.67999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2137,22 +2137,22 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B0CCV74CL7</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>79829.72</v>
+        <v>68200.77</v>
       </c>
       <c r="F49" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2173,22 +2173,22 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>79226.25999999999</v>
+        <v>67024.66</v>
       </c>
       <c r="F50" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -2218,7 +2218,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>72826.33</v>
+        <v>65653.36</v>
       </c>
       <c r="F51" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B0B4G7VWXD</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>68867.89999999999</v>
+        <v>64821.99</v>
       </c>
       <c r="F52" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G7VWXD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>68141.42</v>
+        <v>64548.4</v>
       </c>
       <c r="F53" t="n">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -2341,28 +2341,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>66666.09</v>
+        <v>63196.58</v>
       </c>
       <c r="F54" t="n">
+        <v>38</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>40</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>41</v>
-      </c>
       <c r="J54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>66120.35000000001</v>
+        <v>61338.97</v>
       </c>
       <c r="F55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2389,16 +2389,16 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65604.28</v>
+        <v>60375.38</v>
       </c>
       <c r="F56" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2425,22 +2425,22 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>65257.55</v>
+        <v>58990.7</v>
       </c>
       <c r="F57" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>62288.96</v>
+        <v>58001.73</v>
       </c>
       <c r="F58" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2497,16 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>54640.73</v>
+        <v>55911.07</v>
       </c>
       <c r="F59" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2533,16 +2533,16 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>54557.61</v>
+        <v>52645.83</v>
       </c>
       <c r="F60" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2569,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
         <v>9</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>49943.17</v>
+        <v>49943.19</v>
       </c>
       <c r="F61" t="n">
         <v>17</v>
@@ -2608,19 +2608,19 @@
         <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>47809.34</v>
+        <v>45989.85</v>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2641,16 +2641,16 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>46016.94</v>
+        <v>44786.8</v>
       </c>
       <c r="F63" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2677,16 +2677,16 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>44351.66</v>
+        <v>42573.72</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2716,13 +2716,13 @@
         <v>12</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>43624.4</v>
+        <v>40512.7</v>
       </c>
       <c r="F65" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B0B4G59Y8W</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>42055.93</v>
+        <v>40306.76</v>
       </c>
       <c r="F66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2785,16 +2785,16 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>41848.3</v>
+        <v>39793.22</v>
       </c>
       <c r="F67" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2821,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2845,10 +2845,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>39233</v>
+        <v>39570.35</v>
       </c>
       <c r="F68" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0B4G8ZB64</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>38877.04</v>
+        <v>38366.97</v>
       </c>
       <c r="F69" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J69" t="n">
         <v>5</v>
@@ -2902,13 +2902,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>37593.24</v>
+        <v>35280.48</v>
       </c>
       <c r="F70" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>B0B4G8ZB64</t>
+          <t>B0B4G59Y8W</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>37570.36</v>
+        <v>35236.45</v>
       </c>
       <c r="F71" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2965,16 +2965,16 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>36579.63</v>
+        <v>34734.75</v>
       </c>
       <c r="F72" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -3001,22 +3001,22 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>36359.37</v>
+        <v>34211.88</v>
       </c>
       <c r="F73" t="n">
+        <v>21</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>20</v>
+      </c>
+      <c r="J73" t="n">
         <v>9</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="n">
-        <v>9</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>36009.32</v>
+        <v>33972.04</v>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>35514.57</v>
+        <v>33710.1</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>35501.69999999999</v>
+        <v>32780.43</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3145,16 +3145,16 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>35456.76</v>
+        <v>32343.19</v>
       </c>
       <c r="F77" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -3181,16 +3181,16 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J77" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>32201.7</v>
+        <v>32210.33</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
@@ -3226,7 +3226,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>31866.1</v>
+        <v>32201.7</v>
       </c>
       <c r="F79" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -3253,16 +3253,16 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>31336.45</v>
+        <v>31772.88</v>
       </c>
       <c r="F80" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J80" t="n">
         <v>2</v>
@@ -3298,7 +3298,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>24349.14</v>
+        <v>31604.24</v>
       </c>
       <c r="F81" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -3325,22 +3325,22 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B078WNW4YW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>24348.3</v>
+        <v>30454.2</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>B0B4G94VP3</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>23527.11</v>
+        <v>27144.06</v>
       </c>
       <c r="F83" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="J83" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>22897.5</v>
+        <v>26974.59</v>
       </c>
       <c r="F84" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>22605.09</v>
+        <v>26402.54</v>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3469,10 +3469,10 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -3514,7 +3514,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>22447.46</v>
+        <v>21835.59</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3541,22 +3541,22 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>B078WNW4YW</t>
+          <t>B0FTVS34SD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21644.04</v>
+        <v>21521.19</v>
       </c>
       <c r="F88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>21551.68</v>
+        <v>20745.77</v>
       </c>
       <c r="F89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>20745.77</v>
+        <v>19490.68</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>20056.77</v>
+        <v>19351.7</v>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>19490.68</v>
+        <v>18514.46</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>18604.26</v>
+        <v>18164.4</v>
       </c>
       <c r="F93" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
         <v>1</v>
@@ -3766,7 +3766,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>17993.23</v>
+        <v>17115.24</v>
       </c>
       <c r="F94" t="n">
         <v>4</v>
@@ -3793,16 +3793,16 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>17018.77</v>
+        <v>16896.62</v>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -3829,16 +3829,16 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J95" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>16961.87</v>
+        <v>16667.79</v>
       </c>
       <c r="F96" t="n">
         <v>5</v>
@@ -3865,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>16868.66</v>
+        <v>16094.95</v>
       </c>
       <c r="F97" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3901,16 +3901,16 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>16135.6</v>
+        <v>15336.44</v>
       </c>
       <c r="F98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>15844.07</v>
+        <v>14710.19</v>
       </c>
       <c r="F99" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>15551.69</v>
+        <v>14653.51</v>
       </c>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>15336.44</v>
+        <v>14131.34</v>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4045,16 +4045,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>B0B4G1HPL5</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4069,10 +4069,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>15131.35</v>
+        <v>13266.08</v>
       </c>
       <c r="F102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -4081,16 +4081,16 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>15103.4</v>
+        <v>11692.38</v>
       </c>
       <c r="F103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -4117,16 +4117,16 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>14943.2</v>
+        <v>11604.24</v>
       </c>
       <c r="F104" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J104" t="n">
         <v>3</v>
@@ -4162,7 +4162,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0B4G1HPL5</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>14438.14</v>
+        <v>11573.73</v>
       </c>
       <c r="F105" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -4189,22 +4189,22 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>14131.34</v>
+        <v>11385.59</v>
       </c>
       <c r="F106" t="n">
         <v>5</v>
@@ -4225,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>13977.15</v>
+        <v>11176.27</v>
       </c>
       <c r="F107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4261,16 +4261,16 @@
         <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>B0CSCT63BL</t>
+          <t>B08V1JS3NY</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>13977.13</v>
+        <v>10877.96</v>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0BRKFP94K</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>13757.63</v>
+        <v>10039.82</v>
       </c>
       <c r="F109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -4342,7 +4342,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>13555.92</v>
+        <v>9942.99</v>
       </c>
       <c r="F110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4369,16 +4369,16 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>13348.28</v>
+        <v>9571.17</v>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4405,16 +4405,16 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>13271.18</v>
+        <v>8978.82</v>
       </c>
       <c r="F112" t="n">
         <v>3</v>
@@ -4450,7 +4450,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>11193.2</v>
+        <v>8664.4</v>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4477,22 +4477,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B08V1JS3NY</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>10877.96</v>
+        <v>8056.759999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4513,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J114" t="n">
         <v>2</v>
@@ -4522,13 +4522,13 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0BG8CJXHH</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>9942.99</v>
+        <v>7872.780000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4549,22 +4549,22 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B0BG8CJXHH</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4573,10 +4573,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>9794.130000000001</v>
+        <v>7626.27</v>
       </c>
       <c r="F116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4585,16 +4585,16 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>8896.599999999999</v>
+        <v>7624.58</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>B0FTVS34SD</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4645,28 +4645,28 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>8303.389999999999</v>
+        <v>6729.63</v>
       </c>
       <c r="F118" t="n">
+        <v>9</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>8</v>
+      </c>
+      <c r="J118" t="n">
         <v>2</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>2</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>8056.759999999999</v>
+        <v>6332.21</v>
       </c>
       <c r="F119" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0CSCT63BL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>7624.58</v>
+        <v>5844.91</v>
       </c>
       <c r="F120" t="n">
         <v>3</v>
@@ -4738,7 +4738,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6719.52</v>
+        <v>5041.53</v>
       </c>
       <c r="F121" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4765,22 +4765,22 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>B0BRKFP94K</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6650.84</v>
+        <v>4912.71</v>
       </c>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -4801,16 +4801,16 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5967.77</v>
+        <v>4912.71</v>
       </c>
       <c r="F123" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4861,28 +4861,28 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5373.719999999999</v>
+        <v>4570.35</v>
       </c>
       <c r="F124" t="n">
+        <v>7</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>8</v>
+      </c>
+      <c r="J124" t="n">
         <v>3</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4897,10 +4897,10 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5253.4</v>
+        <v>4401.69</v>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -4909,22 +4909,22 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>B0CCVBQRFX</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5083.9</v>
+        <v>4236.44</v>
       </c>
       <c r="F126" t="n">
         <v>1</v>
@@ -4954,13 +4954,13 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5041.53</v>
+        <v>4128.82</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -4990,7 +4990,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4912.71</v>
+        <v>4066.95</v>
       </c>
       <c r="F128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5026,13 +5026,13 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4128.82</v>
+        <v>4065.24</v>
       </c>
       <c r="F129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5062,7 +5062,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5077,10 +5077,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4066.95</v>
+        <v>4022.87</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5089,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -5098,7 +5098,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4022.87</v>
+        <v>3879.66</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -5134,13 +5134,13 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3879.66</v>
+        <v>3557.62</v>
       </c>
       <c r="F132" t="n">
         <v>2</v>
@@ -5161,16 +5161,16 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3639.83</v>
+        <v>3303.38</v>
       </c>
       <c r="F133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3388.14</v>
+        <v>3211.02</v>
       </c>
       <c r="F134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -5242,13 +5242,13 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>B09Z5Q194D</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3219.5</v>
+        <v>3005.94</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -5269,22 +5269,22 @@
         <v>0</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B089FVQD3Z</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3218.64</v>
+        <v>2372.04</v>
       </c>
       <c r="F136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -5314,7 +5314,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0BLKB6FRR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3211.02</v>
+        <v>2159.32</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -5350,7 +5350,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0B4FZS38V</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2795.760000000002</v>
+        <v>1948.31</v>
       </c>
       <c r="F138" t="n">
         <v>1</v>
@@ -5380,19 +5380,19 @@
         <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2710.16</v>
+        <v>1927.97</v>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -5422,13 +5422,13 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>B089FVQD3Z</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2450.84</v>
+        <v>1863.56</v>
       </c>
       <c r="F140" t="n">
         <v>1</v>
@@ -5458,7 +5458,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>B0BLKB55BM</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2404.24</v>
+        <v>1694.07</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -5485,16 +5485,16 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>B0BLKB6FRR</t>
+          <t>B0B4G5ZLTB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2159.32</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -5530,13 +5530,13 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>B0BLKCSJ7Z</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2032.2</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -5557,16 +5557,16 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B09Z5Q194D</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5581,34 +5581,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1927.97</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
         <v>1</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0CCVBQRFX</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Audio Array</t>
+          <t>Tonor</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1863.56</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B0B4G5ZLTB</t>
+          <t>B0BLKCSJ7Z</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5665,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
         <v>1</v>
@@ -5674,13 +5674,13 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tonor</t>
+          <t>Audio Array</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -5740,13 +5740,13 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5773,16 +5773,16 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0BLKB55BM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5818,7 +5818,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>B0BLNCP74M</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -5854,7 +5854,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>-1707.63</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -5884,42 +5884,6 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>B0FJ8T4WXM</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Audio Array</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
         <v>0</v>
       </c>
     </row>
